--- a/research/traditional_assets/database/data/switzerland/switzerland_steel.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_steel.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,118 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.09720000000000001</v>
+        <v>-0.065</v>
       </c>
       <c r="G2">
-        <v>0.1029666397321944</v>
+        <v>-0.006723062061042792</v>
       </c>
       <c r="H2">
-        <v>0.1029666397321944</v>
+        <v>-0.008877052818464268</v>
       </c>
       <c r="I2">
-        <v>0.05529262380237793</v>
+        <v>-0.06895381321636511</v>
       </c>
       <c r="J2">
-        <v>0.05529262380237793</v>
+        <v>-0.06895381321636511</v>
       </c>
       <c r="K2">
-        <v>-56.3</v>
+        <v>-344.1</v>
       </c>
       <c r="L2">
-        <v>-0.06498903382200162</v>
+        <v>-0.08984099631863397</v>
       </c>
       <c r="M2">
-        <v>0.051</v>
+        <v>0.265</v>
       </c>
       <c r="N2">
-        <v>6.544334659309636E-05</v>
+        <v>0.0002840604566405831</v>
       </c>
       <c r="O2">
-        <v>-0.0009058614564831261</v>
+        <v>-0.0007701249636733507</v>
       </c>
       <c r="P2">
         <v>0.051</v>
       </c>
       <c r="Q2">
-        <v>6.544334659309636E-05</v>
+        <v>5.466823882516883E-05</v>
       </c>
       <c r="R2">
-        <v>-0.0009058614564831261</v>
+        <v>-0.0001482127288578901</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.8075471698113207</v>
       </c>
       <c r="U2">
-        <v>115.1</v>
+        <v>150.5</v>
       </c>
       <c r="V2">
-        <v>0.1476966508404979</v>
+        <v>0.1613249008468217</v>
       </c>
       <c r="W2">
-        <v>-0.04406700062617408</v>
+        <v>-0.2899039396280535</v>
       </c>
       <c r="X2">
-        <v>0.08849824647868032</v>
+        <v>0.1723348187494089</v>
       </c>
       <c r="Y2">
-        <v>-0.1325652471048544</v>
+        <v>-0.4622387583774624</v>
       </c>
       <c r="Z2">
-        <v>0.7554985784801075</v>
+        <v>1.412924788620166</v>
       </c>
       <c r="AA2">
-        <v>0.04177349868313188</v>
+        <v>-0.07885111908116917</v>
       </c>
       <c r="AB2">
-        <v>0.08855736602569302</v>
+        <v>0.08732906137019927</v>
       </c>
       <c r="AC2">
-        <v>-0.04678386734256113</v>
+        <v>-0.1661801804513685</v>
       </c>
       <c r="AD2">
-        <v>3.62</v>
+        <v>714.12</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.62</v>
+        <v>714.12</v>
       </c>
       <c r="AG2">
-        <v>-111.48</v>
+        <v>563.62</v>
       </c>
       <c r="AH2">
-        <v>0.004623716343943187</v>
+        <v>0.4335830773153939</v>
       </c>
       <c r="AI2">
-        <v>0.003336959126859756</v>
+        <v>0.3038136242193217</v>
       </c>
       <c r="AJ2">
-        <v>-0.1669312090084154</v>
+        <v>0.3766204260551145</v>
       </c>
       <c r="AK2">
-        <v>-0.1149610196757827</v>
+        <v>0.2561885801038172</v>
       </c>
       <c r="AL2">
-        <v>0.102</v>
+        <v>84.30200000000001</v>
       </c>
       <c r="AM2">
-        <v>-4.448</v>
+        <v>78.572</v>
       </c>
       <c r="AN2">
-        <v>0.03514563106796117</v>
+        <v>-5.297626112759644</v>
       </c>
       <c r="AO2">
-        <v>469.6078431372549</v>
+        <v>-3.132784512822946</v>
       </c>
       <c r="AP2">
-        <v>-1.082330097087379</v>
+        <v>-4.181157270029673</v>
       </c>
       <c r="AQ2">
-        <v>-10.76888489208633</v>
+        <v>-3.361248281830678</v>
       </c>
     </row>
     <row r="3">
@@ -775,10 +775,10 @@
         <v>-0.04406700062617408</v>
       </c>
       <c r="X3">
-        <v>0.08849824647868032</v>
+        <v>0.08847079530251829</v>
       </c>
       <c r="Y3">
-        <v>-0.1325652471048544</v>
+        <v>-0.1325377959286924</v>
       </c>
       <c r="Z3">
         <v>0.7554985784801075</v>
@@ -787,10 +787,10 @@
         <v>0.04177349868313188</v>
       </c>
       <c r="AB3">
-        <v>0.08855736602569302</v>
+        <v>0.08853004177598287</v>
       </c>
       <c r="AC3">
-        <v>-0.04678386734256113</v>
+        <v>-0.04675654309285098</v>
       </c>
       <c r="AD3">
         <v>3.62</v>
@@ -833,6 +833,137 @@
       </c>
       <c r="AQ3">
         <v>-10.76888489208633</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Swiss Steel Holding AG (SWX:STLN)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.0328</v>
+      </c>
+      <c r="G4">
+        <v>-0.03878466833119643</v>
+      </c>
+      <c r="H4">
+        <v>-0.04156825696740671</v>
+      </c>
+      <c r="I4">
+        <v>-0.1052702611512248</v>
+      </c>
+      <c r="J4">
+        <v>-0.1052702611512248</v>
+      </c>
+      <c r="K4">
+        <v>-287.8</v>
+      </c>
+      <c r="L4">
+        <v>-0.09710506781834131</v>
+      </c>
+      <c r="M4">
+        <v>0.214</v>
+      </c>
+      <c r="N4">
+        <v>0.001393229166666667</v>
+      </c>
+      <c r="O4">
+        <v>-0.0007435719249478804</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0.214</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>35.4</v>
+      </c>
+      <c r="V4">
+        <v>0.23046875</v>
+      </c>
+      <c r="W4">
+        <v>-0.5357408786299329</v>
+      </c>
+      <c r="X4">
+        <v>0.2561988421962995</v>
+      </c>
+      <c r="Y4">
+        <v>-0.7919397208262324</v>
+      </c>
+      <c r="Z4">
+        <v>1.894891630969887</v>
+      </c>
+      <c r="AA4">
+        <v>-0.1994757368454702</v>
+      </c>
+      <c r="AB4">
+        <v>0.0861280809644157</v>
+      </c>
+      <c r="AC4">
+        <v>-0.2856038178098859</v>
+      </c>
+      <c r="AD4">
+        <v>710.5</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>710.5</v>
+      </c>
+      <c r="AG4">
+        <v>675.1</v>
+      </c>
+      <c r="AH4">
+        <v>0.8222427959726883</v>
+      </c>
+      <c r="AI4">
+        <v>0.5613494508967369</v>
+      </c>
+      <c r="AJ4">
+        <v>0.8146494509472668</v>
+      </c>
+      <c r="AK4">
+        <v>0.5487279525319028</v>
+      </c>
+      <c r="AL4">
+        <v>84.2</v>
+      </c>
+      <c r="AM4">
+        <v>83.02</v>
+      </c>
+      <c r="AN4">
+        <v>-2.98780487804878</v>
+      </c>
+      <c r="AO4">
+        <v>-3.705463182897862</v>
+      </c>
+      <c r="AP4">
+        <v>-2.838940285954584</v>
+      </c>
+      <c r="AQ4">
+        <v>-3.75813057094676</v>
       </c>
     </row>
   </sheetData>
@@ -1127,49 +1258,49 @@
         <v>469.607843137255</v>
       </c>
       <c r="F2">
-        <v>10.5339564439066</v>
+        <v>4.60979649082351</v>
       </c>
       <c r="G2">
         <v>0.0351456310679612</v>
       </c>
       <c r="H2">
-        <v>0.836128155339806</v>
+        <v>1.82427961165049</v>
       </c>
       <c r="I2">
         <v>0.00462371634394319</v>
       </c>
       <c r="J2">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="K2">
         <v>779.3</v>
       </c>
       <c r="L2">
-        <v>712.608737199526</v>
+        <v>617.220674994854</v>
       </c>
       <c r="M2">
         <v>667.8200000000001</v>
       </c>
       <c r="N2">
-        <v>683.629937199526</v>
+        <v>690.021474994854</v>
       </c>
       <c r="O2">
         <v>3.62</v>
       </c>
       <c r="P2">
-        <v>86.1212</v>
+        <v>187.9008</v>
       </c>
       <c r="Q2">
-        <v>0.088557366025693</v>
+        <v>0.08853004177598291</v>
       </c>
       <c r="R2">
-        <v>0.0875685397106072</v>
+        <v>0.0871552005740831</v>
       </c>
       <c r="S2">
         <v>0.1012844</v>
       </c>
       <c r="T2">
-        <v>0.0450912</v>
+        <v>0.0472262</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1178,20 +1309,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.08849824647868031</v>
+        <v>0.08847079530251831</v>
       </c>
       <c r="X2">
-        <v>0.09281854798944621</v>
+        <v>0.09976435865010939</v>
       </c>
       <c r="Y2">
         <v>0.985468713684025</v>
       </c>
       <c r="Z2">
-        <v>1.08518058299153</v>
+        <v>1.24629003810876</v>
       </c>
       <c r="AA2">
         <v>3.62</v>
@@ -1224,7 +1355,7 @@
         <v>779.3</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1543,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08832953199443783</v>
+        <v>0.08830218928668868</v>
       </c>
       <c r="C2">
-        <v>786.4975640035902</v>
+        <v>786.5001555626711</v>
       </c>
       <c r="D2">
-        <v>671.3975640035902</v>
+        <v>671.4001555626711</v>
       </c>
       <c r="E2">
         <v>-3.62</v>
@@ -1463,19 +1594,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08832953199443783</v>
+        <v>0.08830218928668868</v>
       </c>
       <c r="T2">
         <v>0.9815748103161358</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.146</v>
       </c>
       <c r="W2">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1625,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08825095687772594</v>
+        <v>0.0882116980903301</v>
       </c>
       <c r="C3">
-        <v>779.9110955185384</v>
+        <v>780.1034802209106</v>
       </c>
       <c r="D3">
-        <v>672.6402955185384</v>
+        <v>672.8326802209106</v>
       </c>
       <c r="E3">
         <v>4.2092</v>
@@ -1527,37 +1658,37 @@
         <v>47.9</v>
       </c>
       <c r="M3">
-        <v>0.4047696400000001</v>
+        <v>0.39380876</v>
       </c>
       <c r="N3">
-        <v>47.49523036</v>
+        <v>47.50619124</v>
       </c>
       <c r="O3">
-        <v>6.93430363256</v>
+        <v>6.93590392104</v>
       </c>
       <c r="P3">
-        <v>40.56092672744</v>
+        <v>40.57028731896</v>
       </c>
       <c r="Q3">
-        <v>95.66092672744</v>
+        <v>95.67028731895999</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08869640290679388</v>
+        <v>0.08866882433366677</v>
       </c>
       <c r="T3">
         <v>0.9900421324172466</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.146</v>
       </c>
       <c r="W3">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>118.3389149443125</v>
+        <v>121.6326421992238</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1707,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08817238176101408</v>
+        <v>0.08812120689397154</v>
       </c>
       <c r="C4">
-        <v>773.3292360627534</v>
+        <v>773.7129309270415</v>
       </c>
       <c r="D4">
-        <v>673.8876360627534</v>
+        <v>674.2713309270415</v>
       </c>
       <c r="E4">
         <v>12.0384</v>
@@ -1609,37 +1740,37 @@
         <v>47.9</v>
       </c>
       <c r="M4">
-        <v>0.8095392800000002</v>
+        <v>0.7876175200000001</v>
       </c>
       <c r="N4">
-        <v>47.09046072</v>
+        <v>47.11238248</v>
       </c>
       <c r="O4">
-        <v>6.875207265119999</v>
+        <v>6.87840784208</v>
       </c>
       <c r="P4">
-        <v>40.21525345488</v>
+        <v>40.23397463792</v>
       </c>
       <c r="Q4">
-        <v>95.31525345488001</v>
+        <v>95.33397463791999</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08907076098062661</v>
+        <v>0.08904294172854239</v>
       </c>
       <c r="T4">
         <v>0.998682257010217</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.146</v>
       </c>
       <c r="W4">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.16945747215624</v>
+        <v>60.8163210996119</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1789,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08809380664430218</v>
+        <v>0.08803071569761296</v>
       </c>
       <c r="C5">
-        <v>766.7520113247501</v>
+        <v>767.3285470614109</v>
       </c>
       <c r="D5">
-        <v>675.1396113247501</v>
+        <v>675.7161470614109</v>
       </c>
       <c r="E5">
         <v>19.8676</v>
@@ -1691,37 +1822,37 @@
         <v>47.9</v>
       </c>
       <c r="M5">
-        <v>1.21430892</v>
+        <v>1.18142628</v>
       </c>
       <c r="N5">
-        <v>46.68569108</v>
+        <v>46.71857372</v>
       </c>
       <c r="O5">
-        <v>6.816110897679999</v>
+        <v>6.82091176312</v>
       </c>
       <c r="P5">
-        <v>39.86958018232</v>
+        <v>39.89766195688</v>
       </c>
       <c r="Q5">
-        <v>94.96958018232</v>
+        <v>94.99766195687999</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08945283777763111</v>
+        <v>0.08942477288413708</v>
       </c>
       <c r="T5">
         <v>1.007500528502011</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.146</v>
       </c>
       <c r="W5">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.4463049814375</v>
+        <v>40.54421406640794</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1871,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08801523152759029</v>
+        <v>0.08794022450125441</v>
       </c>
       <c r="C6">
-        <v>760.1794471842975</v>
+        <v>760.9503683426231</v>
       </c>
       <c r="D6">
-        <v>676.3962471842974</v>
+        <v>677.1671683426231</v>
       </c>
       <c r="E6">
         <v>27.6968</v>
@@ -1773,37 +1904,37 @@
         <v>47.9</v>
       </c>
       <c r="M6">
-        <v>1.61907856</v>
+        <v>1.57523504</v>
       </c>
       <c r="N6">
-        <v>46.28092144</v>
+        <v>46.32476496</v>
       </c>
       <c r="O6">
-        <v>6.757014530239999</v>
+        <v>6.763415684159999</v>
       </c>
       <c r="P6">
-        <v>39.52390690976</v>
+        <v>39.56134927583999</v>
       </c>
       <c r="Q6">
-        <v>94.62390690976</v>
+        <v>94.66134927584</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08984287450790657</v>
+        <v>0.08981455885547335</v>
       </c>
       <c r="T6">
         <v>1.016502513983218</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.146</v>
       </c>
       <c r="W6">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.58472873607812</v>
+        <v>30.40816054980595</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1953,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08793665641087842</v>
+        <v>0.08784973330489584</v>
       </c>
       <c r="C7">
-        <v>753.6115697142042</v>
+        <v>754.578434831182</v>
       </c>
       <c r="D7">
-        <v>677.6575697142041</v>
+        <v>678.6244348311819</v>
       </c>
       <c r="E7">
         <v>35.526</v>
@@ -1855,37 +1986,37 @@
         <v>47.9</v>
       </c>
       <c r="M7">
-        <v>2.0238482</v>
+        <v>1.9690438</v>
       </c>
       <c r="N7">
-        <v>45.8761518</v>
+        <v>45.9309562</v>
       </c>
       <c r="O7">
-        <v>6.697918162799999</v>
+        <v>6.705919605199999</v>
       </c>
       <c r="P7">
-        <v>39.17823363719999</v>
+        <v>39.2250365948</v>
       </c>
       <c r="Q7">
-        <v>94.2782336372</v>
+        <v>94.3250365948</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09024112253776677</v>
+        <v>0.09021255084725879</v>
       </c>
       <c r="T7">
         <v>1.02569401494824</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.146</v>
       </c>
       <c r="W7">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.6677829888625</v>
+        <v>24.32652843984476</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +2035,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08785808129416654</v>
+        <v>0.08775924210853728</v>
       </c>
       <c r="C8">
-        <v>747.0484051821218</v>
+        <v>748.2127869331762</v>
       </c>
       <c r="D8">
-        <v>678.9236051821217</v>
+        <v>680.0879869331761</v>
       </c>
       <c r="E8">
         <v>43.3552</v>
@@ -1937,37 +2068,37 @@
         <v>47.9</v>
       </c>
       <c r="M8">
-        <v>2.42861784</v>
+        <v>2.36285256</v>
       </c>
       <c r="N8">
-        <v>45.47138216</v>
+        <v>45.53714744</v>
       </c>
       <c r="O8">
-        <v>6.638821795359999</v>
+        <v>6.648423526239999</v>
       </c>
       <c r="P8">
-        <v>38.83256036464</v>
+        <v>38.88872391376</v>
       </c>
       <c r="Q8">
-        <v>93.93256036464</v>
+        <v>93.98872391376</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09064784392996442</v>
+        <v>0.09061901075376308</v>
       </c>
       <c r="T8">
         <v>1.035081079763581</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.146</v>
       </c>
       <c r="W8">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.72315249071875</v>
+        <v>20.27210703320397</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +2117,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08777950617745467</v>
+        <v>0.08766875091217873</v>
       </c>
       <c r="C9">
-        <v>740.4899800523674</v>
+        <v>741.8534654040135</v>
       </c>
       <c r="D9">
-        <v>680.1943800523674</v>
+        <v>681.5578654040135</v>
       </c>
       <c r="E9">
         <v>51.1844</v>
@@ -2019,37 +2150,37 @@
         <v>47.9</v>
       </c>
       <c r="M9">
-        <v>2.833387480000001</v>
+        <v>2.75666132</v>
       </c>
       <c r="N9">
-        <v>45.06661252</v>
+        <v>45.14333868</v>
       </c>
       <c r="O9">
-        <v>6.57972542792</v>
+        <v>6.590927447279999</v>
       </c>
       <c r="P9">
-        <v>38.48688709208</v>
+        <v>38.55241123272</v>
       </c>
       <c r="Q9">
-        <v>93.58688709207999</v>
+        <v>93.65241123272</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09106331201876847</v>
+        <v>0.09103421173352551</v>
       </c>
       <c r="T9">
         <v>1.044670016940543</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.146</v>
       </c>
       <c r="W9">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.90555927775893</v>
+        <v>17.37609174274626</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2199,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08770093106074281</v>
+        <v>0.08757825971582014</v>
       </c>
       <c r="C10">
-        <v>733.9363209877678</v>
+        <v>735.5005113522059</v>
       </c>
       <c r="D10">
-        <v>681.4699209877678</v>
+        <v>683.0341113522059</v>
       </c>
       <c r="E10">
         <v>59.0136</v>
@@ -2101,37 +2232,37 @@
         <v>47.9</v>
       </c>
       <c r="M10">
-        <v>3.238157120000001</v>
+        <v>3.15047008</v>
       </c>
       <c r="N10">
-        <v>44.66184287999999</v>
+        <v>44.74952992</v>
       </c>
       <c r="O10">
-        <v>6.520629060479999</v>
+        <v>6.53343136832</v>
       </c>
       <c r="P10">
-        <v>38.14121381952</v>
+        <v>38.21609855168</v>
       </c>
       <c r="Q10">
-        <v>93.24121381952</v>
+        <v>93.31609855168</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09148781202254652</v>
+        <v>0.09145843882154364</v>
       </c>
       <c r="T10">
         <v>1.054467409273525</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.146</v>
       </c>
       <c r="W10">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.79236436803906</v>
+        <v>15.20408027490297</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2281,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08762235594403091</v>
+        <v>0.08748776851946159</v>
       </c>
       <c r="C11">
-        <v>727.3874548515253</v>
+        <v>729.153966243199</v>
       </c>
       <c r="D11">
-        <v>682.7502548515253</v>
+        <v>684.516766243199</v>
       </c>
       <c r="E11">
         <v>66.84279999999998</v>
@@ -2183,37 +2314,37 @@
         <v>47.9</v>
       </c>
       <c r="M11">
-        <v>3.64292676</v>
+        <v>3.54427884</v>
       </c>
       <c r="N11">
-        <v>44.25707324</v>
+        <v>44.35572116</v>
       </c>
       <c r="O11">
-        <v>6.461532693039999</v>
+        <v>6.47593528936</v>
       </c>
       <c r="P11">
-        <v>37.79554054696</v>
+        <v>37.87978587064</v>
       </c>
       <c r="Q11">
-        <v>92.89554054696001</v>
+        <v>92.97978587064</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09192164169673725</v>
+        <v>0.09189198958182591</v>
       </c>
       <c r="T11">
         <v>1.064480128910529</v>
       </c>
       <c r="U11">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.146</v>
       </c>
       <c r="W11">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.14876832714583</v>
+        <v>13.51473802213598</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2363,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08763772082731904</v>
+        <v>0.08752537732310303</v>
       </c>
       <c r="C12">
-        <v>719.3075151416823</v>
+        <v>720.7077830472995</v>
       </c>
       <c r="D12">
-        <v>682.4995151416823</v>
+        <v>683.8997830472995</v>
       </c>
       <c r="E12">
         <v>74.672</v>
@@ -2265,37 +2396,37 @@
         <v>47.9</v>
       </c>
       <c r="M12">
-        <v>4.1338176</v>
+        <v>4.0555256</v>
       </c>
       <c r="N12">
-        <v>43.7661824</v>
+        <v>43.8444744</v>
       </c>
       <c r="O12">
-        <v>6.3898626304</v>
+        <v>6.401293262399999</v>
       </c>
       <c r="P12">
-        <v>37.3763197696</v>
+        <v>37.44318113759999</v>
       </c>
       <c r="Q12">
-        <v>92.4763197696</v>
+        <v>92.54318113759999</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09236511203035448</v>
+        <v>0.0923351748034478</v>
       </c>
       <c r="T12">
         <v>1.074715353428356</v>
       </c>
       <c r="U12">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V12">
         <v>0.146</v>
       </c>
       <c r="W12">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2434,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.58735208829727</v>
+        <v>11.8110461440559</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2445,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08756853971060717</v>
+        <v>0.08744769612674447</v>
       </c>
       <c r="C13">
-        <v>712.6087371995263</v>
+        <v>714.1541915029221</v>
       </c>
       <c r="D13">
-        <v>683.6299371995264</v>
+        <v>685.1753915029221</v>
       </c>
       <c r="E13">
         <v>82.5012</v>
@@ -2347,37 +2478,37 @@
         <v>47.9</v>
       </c>
       <c r="M13">
-        <v>4.54719936</v>
+        <v>4.46107816</v>
       </c>
       <c r="N13">
-        <v>43.35280064</v>
+        <v>43.43892184</v>
       </c>
       <c r="O13">
-        <v>6.329508893439999</v>
+        <v>6.342082588639999</v>
       </c>
       <c r="P13">
-        <v>37.02329174656</v>
+        <v>37.09683925136</v>
       </c>
       <c r="Q13">
-        <v>92.12329174656</v>
+        <v>92.19683925136</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09281854798944625</v>
+        <v>0.0927883192435331</v>
       </c>
       <c r="T13">
         <v>1.085180582991527</v>
       </c>
       <c r="U13">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V13">
         <v>0.146</v>
       </c>
       <c r="W13">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.53395644390661</v>
+        <v>10.73731467641445</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2527,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08772481459389528</v>
+        <v>0.08737001493038589</v>
       </c>
       <c r="C14">
-        <v>702.2313043764846</v>
+        <v>707.6053673752075</v>
       </c>
       <c r="D14">
-        <v>681.0817043764845</v>
+        <v>686.4557673752074</v>
       </c>
       <c r="E14">
         <v>90.33039999999998</v>
@@ -2429,45 +2560,45 @@
         <v>47.9</v>
       </c>
       <c r="M14">
-        <v>5.167272</v>
+        <v>4.86663072</v>
       </c>
       <c r="N14">
-        <v>42.732728</v>
+        <v>43.03336928</v>
       </c>
       <c r="O14">
-        <v>6.238978288</v>
+        <v>6.28287191488</v>
       </c>
       <c r="P14">
-        <v>36.493749712</v>
+        <v>36.75049736512</v>
       </c>
       <c r="Q14">
-        <v>91.593749712</v>
+        <v>91.85049736512001</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09328228931124463</v>
+        <v>0.09325176242089306</v>
       </c>
       <c r="T14">
         <v>1.095883658681133</v>
       </c>
       <c r="U14">
-        <v>0.05500000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V14">
         <v>0.146</v>
       </c>
       <c r="W14">
-        <v>0.04697</v>
+        <v>0.0442372</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>9.269881670637815</v>
+        <v>9.84253845337992</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2609,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08767442147718341</v>
+        <v>0.08748106773402733</v>
       </c>
       <c r="C15">
-        <v>695.2217414868782</v>
+        <v>697.9472114082129</v>
       </c>
       <c r="D15">
-        <v>681.9013414868781</v>
+        <v>684.6268114082128</v>
       </c>
       <c r="E15">
         <v>98.1596</v>
@@ -2511,37 +2642,37 @@
         <v>47.9</v>
       </c>
       <c r="M15">
-        <v>5.597878000000001</v>
+        <v>5.445208600000001</v>
       </c>
       <c r="N15">
-        <v>42.302122</v>
+        <v>42.4547914</v>
       </c>
       <c r="O15">
-        <v>6.176109811999999</v>
+        <v>6.198399544399999</v>
       </c>
       <c r="P15">
-        <v>36.126012188</v>
+        <v>36.2563918556</v>
       </c>
       <c r="Q15">
-        <v>91.226012188</v>
+        <v>91.35639185560001</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09375669135308437</v>
+        <v>0.09372585946439922</v>
       </c>
       <c r="T15">
         <v>1.106832782087742</v>
       </c>
       <c r="U15">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V15">
         <v>0.146</v>
       </c>
       <c r="W15">
-        <v>0.04697</v>
+        <v>0.04568900000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.55681384981952</v>
+        <v>8.796724518506048</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2691,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08762402836047152</v>
+        <v>0.08741790453766876</v>
       </c>
       <c r="C16">
-        <v>688.2141537331059</v>
+        <v>691.1570646282562</v>
       </c>
       <c r="D16">
-        <v>682.7229537331059</v>
+        <v>685.6658646282561</v>
       </c>
       <c r="E16">
         <v>105.9888</v>
@@ -2593,37 +2724,37 @@
         <v>47.9</v>
       </c>
       <c r="M16">
-        <v>6.028484000000001</v>
+        <v>5.8640708</v>
       </c>
       <c r="N16">
-        <v>41.871516</v>
+        <v>42.0359292</v>
       </c>
       <c r="O16">
-        <v>6.113241336</v>
+        <v>6.137245663199999</v>
       </c>
       <c r="P16">
-        <v>35.758274664</v>
+        <v>35.8986835368</v>
       </c>
       <c r="Q16">
-        <v>90.85827466399999</v>
+        <v>90.9986835368</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09424212600054827</v>
+        <v>0.09421098202054506</v>
       </c>
       <c r="T16">
         <v>1.118036536271249</v>
       </c>
       <c r="U16">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V16">
         <v>0.146</v>
       </c>
       <c r="W16">
-        <v>0.04697</v>
+        <v>0.04568900000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.945612860546698</v>
+        <v>8.168387052898474</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2773,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08776578524375964</v>
+        <v>0.08735474134131019</v>
       </c>
       <c r="C17">
-        <v>678.0787731741503</v>
+        <v>684.3700765695644</v>
       </c>
       <c r="D17">
-        <v>680.4167731741503</v>
+        <v>686.7080765695644</v>
       </c>
       <c r="E17">
         <v>113.818</v>
@@ -2675,45 +2806,45 @@
         <v>47.9</v>
       </c>
       <c r="M17">
-        <v>6.635247000000001</v>
+        <v>6.282933</v>
       </c>
       <c r="N17">
-        <v>41.264753</v>
+        <v>41.617067</v>
       </c>
       <c r="O17">
-        <v>6.024653937999999</v>
+        <v>6.076091782</v>
       </c>
       <c r="P17">
-        <v>35.240099062</v>
+        <v>35.540975218</v>
       </c>
       <c r="Q17">
-        <v>90.34009906200001</v>
+        <v>90.64097521799999</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09473898263971722</v>
+        <v>0.09470751922507083</v>
       </c>
       <c r="T17">
         <v>1.12950390820025</v>
       </c>
       <c r="U17">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V17">
         <v>0.146</v>
       </c>
       <c r="W17">
-        <v>0.04825100000000001</v>
+        <v>0.04568900000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.219022893948032</v>
+        <v>7.623827916038576</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2855,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08772820212704775</v>
+        <v>0.08740089014495163</v>
       </c>
       <c r="C18">
-        <v>670.8594772888424</v>
+        <v>675.779095846263</v>
       </c>
       <c r="D18">
-        <v>681.0266772888424</v>
+        <v>685.946295846263</v>
       </c>
       <c r="E18">
         <v>121.6472</v>
@@ -2757,37 +2888,37 @@
         <v>47.9</v>
       </c>
       <c r="M18">
-        <v>7.077596800000001</v>
+        <v>6.802008960000001</v>
       </c>
       <c r="N18">
-        <v>40.8224032</v>
+        <v>41.09799104</v>
       </c>
       <c r="O18">
-        <v>5.960070867199999</v>
+        <v>6.000306691839999</v>
       </c>
       <c r="P18">
-        <v>34.86233233279999</v>
+        <v>35.09768434816</v>
       </c>
       <c r="Q18">
-        <v>89.9623323328</v>
+        <v>90.19768434816001</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09524766919886637</v>
+        <v>0.09521587874399004</v>
       </c>
       <c r="T18">
         <v>1.141244312794227</v>
       </c>
       <c r="U18">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V18">
         <v>0.146</v>
       </c>
       <c r="W18">
-        <v>0.04825100000000001</v>
+        <v>0.04637220000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.767833963076279</v>
+        <v>7.042037180733145</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2937,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08769061901033587</v>
+        <v>0.08734455894859305</v>
       </c>
       <c r="C19">
-        <v>663.6412757820884</v>
+        <v>668.8799857656328</v>
       </c>
       <c r="D19">
-        <v>681.6376757820884</v>
+        <v>686.8763857656328</v>
       </c>
       <c r="E19">
         <v>129.4764</v>
@@ -2839,37 +2970,37 @@
         <v>47.9</v>
       </c>
       <c r="M19">
-        <v>7.519946600000001</v>
+        <v>7.227134520000001</v>
       </c>
       <c r="N19">
-        <v>40.38005339999999</v>
+        <v>40.67286548</v>
       </c>
       <c r="O19">
-        <v>5.895487796399999</v>
+        <v>5.93823836008</v>
       </c>
       <c r="P19">
-        <v>34.4845656036</v>
+        <v>34.73462711992</v>
       </c>
       <c r="Q19">
-        <v>89.5845656036</v>
+        <v>89.83462711992</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09576861326546492</v>
+        <v>0.09573648788987116</v>
       </c>
       <c r="T19">
         <v>1.153267618703722</v>
       </c>
       <c r="U19">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V19">
         <v>0.146</v>
       </c>
       <c r="W19">
-        <v>0.04825100000000001</v>
+        <v>0.04637220000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.369726082895322</v>
+        <v>6.627799699513549</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +3019,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08786824389362401</v>
+        <v>0.08728822775223449</v>
       </c>
       <c r="C20">
-        <v>652.9339948022464</v>
+        <v>661.9834013690684</v>
       </c>
       <c r="D20">
-        <v>678.7595948022463</v>
+        <v>687.8090013690684</v>
       </c>
       <c r="E20">
         <v>137.3056</v>
@@ -2921,45 +3052,45 @@
         <v>47.9</v>
       </c>
       <c r="M20">
-        <v>8.15959224</v>
+        <v>7.65226008</v>
       </c>
       <c r="N20">
-        <v>39.74040776</v>
+        <v>40.24773992</v>
       </c>
       <c r="O20">
-        <v>5.802099532959999</v>
+        <v>5.87617002832</v>
       </c>
       <c r="P20">
-        <v>33.93830822704</v>
+        <v>34.37156989168</v>
       </c>
       <c r="Q20">
-        <v>89.03830822704001</v>
+        <v>89.47156989168001</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09630226328490732</v>
+        <v>0.09626979481979817</v>
       </c>
       <c r="T20">
         <v>1.165584175976863</v>
       </c>
       <c r="U20">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V20">
         <v>0.146</v>
       </c>
       <c r="W20">
-        <v>0.04944660000000001</v>
+        <v>0.04637220000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>5.870391386126422</v>
+        <v>6.25958860509613</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +3101,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08784261677691213</v>
+        <v>0.08739415655587596</v>
       </c>
       <c r="C21">
-        <v>645.5185333534789</v>
+        <v>652.4025422255304</v>
       </c>
       <c r="D21">
-        <v>679.1733333534789</v>
+        <v>686.0573422255303</v>
       </c>
       <c r="E21">
         <v>145.1348</v>
@@ -3003,37 +3134,37 @@
         <v>47.9</v>
       </c>
       <c r="M21">
-        <v>8.61290292</v>
+        <v>8.22614044</v>
       </c>
       <c r="N21">
-        <v>39.28709708</v>
+        <v>39.67385956</v>
       </c>
       <c r="O21">
-        <v>5.735916173679999</v>
+        <v>5.792383495759999</v>
       </c>
       <c r="P21">
-        <v>33.55118090632</v>
+        <v>33.88147606424</v>
       </c>
       <c r="Q21">
-        <v>88.65118090632001</v>
+        <v>88.98147606424</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09684908984803967</v>
+        <v>0.09681626982206906</v>
       </c>
       <c r="T21">
         <v>1.178204845775267</v>
       </c>
       <c r="U21">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V21">
         <v>0.146</v>
       </c>
       <c r="W21">
-        <v>0.04944660000000001</v>
+        <v>0.04722620000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.561423418435558</v>
+        <v>5.822900830513902</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3183,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08781698966020025</v>
+        <v>0.08734636535951738</v>
       </c>
       <c r="C22">
-        <v>638.1035766017983</v>
+        <v>645.3625207943851</v>
       </c>
       <c r="D22">
-        <v>679.5875766017983</v>
+        <v>686.846520794385</v>
       </c>
       <c r="E22">
         <v>152.964</v>
@@ -3085,37 +3216,37 @@
         <v>47.9</v>
       </c>
       <c r="M22">
-        <v>9.066213600000001</v>
+        <v>8.659095200000001</v>
       </c>
       <c r="N22">
-        <v>38.83378639999999</v>
+        <v>39.2409048</v>
       </c>
       <c r="O22">
-        <v>5.669732814399999</v>
+        <v>5.729172100799999</v>
       </c>
       <c r="P22">
-        <v>33.16405358559999</v>
+        <v>33.5117326992</v>
       </c>
       <c r="Q22">
-        <v>88.2640535856</v>
+        <v>88.61173269919999</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.0974095870752503</v>
+        <v>0.09737640669939671</v>
       </c>
       <c r="T22">
         <v>1.191141032318631</v>
       </c>
       <c r="U22">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V22">
         <v>0.146</v>
       </c>
       <c r="W22">
-        <v>0.04944660000000001</v>
+        <v>0.04722620000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.283352247513779</v>
+        <v>5.531755788988207</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3265,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08779136254348838</v>
+        <v>0.08729857416315881</v>
       </c>
       <c r="C23">
-        <v>630.6891254712469</v>
+        <v>638.324317054026</v>
       </c>
       <c r="D23">
-        <v>680.0023254712469</v>
+        <v>687.6375170540259</v>
       </c>
       <c r="E23">
         <v>160.7932</v>
@@ -3167,37 +3298,37 @@
         <v>47.9</v>
       </c>
       <c r="M23">
-        <v>9.519524280000001</v>
+        <v>9.092049960000001</v>
       </c>
       <c r="N23">
-        <v>38.38047572</v>
+        <v>38.80795003999999</v>
       </c>
       <c r="O23">
-        <v>5.60354945512</v>
+        <v>5.665960705839999</v>
       </c>
       <c r="P23">
-        <v>32.77692626488</v>
+        <v>33.14198933415999</v>
       </c>
       <c r="Q23">
-        <v>87.87692626488001</v>
+        <v>88.24198933416</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09798427410568147</v>
+        <v>0.09795072425716303</v>
       </c>
       <c r="T23">
         <v>1.204404717255497</v>
       </c>
       <c r="U23">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V23">
         <v>0.146</v>
       </c>
       <c r="W23">
-        <v>0.04944660000000001</v>
+        <v>0.04722620000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.031764045251219</v>
+        <v>5.268338846655435</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3347,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.0877657354267765</v>
+        <v>0.08725078296680025</v>
       </c>
       <c r="C24">
-        <v>623.2751808881239</v>
+        <v>631.2879372916403</v>
       </c>
       <c r="D24">
-        <v>680.4175808881239</v>
+        <v>688.4303372916403</v>
       </c>
       <c r="E24">
         <v>168.6224</v>
@@ -3249,37 +3380,37 @@
         <v>47.9</v>
       </c>
       <c r="M24">
-        <v>9.972834960000002</v>
+        <v>9.525004720000002</v>
       </c>
       <c r="N24">
-        <v>37.92716504</v>
+        <v>38.37499527999999</v>
       </c>
       <c r="O24">
-        <v>5.53736609584</v>
+        <v>5.602749310879998</v>
       </c>
       <c r="P24">
-        <v>32.38979894416</v>
+        <v>32.77224596911999</v>
       </c>
       <c r="Q24">
-        <v>87.48979894416</v>
+        <v>87.87224596912</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.0985736967009955</v>
+        <v>0.09853976790615415</v>
       </c>
       <c r="T24">
         <v>1.218008496677925</v>
       </c>
       <c r="U24">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V24">
         <v>0.146</v>
       </c>
       <c r="W24">
-        <v>0.04944660000000001</v>
+        <v>0.04722620000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3418,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.803047497739799</v>
+        <v>5.028868899080187</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3429,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08774010831006461</v>
+        <v>0.08720299177044168</v>
       </c>
       <c r="C25">
-        <v>615.8617437809932</v>
+        <v>624.2533878234455</v>
       </c>
       <c r="D25">
-        <v>680.8333437809931</v>
+        <v>689.2249878234454</v>
       </c>
       <c r="E25">
         <v>176.4516</v>
@@ -3331,37 +3462,37 @@
         <v>47.9</v>
       </c>
       <c r="M25">
-        <v>10.42614564</v>
+        <v>9.957959480000001</v>
       </c>
       <c r="N25">
-        <v>37.47385436</v>
+        <v>37.94204052</v>
       </c>
       <c r="O25">
-        <v>5.471182736559999</v>
+        <v>5.53953791592</v>
       </c>
       <c r="P25">
-        <v>32.00267162343999</v>
+        <v>32.40250260408</v>
       </c>
       <c r="Q25">
-        <v>87.10267162343999</v>
+        <v>87.50250260408001</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09917842897410988</v>
+        <v>0.09914411139018399</v>
       </c>
       <c r="T25">
         <v>1.231965621020416</v>
       </c>
       <c r="U25">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V25">
         <v>0.146</v>
       </c>
       <c r="W25">
-        <v>0.04944660000000001</v>
+        <v>0.04722620000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.594219345664156</v>
+        <v>4.810222425207137</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3511,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08824737719335274</v>
+        <v>0.0871552005740831</v>
       </c>
       <c r="C26">
-        <v>599.8962208126287</v>
+        <v>617.2206749948544</v>
       </c>
       <c r="D26">
-        <v>672.6970208126287</v>
+        <v>690.0214749948544</v>
       </c>
       <c r="E26">
         <v>184.2808</v>
@@ -3413,45 +3544,45 @@
         <v>47.9</v>
       </c>
       <c r="M26">
-        <v>11.3679984</v>
+        <v>10.39091424</v>
       </c>
       <c r="N26">
-        <v>36.5320016</v>
+        <v>37.50908576</v>
       </c>
       <c r="O26">
-        <v>5.3336722336</v>
+        <v>5.476326520959999</v>
       </c>
       <c r="P26">
-        <v>31.1983293664</v>
+        <v>32.03275923904</v>
       </c>
       <c r="Q26">
-        <v>86.2983293664</v>
+        <v>87.13275923904</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09979907525441148</v>
+        <v>0.09976435865010935</v>
       </c>
       <c r="T26">
         <v>1.246290038108761</v>
       </c>
       <c r="U26">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V26">
         <v>0.146</v>
       </c>
       <c r="W26">
-        <v>0.051667</v>
+        <v>0.04722620000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.213582577562644</v>
+        <v>4.609796490823506</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3593,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08824395407664085</v>
+        <v>0.08764115937772454</v>
       </c>
       <c r="C27">
-        <v>592.1212740146236</v>
+        <v>601.3773086700579</v>
       </c>
       <c r="D27">
-        <v>672.7512740146236</v>
+        <v>682.0073086700579</v>
       </c>
       <c r="E27">
         <v>192.11</v>
@@ -3495,37 +3626,37 @@
         <v>47.9</v>
       </c>
       <c r="M27">
-        <v>11.841665</v>
+        <v>11.313194</v>
       </c>
       <c r="N27">
-        <v>36.058335</v>
+        <v>36.586806</v>
       </c>
       <c r="O27">
-        <v>5.264516909999999</v>
+        <v>5.341673675999999</v>
       </c>
       <c r="P27">
-        <v>30.79381809</v>
+        <v>31.245132324</v>
       </c>
       <c r="Q27">
-        <v>85.89381809</v>
+        <v>86.34513232399999</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1004362721021878</v>
+        <v>0.100401145836966</v>
       </c>
       <c r="T27">
         <v>1.260996439652796</v>
       </c>
       <c r="U27">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0.146</v>
       </c>
       <c r="W27">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.045039274460137</v>
+        <v>4.233994396277478</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3675,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08884003895992897</v>
+        <v>0.08761471818136597</v>
       </c>
       <c r="C28">
-        <v>574.9747761137947</v>
+        <v>593.9793704350735</v>
       </c>
       <c r="D28">
-        <v>663.4339761137948</v>
+        <v>682.4385704350735</v>
       </c>
       <c r="E28">
         <v>199.9392</v>
@@ -3577,45 +3708,45 @@
         <v>47.9</v>
       </c>
       <c r="M28">
-        <v>12.86494144</v>
+        <v>11.76572176</v>
       </c>
       <c r="N28">
-        <v>35.03505856</v>
+        <v>36.13427824</v>
       </c>
       <c r="O28">
-        <v>5.115118549759999</v>
+        <v>5.27560462304</v>
       </c>
       <c r="P28">
-        <v>29.91994001024</v>
+        <v>30.85867361696</v>
       </c>
       <c r="Q28">
-        <v>85.01994001023999</v>
+        <v>85.95867361696</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1010906904863905</v>
+        <v>0.1010551434883324</v>
       </c>
       <c r="T28">
         <v>1.276100311508831</v>
       </c>
       <c r="U28">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.146</v>
       </c>
       <c r="W28">
-        <v>0.0539728</v>
+        <v>0.0493612</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.723297165665139</v>
+        <v>4.071148457959114</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3757,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08885967384321709</v>
+        <v>0.08839530698500742</v>
       </c>
       <c r="C29">
-        <v>566.8430552740456</v>
+        <v>573.644006142322</v>
       </c>
       <c r="D29">
-        <v>663.1314552740456</v>
+        <v>669.932406142322</v>
       </c>
       <c r="E29">
         <v>207.7684</v>
@@ -3659,37 +3790,37 @@
         <v>47.9</v>
       </c>
       <c r="M29">
-        <v>13.35974688</v>
+        <v>12.95810892</v>
       </c>
       <c r="N29">
-        <v>34.54025312</v>
+        <v>34.94189108</v>
       </c>
       <c r="O29">
-        <v>5.042876955519999</v>
+        <v>5.101516097679999</v>
       </c>
       <c r="P29">
-        <v>29.49737616447999</v>
+        <v>29.84037498232</v>
       </c>
       <c r="Q29">
-        <v>84.59737616448</v>
+        <v>84.94037498232001</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1017630381413933</v>
+        <v>0.1017270588835718</v>
       </c>
       <c r="T29">
         <v>1.291617988073252</v>
       </c>
       <c r="U29">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V29">
         <v>0.146</v>
       </c>
       <c r="W29">
-        <v>0.0539728</v>
+        <v>0.05235020000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.585397270640504</v>
+        <v>3.696527039224794</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3839,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09000317272650522</v>
+        <v>0.08839875578864885</v>
       </c>
       <c r="C30">
-        <v>541.8592025238729</v>
+        <v>565.7605682830456</v>
       </c>
       <c r="D30">
-        <v>645.9768025238728</v>
+        <v>669.8781682830455</v>
       </c>
       <c r="E30">
         <v>215.5976</v>
@@ -3741,45 +3872,45 @@
         <v>47.9</v>
       </c>
       <c r="M30">
-        <v>14.88487504</v>
+        <v>13.43803888</v>
       </c>
       <c r="N30">
-        <v>33.01512495999999</v>
+        <v>34.46196112</v>
       </c>
       <c r="O30">
-        <v>4.820208244159999</v>
+        <v>5.031446323519999</v>
       </c>
       <c r="P30">
-        <v>28.19491671583999</v>
+        <v>29.43051479648</v>
       </c>
       <c r="Q30">
-        <v>83.29491671584</v>
+        <v>84.53051479647999</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1024540621201461</v>
+        <v>0.1024176385953456</v>
       </c>
       <c r="T30">
         <v>1.307566711208906</v>
       </c>
       <c r="U30">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.05798660000000001</v>
+        <v>0.05235020000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.218031718189015</v>
+        <v>3.564508216395337</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3921,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09006294560979335</v>
+        <v>0.08909565259229027</v>
       </c>
       <c r="C31">
-        <v>533.1576725085033</v>
+        <v>547.1488548814863</v>
       </c>
       <c r="D31">
-        <v>645.1044725085032</v>
+        <v>659.0956548814862</v>
       </c>
       <c r="E31">
         <v>223.4268</v>
@@ -3823,37 +3954,37 @@
         <v>47.9</v>
       </c>
       <c r="M31">
-        <v>15.41647772</v>
+        <v>14.55369988</v>
       </c>
       <c r="N31">
-        <v>32.48352228</v>
+        <v>33.34630012</v>
       </c>
       <c r="O31">
-        <v>4.742594252879999</v>
+        <v>4.86855981752</v>
       </c>
       <c r="P31">
-        <v>27.74092802712</v>
+        <v>28.47774030248</v>
       </c>
       <c r="Q31">
-        <v>82.84092802712</v>
+        <v>83.57774030248001</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1031645515630892</v>
+        <v>0.1031276712567469</v>
       </c>
       <c r="T31">
         <v>1.323964694151198</v>
       </c>
       <c r="U31">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V31">
         <v>0.146</v>
       </c>
       <c r="W31">
-        <v>0.05798660000000001</v>
+        <v>0.0547414</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.107065107216981</v>
+        <v>3.291259294540297</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +4003,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09012271849308144</v>
+        <v>0.08912301339593171</v>
       </c>
       <c r="C32">
-        <v>524.4584953127251</v>
+        <v>538.9034006696814</v>
       </c>
       <c r="D32">
-        <v>644.234495312725</v>
+        <v>658.6794006696814</v>
       </c>
       <c r="E32">
         <v>231.256</v>
@@ -3905,37 +4036,37 @@
         <v>47.9</v>
       </c>
       <c r="M32">
-        <v>15.9480804</v>
+        <v>15.0555516</v>
       </c>
       <c r="N32">
-        <v>31.9519196</v>
+        <v>32.8444484</v>
       </c>
       <c r="O32">
-        <v>4.664980261599999</v>
+        <v>4.795289466399999</v>
       </c>
       <c r="P32">
-        <v>27.2869393384</v>
+        <v>28.0491589336</v>
       </c>
       <c r="Q32">
-        <v>82.3869393384</v>
+        <v>83.14915893360001</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1038953407044021</v>
+        <v>0.1038579905656167</v>
       </c>
       <c r="T32">
         <v>1.340831190891842</v>
       </c>
       <c r="U32">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.05798660000000001</v>
+        <v>0.0547414</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.003496270309748</v>
+        <v>3.181550651388954</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +4085,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.09264457337636957</v>
+        <v>0.08915037419957315</v>
       </c>
       <c r="C33">
-        <v>481.9472437774535</v>
+        <v>530.6584718996961</v>
       </c>
       <c r="D33">
-        <v>609.5524437774535</v>
+        <v>658.2636718996961</v>
       </c>
       <c r="E33">
         <v>239.0852</v>
@@ -3987,45 +4118,45 @@
         <v>47.9</v>
       </c>
       <c r="M33">
-        <v>18.73684144</v>
+        <v>15.55740332</v>
       </c>
       <c r="N33">
-        <v>29.16315856</v>
+        <v>32.34259668</v>
       </c>
       <c r="O33">
-        <v>4.25782114976</v>
+        <v>4.722019115279999</v>
       </c>
       <c r="P33">
-        <v>24.90533741024</v>
+        <v>27.62057756472</v>
       </c>
       <c r="Q33">
-        <v>80.00533741024</v>
+        <v>82.72057756472</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.104647312139666</v>
+        <v>0.104609478550106</v>
       </c>
       <c r="T33">
         <v>1.358186571595982</v>
       </c>
       <c r="U33">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.146</v>
       </c>
       <c r="W33">
-        <v>0.0659288</v>
+        <v>0.0547414</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.556460764926022</v>
+        <v>3.078919985215116</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4167,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.09406818425965768</v>
+        <v>0.0913093190032146</v>
       </c>
       <c r="C34">
-        <v>456.1400421971927</v>
+        <v>491.6014933918833</v>
       </c>
       <c r="D34">
-        <v>591.5744421971926</v>
+        <v>627.0358933918833</v>
       </c>
       <c r="E34">
         <v>246.9144</v>
@@ -4069,45 +4200,45 @@
         <v>47.9</v>
       </c>
       <c r="M34">
-        <v>20.51876736</v>
+        <v>18.01342336</v>
       </c>
       <c r="N34">
-        <v>27.38123264</v>
+        <v>29.88657664</v>
       </c>
       <c r="O34">
-        <v>3.997659965439999</v>
+        <v>4.363440189439999</v>
       </c>
       <c r="P34">
-        <v>23.38357267456</v>
+        <v>25.52313645056</v>
       </c>
       <c r="Q34">
-        <v>78.48357267455999</v>
+        <v>80.62313645056</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1054214003818496</v>
+        <v>0.1053830691223744</v>
       </c>
       <c r="T34">
         <v>1.376052404673774</v>
       </c>
       <c r="U34">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V34">
         <v>0.146</v>
       </c>
       <c r="W34">
-        <v>0.06994259999999999</v>
+        <v>0.0614026</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.334448222917032</v>
+        <v>2.659128087022321</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4249,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09424751714294581</v>
+        <v>0.09140329180685602</v>
       </c>
       <c r="C35">
-        <v>446.1210756899479</v>
+        <v>482.4801866480235</v>
       </c>
       <c r="D35">
-        <v>589.3846756899479</v>
+        <v>625.7437866480235</v>
       </c>
       <c r="E35">
         <v>254.7436</v>
@@ -4151,45 +4282,45 @@
         <v>47.9</v>
       </c>
       <c r="M35">
-        <v>21.15997884</v>
+        <v>18.57634284</v>
       </c>
       <c r="N35">
-        <v>26.74002116</v>
+        <v>29.32365716</v>
       </c>
       <c r="O35">
-        <v>3.90404308936</v>
+        <v>4.28125394536</v>
       </c>
       <c r="P35">
-        <v>22.83597807064</v>
+        <v>25.04240321464</v>
       </c>
       <c r="Q35">
-        <v>77.93597807064</v>
+        <v>80.14240321464</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.10621859573574</v>
+        <v>0.1061797519505314</v>
       </c>
       <c r="T35">
         <v>1.394451546201648</v>
       </c>
       <c r="U35">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V35">
         <v>0.146</v>
       </c>
       <c r="W35">
-        <v>0.06994259999999999</v>
+        <v>0.0614026</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.263707367677122</v>
+        <v>2.578548448021645</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4331,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09442685002623394</v>
+        <v>0.09149726461049744</v>
       </c>
       <c r="C36">
-        <v>436.1182606357074</v>
+        <v>473.3641941344296</v>
       </c>
       <c r="D36">
-        <v>587.2110606357073</v>
+        <v>624.4569941344296</v>
       </c>
       <c r="E36">
         <v>262.5728</v>
@@ -4233,45 +4364,45 @@
         <v>47.9</v>
       </c>
       <c r="M36">
-        <v>21.80119032</v>
+        <v>19.13926232</v>
       </c>
       <c r="N36">
-        <v>26.09880968</v>
+        <v>28.76073768</v>
       </c>
       <c r="O36">
-        <v>3.81042621328</v>
+        <v>4.19906770128</v>
       </c>
       <c r="P36">
-        <v>22.28838346672</v>
+        <v>24.56166997872</v>
       </c>
       <c r="Q36">
-        <v>77.38838346672</v>
+        <v>79.66166997872</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1070399485245969</v>
+        <v>0.1070005766825719</v>
       </c>
       <c r="T36">
         <v>1.413408237472792</v>
       </c>
       <c r="U36">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.146</v>
       </c>
       <c r="W36">
-        <v>0.06994259999999999</v>
+        <v>0.0614026</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.19712773921603</v>
+        <v>2.502708787785714</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4413,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09460618290952205</v>
+        <v>0.09275694741413888</v>
       </c>
       <c r="C37">
-        <v>426.1314189943258</v>
+        <v>448.7831015936484</v>
       </c>
       <c r="D37">
-        <v>585.0534189943257</v>
+        <v>607.7051015936484</v>
       </c>
       <c r="E37">
         <v>270.402</v>
@@ -4315,37 +4446,37 @@
         <v>47.9</v>
       </c>
       <c r="M37">
-        <v>22.4424018</v>
+        <v>20.7708676</v>
       </c>
       <c r="N37">
-        <v>25.4575982</v>
+        <v>27.1291324</v>
       </c>
       <c r="O37">
-        <v>3.7168093372</v>
+        <v>3.960853330399999</v>
       </c>
       <c r="P37">
-        <v>21.7407888628</v>
+        <v>23.1682790696</v>
       </c>
       <c r="Q37">
-        <v>76.8407888628</v>
+        <v>78.2682790696</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.107886573706957</v>
+        <v>0.1078466575602137</v>
       </c>
       <c r="T37">
         <v>1.432948211552279</v>
       </c>
       <c r="U37">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V37">
         <v>0.146</v>
       </c>
       <c r="W37">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4484,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.134352660952715</v>
+        <v>2.30611455055445</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4495,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09478551579281017</v>
+        <v>0.09288422621778034</v>
       </c>
       <c r="C38">
-        <v>416.1603753328324</v>
+        <v>439.3111438271751</v>
       </c>
       <c r="D38">
-        <v>582.9115753328323</v>
+        <v>606.062343827175</v>
       </c>
       <c r="E38">
         <v>278.2311999999999</v>
@@ -4397,37 +4528,37 @@
         <v>47.9</v>
       </c>
       <c r="M38">
-        <v>23.08361327999999</v>
+        <v>21.36432096</v>
       </c>
       <c r="N38">
-        <v>24.81638672</v>
+        <v>26.53567904</v>
       </c>
       <c r="O38">
-        <v>3.62319246112</v>
+        <v>3.87420913984</v>
       </c>
       <c r="P38">
-        <v>21.19319425888001</v>
+        <v>22.66146990016</v>
       </c>
       <c r="Q38">
-        <v>76.29319425888001</v>
+        <v>77.76146990015999</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1087596559262659</v>
+        <v>0.1087191784652818</v>
       </c>
       <c r="T38">
         <v>1.453098809821749</v>
       </c>
       <c r="U38">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.146</v>
       </c>
       <c r="W38">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.075065087037362</v>
+        <v>2.24205581303905</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4577,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.09496484867609831</v>
+        <v>0.09301150502142176</v>
       </c>
       <c r="C39">
-        <v>406.2049567778815</v>
+        <v>429.848043573001</v>
       </c>
       <c r="D39">
-        <v>580.7853567778815</v>
+        <v>604.4284435730009</v>
       </c>
       <c r="E39">
         <v>286.0604</v>
@@ -4479,37 +4610,37 @@
         <v>47.9</v>
       </c>
       <c r="M39">
-        <v>23.72482476</v>
+        <v>21.95777432</v>
       </c>
       <c r="N39">
-        <v>24.17517524</v>
+        <v>25.94222568</v>
       </c>
       <c r="O39">
-        <v>3.52957558504</v>
+        <v>3.78756494928</v>
       </c>
       <c r="P39">
-        <v>20.64559965496</v>
+        <v>22.15466073072</v>
       </c>
       <c r="Q39">
-        <v>75.74559965496</v>
+        <v>77.25466073072</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1096604550414259</v>
+        <v>0.1096193984467012</v>
       </c>
       <c r="T39">
         <v>1.473889109623584</v>
       </c>
       <c r="U39">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.146</v>
       </c>
       <c r="W39">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.018982246847163</v>
+        <v>2.18145970998394</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4659,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1004338575593864</v>
+        <v>0.09313878382506319</v>
       </c>
       <c r="C40">
-        <v>340.2374444310138</v>
+        <v>420.3937293860985</v>
       </c>
       <c r="D40">
-        <v>522.6470444310138</v>
+        <v>602.8033293860984</v>
       </c>
       <c r="E40">
         <v>293.8896</v>
@@ -4561,45 +4692,45 @@
         <v>47.9</v>
       </c>
       <c r="M40">
-        <v>29.21544272</v>
+        <v>22.55122768</v>
       </c>
       <c r="N40">
-        <v>18.68455728</v>
+        <v>25.34877232</v>
       </c>
       <c r="O40">
-        <v>2.727945362879999</v>
+        <v>3.70092075872</v>
       </c>
       <c r="P40">
-        <v>15.95661191712</v>
+        <v>21.64785156128</v>
       </c>
       <c r="Q40">
-        <v>71.05661191711999</v>
+        <v>76.74785156128</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1105903121925587</v>
+        <v>0.11054865778236</v>
       </c>
       <c r="T40">
         <v>1.495350064257736</v>
       </c>
       <c r="U40">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V40">
         <v>0.146</v>
       </c>
       <c r="W40">
-        <v>0.0838628</v>
+        <v>0.0647332</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y40">
-        <v>1.63954386928421</v>
+        <v>2.124052875510678</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4741,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1007523924426745</v>
+        <v>0.09326606262870464</v>
       </c>
       <c r="C41">
-        <v>329.3786890668432</v>
+        <v>410.9481305877505</v>
       </c>
       <c r="D41">
-        <v>519.6174890668432</v>
+        <v>601.1869305877505</v>
       </c>
       <c r="E41">
         <v>301.7188</v>
@@ -4643,45 +4774,45 @@
         <v>47.9</v>
       </c>
       <c r="M41">
-        <v>29.98427016</v>
+        <v>23.14468104</v>
       </c>
       <c r="N41">
-        <v>17.91572984</v>
+        <v>24.75531896</v>
       </c>
       <c r="O41">
-        <v>2.61569655664</v>
+        <v>3.614276568159999</v>
       </c>
       <c r="P41">
-        <v>15.30003328336</v>
+        <v>21.14104239184</v>
       </c>
       <c r="Q41">
-        <v>70.40003328336</v>
+        <v>76.24104239184</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1115506564634009</v>
+        <v>0.1115083846372207</v>
       </c>
       <c r="T41">
         <v>1.517514656748746</v>
       </c>
       <c r="U41">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0.146</v>
       </c>
       <c r="W41">
-        <v>0.0838628</v>
+        <v>0.0647332</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.597504282892307</v>
+        <v>2.069589981266814</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4823,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1010709273259627</v>
+        <v>0.09339334143234605</v>
       </c>
       <c r="C42">
-        <v>318.554853292809</v>
+        <v>401.5111772553053</v>
       </c>
       <c r="D42">
-        <v>516.6228532928089</v>
+        <v>599.5791772553052</v>
       </c>
       <c r="E42">
         <v>309.548</v>
@@ -4725,45 +4856,45 @@
         <v>47.9</v>
       </c>
       <c r="M42">
-        <v>30.7530976</v>
+        <v>23.7381344</v>
       </c>
       <c r="N42">
-        <v>17.14690239999999</v>
+        <v>24.1618656</v>
       </c>
       <c r="O42">
-        <v>2.503447750399999</v>
+        <v>3.527632377599999</v>
       </c>
       <c r="P42">
-        <v>14.6434546496</v>
+        <v>20.6342332224</v>
       </c>
       <c r="Q42">
-        <v>69.7434546496</v>
+        <v>75.73423322239999</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1125430122099378</v>
+        <v>0.1125001023872434</v>
       </c>
       <c r="T42">
         <v>1.540418068989456</v>
       </c>
       <c r="U42">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.146</v>
       </c>
       <c r="W42">
-        <v>0.0838628</v>
+        <v>0.0647332</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.557566675819999</v>
+        <v>2.017850231735144</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4905,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1013894622092508</v>
+        <v>0.09849260823598752</v>
       </c>
       <c r="C43">
-        <v>307.7653368274659</v>
+        <v>335.6583891831452</v>
       </c>
       <c r="D43">
-        <v>513.6625368274659</v>
+        <v>541.5555891831452</v>
       </c>
       <c r="E43">
         <v>317.3772</v>
@@ -4807,37 +4938,37 @@
         <v>47.9</v>
       </c>
       <c r="M43">
-        <v>31.52192504000001</v>
+        <v>28.889748</v>
       </c>
       <c r="N43">
-        <v>16.37807495999999</v>
+        <v>19.01025199999999</v>
       </c>
       <c r="O43">
-        <v>2.391198944159999</v>
+        <v>2.775496791999999</v>
       </c>
       <c r="P43">
-        <v>13.98687601583999</v>
+        <v>16.234755208</v>
       </c>
       <c r="Q43">
-        <v>69.08687601583999</v>
+        <v>71.33475520799999</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1135690071343234</v>
+        <v>0.1135254376881144</v>
       </c>
       <c r="T43">
         <v>1.564097868085783</v>
       </c>
       <c r="U43">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V43">
         <v>0.146</v>
       </c>
       <c r="W43">
-        <v>0.0838628</v>
+        <v>0.07686000000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.519577244702438</v>
+        <v>1.658027615886438</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4987,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1265509880914465</v>
+        <v>0.09874115503962894</v>
       </c>
       <c r="C44">
-        <v>139.8819564320234</v>
+        <v>325.2867076187583</v>
       </c>
       <c r="D44">
-        <v>353.6083564320234</v>
+        <v>539.0131076187582</v>
       </c>
       <c r="E44">
         <v>325.2064</v>
@@ -4889,45 +5020,45 @@
         <v>47.9</v>
       </c>
       <c r="M44">
-        <v>53.79599904000001</v>
+        <v>29.594376</v>
       </c>
       <c r="N44">
-        <v>-5.895999040000007</v>
+        <v>18.305624</v>
       </c>
       <c r="O44">
-        <v>-0.8608158598400009</v>
+        <v>2.672621104</v>
       </c>
       <c r="P44">
-        <v>-5.035183180160006</v>
+        <v>15.633002896</v>
       </c>
       <c r="Q44">
-        <v>50.06481681984</v>
+        <v>70.733002896</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1151231828780571</v>
+        <v>0.1145861293786706</v>
       </c>
       <c r="T44">
-        <v>1.599967996190012</v>
+        <v>1.588594211978535</v>
       </c>
       <c r="U44">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V44">
-        <v>0.129998515220436</v>
+        <v>0.146</v>
       </c>
       <c r="W44">
-        <v>0.1423322429099367</v>
+        <v>0.07686000000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.8904007891810684</v>
+        <v>1.618550767889142</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +5069,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1277289880914465</v>
+        <v>0.09898970184327037</v>
       </c>
       <c r="C45">
-        <v>126.9684675425771</v>
+        <v>314.9387872579215</v>
       </c>
       <c r="D45">
-        <v>348.5240675425771</v>
+        <v>536.4943872579215</v>
       </c>
       <c r="E45">
         <v>333.0356</v>
@@ -4971,45 +5102,45 @@
         <v>47.9</v>
       </c>
       <c r="M45">
-        <v>55.07685616000001</v>
+        <v>30.299004</v>
       </c>
       <c r="N45">
-        <v>-7.176856160000007</v>
+        <v>17.60099599999999</v>
       </c>
       <c r="O45">
-        <v>-1.047820999360001</v>
+        <v>2.569745415999999</v>
       </c>
       <c r="P45">
-        <v>-6.129035160640006</v>
+        <v>15.031250584</v>
       </c>
       <c r="Q45">
-        <v>48.97096483935999</v>
+        <v>70.131250584</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1163393790689002</v>
+        <v>0.1156840383215269</v>
       </c>
       <c r="T45">
-        <v>1.628037610158257</v>
+        <v>1.613950076709629</v>
       </c>
       <c r="U45">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V45">
-        <v>0.1269752939362398</v>
+        <v>0.146</v>
       </c>
       <c r="W45">
-        <v>0.1428268419120312</v>
+        <v>0.07686000000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.8696937940838342</v>
+        <v>1.580910052356836</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5151,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1289069880914465</v>
+        <v>0.0992382486469118</v>
       </c>
       <c r="C46">
-        <v>114.1991131585269</v>
+        <v>304.6142965532133</v>
       </c>
       <c r="D46">
-        <v>343.5839131585269</v>
+        <v>533.9990965532132</v>
       </c>
       <c r="E46">
         <v>340.8648</v>
@@ -5053,45 +5184,45 @@
         <v>47.9</v>
       </c>
       <c r="M46">
-        <v>56.35771328000001</v>
+        <v>31.003632</v>
       </c>
       <c r="N46">
-        <v>-8.457713280000007</v>
+        <v>16.896368</v>
       </c>
       <c r="O46">
-        <v>-1.234826138880001</v>
+        <v>2.466869727999999</v>
       </c>
       <c r="P46">
-        <v>-7.222887141120006</v>
+        <v>14.429498272</v>
       </c>
       <c r="Q46">
-        <v>47.87711285888</v>
+        <v>69.529498272</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1175990108379877</v>
+        <v>0.1168211582980568</v>
       </c>
       <c r="T46">
-        <v>1.657109710339655</v>
+        <v>1.640211508038263</v>
       </c>
       <c r="U46">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V46">
-        <v>0.1240894918013252</v>
+        <v>0.146</v>
       </c>
       <c r="W46">
-        <v>0.1432989591413032</v>
+        <v>0.07686000000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.8499280260364743</v>
+        <v>1.544980278439636</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5233,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1300849880914465</v>
+        <v>0.09948679545055325</v>
       </c>
       <c r="C47">
-        <v>101.5678498389996</v>
+        <v>294.3129100968999</v>
       </c>
       <c r="D47">
-        <v>338.7818498389996</v>
+        <v>531.5269100968999</v>
       </c>
       <c r="E47">
         <v>348.694</v>
@@ -5135,45 +5266,45 @@
         <v>47.9</v>
       </c>
       <c r="M47">
-        <v>57.6385704</v>
+        <v>31.70826</v>
       </c>
       <c r="N47">
-        <v>-9.7385704</v>
+        <v>16.19174</v>
       </c>
       <c r="O47">
-        <v>-1.4218312784</v>
+        <v>2.36399404</v>
       </c>
       <c r="P47">
-        <v>-8.316739121600001</v>
+        <v>13.82774596</v>
       </c>
       <c r="Q47">
-        <v>46.7832608784</v>
+        <v>68.92774596</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1189044473986784</v>
+        <v>0.117999628091915</v>
       </c>
       <c r="T47">
-        <v>1.687238977800376</v>
+        <v>1.667427900506119</v>
       </c>
       <c r="U47">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V47">
-        <v>0.1213319475390736</v>
+        <v>0.146</v>
       </c>
       <c r="W47">
-        <v>0.1437500933826076</v>
+        <v>0.07686000000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.8310407365689971</v>
+        <v>1.510647383363199</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5315,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1312629880914465</v>
+        <v>0.1232435663240598</v>
       </c>
       <c r="C48">
-        <v>89.068967348103</v>
+        <v>123.4312628033931</v>
       </c>
       <c r="D48">
-        <v>334.112167348103</v>
+        <v>368.4744628033931</v>
       </c>
       <c r="E48">
         <v>356.5232</v>
@@ -5217,37 +5348,37 @@
         <v>47.9</v>
       </c>
       <c r="M48">
-        <v>58.91942752000001</v>
+        <v>52.86902176</v>
       </c>
       <c r="N48">
-        <v>-11.01942752000001</v>
+        <v>-4.969021760000004</v>
       </c>
       <c r="O48">
-        <v>-1.608836417920001</v>
+        <v>-0.7254771769600006</v>
       </c>
       <c r="P48">
-        <v>-9.410591102080007</v>
+        <v>-4.243544583040004</v>
       </c>
       <c r="Q48">
-        <v>45.68940889792</v>
+        <v>50.85645541696</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1202582334616168</v>
+        <v>0.1197185635220118</v>
       </c>
       <c r="T48">
-        <v>1.718484144055938</v>
+        <v>1.707126178337455</v>
       </c>
       <c r="U48">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.1186942965056154</v>
+        <v>0.132277839974923</v>
       </c>
       <c r="W48">
-        <v>0.1441816130916813</v>
+        <v>0.1273816130916813</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8129746336001058</v>
+        <v>0.9060126025679655</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5397,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1575366789408145</v>
+        <v>0.1242535663240598</v>
       </c>
       <c r="C49">
-        <v>2.676847122362801</v>
+        <v>110.858375232911</v>
       </c>
       <c r="D49">
-        <v>255.5492471223628</v>
+        <v>363.7307752329111</v>
       </c>
       <c r="E49">
         <v>364.3524</v>
@@ -5299,45 +5430,45 @@
         <v>47.9</v>
       </c>
       <c r="M49">
-        <v>79.40844392000001</v>
+        <v>54.01834832</v>
       </c>
       <c r="N49">
-        <v>-31.50844392000001</v>
+        <v>-6.118348320000003</v>
       </c>
       <c r="O49">
-        <v>-4.600232812320002</v>
+        <v>-0.8932788547200003</v>
       </c>
       <c r="P49">
-        <v>-26.90821110768001</v>
+        <v>-5.225069465280002</v>
       </c>
       <c r="Q49">
-        <v>28.19178889231999</v>
+        <v>49.87493053472</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1227228998464925</v>
+        <v>0.1211132533997856</v>
       </c>
       <c r="T49">
-        <v>1.775368250834806</v>
+        <v>1.739336106230615</v>
       </c>
       <c r="U49">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.0880687198334411</v>
+        <v>0.1294634178477969</v>
       </c>
       <c r="W49">
-        <v>0.1967947702599434</v>
+        <v>0.1277947702599434</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.6032104098180897</v>
+        <v>0.8867357386835406</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5479,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1592366789408144</v>
+        <v>0.1252635663240598</v>
       </c>
       <c r="C50">
-        <v>-8.98209934204732</v>
+        <v>98.40607435813951</v>
       </c>
       <c r="D50">
-        <v>251.7195006579526</v>
+        <v>359.1076743581394</v>
       </c>
       <c r="E50">
         <v>372.1815999999999</v>
@@ -5381,45 +5512,45 @@
         <v>47.9</v>
       </c>
       <c r="M50">
-        <v>81.09798528</v>
+        <v>55.16767488</v>
       </c>
       <c r="N50">
-        <v>-33.19798528</v>
+        <v>-7.267674880000001</v>
       </c>
       <c r="O50">
-        <v>-4.846905850880001</v>
+        <v>-1.06108053248</v>
       </c>
       <c r="P50">
-        <v>-28.35107942912001</v>
+        <v>-6.206594347520001</v>
       </c>
       <c r="Q50">
-        <v>26.74892057088</v>
+        <v>48.89340565248</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.124202186382002</v>
+        <v>0.1225615851959353</v>
       </c>
       <c r="T50">
-        <v>1.809509947966244</v>
+        <v>1.77278487750428</v>
       </c>
       <c r="U50">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.08623395483691107</v>
+        <v>0.1267662633093012</v>
       </c>
       <c r="W50">
-        <v>0.1971907125461946</v>
+        <v>0.1281907125461946</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.5906435262802129</v>
+        <v>0.868262077460967</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5561,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1609366789408144</v>
+        <v>0.1262735663240598</v>
       </c>
       <c r="C51">
-        <v>-20.52795293198182</v>
+        <v>86.06981983490419</v>
       </c>
       <c r="D51">
-        <v>248.0028470680181</v>
+        <v>354.6006198349042</v>
       </c>
       <c r="E51">
         <v>380.0108</v>
@@ -5463,45 +5594,45 @@
         <v>47.9</v>
       </c>
       <c r="M51">
-        <v>82.78752664</v>
+        <v>56.31700144</v>
       </c>
       <c r="N51">
-        <v>-34.88752664</v>
+        <v>-8.41700144</v>
       </c>
       <c r="O51">
-        <v>-5.093578889439999</v>
+        <v>-1.22888221024</v>
       </c>
       <c r="P51">
-        <v>-29.79394775056</v>
+        <v>-7.18811922976</v>
       </c>
       <c r="Q51">
-        <v>25.30605224944</v>
+        <v>47.91188077024</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1257394841541981</v>
+        <v>0.1240667143174242</v>
       </c>
       <c r="T51">
-        <v>1.844990535181269</v>
+        <v>1.807545365298482</v>
       </c>
       <c r="U51">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.08447407820758637</v>
+        <v>0.1241791967111522</v>
       </c>
       <c r="W51">
-        <v>0.1975704939228029</v>
+        <v>0.1285704939228029</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.5785895767642902</v>
+        <v>0.8505424432270696</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5643,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1626366789408144</v>
+        <v>0.1272835663240598</v>
       </c>
       <c r="C52">
-        <v>-31.96565022784563</v>
+        <v>73.84529643179116</v>
       </c>
       <c r="D52">
-        <v>244.3943497721543</v>
+        <v>350.2052964317911</v>
       </c>
       <c r="E52">
         <v>387.84</v>
@@ -5545,45 +5676,45 @@
         <v>47.9</v>
       </c>
       <c r="M52">
-        <v>84.477068</v>
+        <v>57.466328</v>
       </c>
       <c r="N52">
-        <v>-36.577068</v>
+        <v>-9.566328000000006</v>
       </c>
       <c r="O52">
-        <v>-5.340251928000001</v>
+        <v>-1.396683888000001</v>
       </c>
       <c r="P52">
-        <v>-31.236816072</v>
+        <v>-8.169644112000006</v>
       </c>
       <c r="Q52">
-        <v>23.863183928</v>
+        <v>46.93035588799999</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1273382738372821</v>
+        <v>0.1256320486037728</v>
       </c>
       <c r="T52">
-        <v>1.881890345884894</v>
+        <v>1.843696272604451</v>
       </c>
       <c r="U52">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.08278459664343463</v>
+        <v>0.1216956127769291</v>
       </c>
       <c r="W52">
-        <v>0.1979350840443468</v>
+        <v>0.1289350840443468</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.5670177852290044</v>
+        <v>0.8335315943625281</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5725,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1643366789408144</v>
+        <v>0.1282935663240598</v>
       </c>
       <c r="C53">
-        <v>-43.29984461713599</v>
+        <v>61.72840024944122</v>
       </c>
       <c r="D53">
-        <v>240.889355382864</v>
+        <v>345.9176002494412</v>
       </c>
       <c r="E53">
         <v>395.6692</v>
@@ -5627,45 +5758,45 @@
         <v>47.9</v>
       </c>
       <c r="M53">
-        <v>86.16660936000001</v>
+        <v>58.61565456</v>
       </c>
       <c r="N53">
-        <v>-38.26660936000001</v>
+        <v>-10.71565456</v>
       </c>
       <c r="O53">
-        <v>-5.586924966560002</v>
+        <v>-1.564485565760001</v>
       </c>
       <c r="P53">
-        <v>-32.67968439344001</v>
+        <v>-9.151168994240004</v>
       </c>
       <c r="Q53">
-        <v>22.42031560655999</v>
+        <v>45.94883100576</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1290023202421246</v>
+        <v>0.1272612740854824</v>
       </c>
       <c r="T53">
-        <v>1.920296271311117</v>
+        <v>1.8813227271474</v>
       </c>
       <c r="U53">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.08116136925826925</v>
+        <v>0.119309424291107</v>
       </c>
       <c r="W53">
-        <v>0.1982853765140655</v>
+        <v>0.1292853765140655</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.5558997894402002</v>
+        <v>0.8171878376103218</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5807,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1660366789408144</v>
+        <v>0.1293035663240598</v>
       </c>
       <c r="C54">
-        <v>-54.53492631445437</v>
+        <v>49.71522593993581</v>
       </c>
       <c r="D54">
-        <v>237.4834736855456</v>
+        <v>341.7336259399358</v>
       </c>
       <c r="E54">
         <v>403.4984</v>
@@ -5709,45 +5840,45 @@
         <v>47.9</v>
       </c>
       <c r="M54">
-        <v>87.85615072000002</v>
+        <v>59.76498112000001</v>
       </c>
       <c r="N54">
-        <v>-39.95615072000002</v>
+        <v>-11.86498112000001</v>
       </c>
       <c r="O54">
-        <v>-5.833598005120002</v>
+        <v>-1.732287243520001</v>
       </c>
       <c r="P54">
-        <v>-34.12255271488002</v>
+        <v>-10.13269387648001</v>
       </c>
       <c r="Q54">
-        <v>20.97744728511999</v>
+        <v>44.96730612351999</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1307357019138355</v>
+        <v>0.1289583839622633</v>
       </c>
       <c r="T54">
-        <v>1.960302443630098</v>
+        <v>1.920516950629637</v>
       </c>
       <c r="U54">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.07960057369561022</v>
+        <v>0.1170150122855088</v>
       </c>
       <c r="W54">
-        <v>0.1986221961964873</v>
+        <v>0.1296221961964873</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.5452094088740426</v>
+        <v>0.8014726868870463</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5889,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1677366789408145</v>
+        <v>0.1596290489394947</v>
       </c>
       <c r="C55">
-        <v>-65.67504070684487</v>
+        <v>-49.15608702772664</v>
       </c>
       <c r="D55">
-        <v>234.1725592931552</v>
+        <v>250.6915129722734</v>
       </c>
       <c r="E55">
         <v>411.3276</v>
@@ -5791,37 +5922,37 @@
         <v>47.9</v>
       </c>
       <c r="M55">
-        <v>89.54569208000001</v>
+        <v>83.32147808000001</v>
       </c>
       <c r="N55">
-        <v>-41.64569208000001</v>
+        <v>-35.42147808000001</v>
       </c>
       <c r="O55">
-        <v>-6.080271043680002</v>
+        <v>-5.171535799680001</v>
       </c>
       <c r="P55">
-        <v>-35.56542103632001</v>
+        <v>-30.24994228032001</v>
       </c>
       <c r="Q55">
-        <v>19.53457896367999</v>
+        <v>24.85005771968</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1325428445077469</v>
+        <v>0.1322074615262154</v>
       </c>
       <c r="T55">
-        <v>2.002011006260526</v>
+        <v>1.995553383977262</v>
       </c>
       <c r="U55">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.07809867607871192</v>
+        <v>0.08393274052682285</v>
       </c>
       <c r="W55">
-        <v>0.198946305702214</v>
+        <v>0.183946305702214</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5349224388952871</v>
+        <v>0.5748817844302936</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5971,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1694366789408144</v>
+        <v>0.1611790489394947</v>
       </c>
       <c r="C56">
-        <v>-76.72410518564504</v>
+        <v>-60.35307215577689</v>
       </c>
       <c r="D56">
-        <v>230.9526948143549</v>
+        <v>247.3237278442231</v>
       </c>
       <c r="E56">
         <v>419.1568</v>
@@ -5873,37 +6004,37 @@
         <v>47.9</v>
       </c>
       <c r="M56">
-        <v>91.23523344</v>
+        <v>84.89358144000001</v>
       </c>
       <c r="N56">
-        <v>-43.33523344</v>
+        <v>-36.99358144000001</v>
       </c>
       <c r="O56">
-        <v>-6.32694408224</v>
+        <v>-5.40106289024</v>
       </c>
       <c r="P56">
-        <v>-37.00828935776001</v>
+        <v>-31.59251854976001</v>
       </c>
       <c r="Q56">
-        <v>18.09171064224</v>
+        <v>23.50748145023999</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1344285585187849</v>
+        <v>0.1340858846028723</v>
       </c>
       <c r="T56">
-        <v>2.045532984657494</v>
+        <v>2.038934979281116</v>
       </c>
       <c r="U56">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.07665240429947651</v>
+        <v>0.08237843051706688</v>
       </c>
       <c r="W56">
-        <v>0.199258411152173</v>
+        <v>0.184258411152173</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5250164678046336</v>
+        <v>0.5642358254593622</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +6053,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1711366789408145</v>
+        <v>0.1627290489394946</v>
       </c>
       <c r="C57">
-        <v>-87.68582460854924</v>
+        <v>-71.46077122538713</v>
       </c>
       <c r="D57">
-        <v>227.8201753914508</v>
+        <v>244.0452287746129</v>
       </c>
       <c r="E57">
         <v>426.986</v>
@@ -5955,37 +6086,37 @@
         <v>47.9</v>
       </c>
       <c r="M57">
-        <v>92.92477480000001</v>
+        <v>86.46568480000001</v>
       </c>
       <c r="N57">
-        <v>-45.02477480000001</v>
+        <v>-38.56568480000001</v>
       </c>
       <c r="O57">
-        <v>-6.573617120800001</v>
+        <v>-5.630589980800001</v>
       </c>
       <c r="P57">
-        <v>-38.45115767920001</v>
+        <v>-32.9350948192</v>
       </c>
       <c r="Q57">
-        <v>16.64884232079999</v>
+        <v>22.1649051808</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1363980820414245</v>
+        <v>0.1360477931496028</v>
       </c>
       <c r="T57">
-        <v>2.090989273205439</v>
+        <v>2.084244645487363</v>
       </c>
       <c r="U57">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.0752587242213042</v>
+        <v>0.08088064087130203</v>
       </c>
       <c r="W57">
-        <v>0.1995591673130426</v>
+        <v>0.1845591673130425</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5154707138445493</v>
+        <v>0.5539769922691921</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6135,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1728366789408144</v>
+        <v>0.1642790489394947</v>
       </c>
       <c r="C58">
-        <v>-98.56370552019291</v>
+        <v>-82.48268848625776</v>
       </c>
       <c r="D58">
-        <v>224.7714944798071</v>
+        <v>240.8525115137422</v>
       </c>
       <c r="E58">
         <v>434.8152</v>
@@ -6037,37 +6168,37 @@
         <v>47.9</v>
       </c>
       <c r="M58">
-        <v>94.61431616000002</v>
+        <v>88.03778816000001</v>
       </c>
       <c r="N58">
-        <v>-46.71431616000002</v>
+        <v>-40.13778816000001</v>
       </c>
       <c r="O58">
-        <v>-6.820290159360002</v>
+        <v>-5.86011707136</v>
       </c>
       <c r="P58">
-        <v>-39.89402600064001</v>
+        <v>-34.27767108864001</v>
       </c>
       <c r="Q58">
-        <v>15.20597399935999</v>
+        <v>20.82232891136</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1384571293605478</v>
+        <v>0.1380988793575483</v>
       </c>
       <c r="T58">
-        <v>2.13851175668738</v>
+        <v>2.131613841975712</v>
       </c>
       <c r="U58">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.07391481843163805</v>
+        <v>0.07943634371288592</v>
       </c>
       <c r="W58">
-        <v>0.1998491821824525</v>
+        <v>0.1848491821824525</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5062658796687538</v>
+        <v>0.5440845459786707</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6217,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1918515359476245</v>
+        <v>0.1658290489394947</v>
       </c>
       <c r="C59">
-        <v>-135.6565335882553</v>
+        <v>-93.42214717900549</v>
       </c>
       <c r="D59">
-        <v>195.5078664117447</v>
+        <v>237.7422528209946</v>
       </c>
       <c r="E59">
         <v>442.6444</v>
@@ -6119,45 +6250,45 @@
         <v>47.9</v>
       </c>
       <c r="M59">
-        <v>109.69178952</v>
+        <v>89.60989152000001</v>
       </c>
       <c r="N59">
-        <v>-61.79178952000002</v>
+        <v>-41.70989152000001</v>
       </c>
       <c r="O59">
-        <v>-9.021601269920001</v>
+        <v>-6.089644161920001</v>
       </c>
       <c r="P59">
-        <v>-52.77018825008001</v>
+        <v>-35.62024735808001</v>
       </c>
       <c r="Q59">
-        <v>2.32981174991999</v>
+        <v>19.47975264191999</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1411116137801188</v>
+        <v>0.1402453649240029</v>
       </c>
       <c r="T59">
-        <v>2.199776833410262</v>
+        <v>2.181186256905379</v>
       </c>
       <c r="U59">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.06375499962761479</v>
+        <v>0.07804272364774759</v>
       </c>
       <c r="W59">
-        <v>0.2301290210915323</v>
+        <v>0.1851290210915323</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.4366780796411971</v>
+        <v>0.5345392030667643</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6299,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1938515359476245</v>
+        <v>0.1673790489394947</v>
       </c>
       <c r="C60">
-        <v>-146.1268121175709</v>
+        <v>-104.2823010735035</v>
       </c>
       <c r="D60">
-        <v>192.866787882429</v>
+        <v>234.7112989264965</v>
       </c>
       <c r="E60">
         <v>450.4735999999999</v>
@@ -6201,45 +6332,45 @@
         <v>47.9</v>
       </c>
       <c r="M60">
-        <v>111.61620688</v>
+        <v>91.18199487999999</v>
       </c>
       <c r="N60">
-        <v>-63.71620687999999</v>
+        <v>-43.28199487999999</v>
       </c>
       <c r="O60">
-        <v>-9.302566204479998</v>
+        <v>-6.319171252479999</v>
       </c>
       <c r="P60">
-        <v>-54.41364067552</v>
+        <v>-36.96282362752</v>
       </c>
       <c r="Q60">
-        <v>0.6863593244800015</v>
+        <v>18.13717637248001</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1433809379177406</v>
+        <v>0.1424940640888601</v>
       </c>
       <c r="T60">
-        <v>2.252152472300982</v>
+        <v>2.233119263022174</v>
       </c>
       <c r="U60">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.0626557754961042</v>
+        <v>0.07669715944692435</v>
       </c>
       <c r="W60">
-        <v>0.2303992103830576</v>
+        <v>0.1853992103830576</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.4291491472335903</v>
+        <v>0.5253230099104408</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6381,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1958515359476245</v>
+        <v>0.1689290489394947</v>
       </c>
       <c r="C61">
-        <v>-156.5266860752137</v>
+        <v>-115.0661451357251</v>
       </c>
       <c r="D61">
-        <v>190.2961139247862</v>
+        <v>231.7566548642749</v>
       </c>
       <c r="E61">
         <v>458.3027999999999</v>
@@ -6283,45 +6414,45 @@
         <v>47.9</v>
       </c>
       <c r="M61">
-        <v>113.54062424</v>
+        <v>92.75409823999999</v>
       </c>
       <c r="N61">
-        <v>-65.64062423999999</v>
+        <v>-44.85409823999999</v>
       </c>
       <c r="O61">
-        <v>-9.583531139039998</v>
+        <v>-6.548698343039998</v>
       </c>
       <c r="P61">
-        <v>-56.05709310096</v>
+        <v>-38.30539989696</v>
       </c>
       <c r="Q61">
-        <v>-0.9570931009599946</v>
+        <v>16.79460010304</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1457609607937831</v>
+        <v>0.1448524558959055</v>
       </c>
       <c r="T61">
-        <v>2.307083020405884</v>
+        <v>2.28758558651052</v>
       </c>
       <c r="U61">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.06159381319956005</v>
+        <v>0.07539720759189174</v>
       </c>
       <c r="W61">
-        <v>0.2306602407155482</v>
+        <v>0.1856602407155482</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.421875432873699</v>
+        <v>0.5164192300814503</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6463,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1978515359476245</v>
+        <v>0.1704790489394946</v>
       </c>
       <c r="C62">
-        <v>-166.8589336470625</v>
+        <v>-125.7765253989299</v>
       </c>
       <c r="D62">
-        <v>187.7930663529375</v>
+        <v>228.87547460107</v>
       </c>
       <c r="E62">
         <v>466.1319999999999</v>
@@ -6365,45 +6496,45 @@
         <v>47.9</v>
       </c>
       <c r="M62">
-        <v>115.4650416</v>
+        <v>94.32620159999999</v>
       </c>
       <c r="N62">
-        <v>-67.5650416</v>
+        <v>-46.42620159999999</v>
       </c>
       <c r="O62">
-        <v>-9.8644960736</v>
+        <v>-6.778225433599999</v>
       </c>
       <c r="P62">
-        <v>-57.7005455264</v>
+        <v>-39.64797616639999</v>
       </c>
       <c r="Q62">
-        <v>-2.600545526399998</v>
+        <v>15.45202383360001</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1482599848136276</v>
+        <v>0.1473287672933031</v>
       </c>
       <c r="T62">
-        <v>2.364760095916031</v>
+        <v>2.344775226173283</v>
       </c>
       <c r="U62">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.06056724964623405</v>
+        <v>0.0741405874653602</v>
       </c>
       <c r="W62">
-        <v>0.2309125700369557</v>
+        <v>0.1859125700369557</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.4148441756591373</v>
+        <v>0.5078122429134262</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6545,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1998515359476245</v>
+        <v>0.1936596845753211</v>
       </c>
       <c r="C63">
-        <v>-177.1261887459326</v>
+        <v>-169.4875751265452</v>
       </c>
       <c r="D63">
-        <v>185.3550112540674</v>
+        <v>192.9936248734548</v>
       </c>
       <c r="E63">
         <v>473.9612</v>
@@ -6447,37 +6578,37 @@
         <v>47.9</v>
       </c>
       <c r="M63">
-        <v>117.38945896</v>
+        <v>112.61364696</v>
       </c>
       <c r="N63">
-        <v>-69.48945896000001</v>
+        <v>-64.71364696000001</v>
       </c>
       <c r="O63">
-        <v>-10.14546100816</v>
+        <v>-9.448192456160001</v>
       </c>
       <c r="P63">
-        <v>-59.34399795184001</v>
+        <v>-55.26545450384</v>
       </c>
       <c r="Q63">
-        <v>-4.243997951840008</v>
+        <v>-0.165454503840003</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.150887163911413</v>
+        <v>0.1506516475721734</v>
       </c>
       <c r="T63">
-        <v>2.425394970170288</v>
+        <v>2.421516110211857</v>
       </c>
       <c r="U63">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05957434391432857</v>
+        <v>0.06210082160365549</v>
       </c>
       <c r="W63">
-        <v>0.2311566262658581</v>
+        <v>0.2211566262658581</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4080434514680039</v>
+        <v>0.4253480931757224</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6627,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2018515359476245</v>
+        <v>0.195559684575321</v>
       </c>
       <c r="C64">
-        <v>-187.3309502567949</v>
+        <v>-179.7652838042936</v>
       </c>
       <c r="D64">
-        <v>182.979449743205</v>
+        <v>190.5451161957063</v>
       </c>
       <c r="E64">
         <v>481.7904</v>
@@ -6529,37 +6660,37 @@
         <v>47.9</v>
       </c>
       <c r="M64">
-        <v>119.31387632</v>
+        <v>114.45977232</v>
       </c>
       <c r="N64">
-        <v>-71.41387632000001</v>
+        <v>-66.55977232000001</v>
       </c>
       <c r="O64">
-        <v>-10.42642594272</v>
+        <v>-9.717726758720001</v>
       </c>
       <c r="P64">
-        <v>-60.98745037728001</v>
+        <v>-56.84204556128</v>
       </c>
       <c r="Q64">
-        <v>-5.887450377280011</v>
+        <v>-1.742045561280001</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1536526155932922</v>
+        <v>0.1534109014556517</v>
       </c>
       <c r="T64">
-        <v>2.489221153595822</v>
+        <v>2.485240218375327</v>
       </c>
       <c r="U64">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05861346739958134</v>
+        <v>0.06109919544875782</v>
       </c>
       <c r="W64">
-        <v>0.2313928097131829</v>
+        <v>0.2213928097131829</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4014621054765845</v>
+        <v>0.418487640059985</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6709,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2038515359476245</v>
+        <v>0.197459684575321</v>
       </c>
       <c r="C65">
-        <v>-197.4755905800556</v>
+        <v>-189.981642407357</v>
       </c>
       <c r="D65">
-        <v>180.6640094199444</v>
+        <v>188.157957592643</v>
       </c>
       <c r="E65">
         <v>489.6196</v>
@@ -6611,37 +6742,37 @@
         <v>47.9</v>
       </c>
       <c r="M65">
-        <v>121.23829368</v>
+        <v>116.30589768</v>
       </c>
       <c r="N65">
-        <v>-73.33829368000002</v>
+        <v>-68.40589768000001</v>
       </c>
       <c r="O65">
-        <v>-10.70739087728</v>
+        <v>-9.98726106128</v>
       </c>
       <c r="P65">
-        <v>-62.63090280272002</v>
+        <v>-58.41863661872001</v>
       </c>
       <c r="Q65">
-        <v>-7.530902802720014</v>
+        <v>-3.318636618720006</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1565675511498677</v>
+        <v>0.1563193041976963</v>
       </c>
       <c r="T65">
-        <v>2.556497400990304</v>
+        <v>2.552408872926012</v>
       </c>
       <c r="U65">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05768309490117528</v>
+        <v>0.06012936694957118</v>
       </c>
       <c r="W65">
-        <v>0.2316214952732911</v>
+        <v>0.2216214952732911</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3950896911039402</v>
+        <v>0.4118449791066519</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6791,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2058515359476245</v>
+        <v>0.1993596845753211</v>
       </c>
       <c r="C66">
-        <v>-207.5623635342954</v>
+        <v>-200.1389281963759</v>
       </c>
       <c r="D66">
-        <v>178.4064364657046</v>
+        <v>185.8298718036241</v>
       </c>
       <c r="E66">
         <v>497.4488</v>
@@ -6693,37 +6824,37 @@
         <v>47.9</v>
       </c>
       <c r="M66">
-        <v>123.16271104</v>
+        <v>118.15202304</v>
       </c>
       <c r="N66">
-        <v>-75.26271104</v>
+        <v>-70.25202304000001</v>
       </c>
       <c r="O66">
-        <v>-10.98835581184</v>
+        <v>-10.25679536384</v>
       </c>
       <c r="P66">
-        <v>-64.27435522816</v>
+        <v>-59.99522767616001</v>
       </c>
       <c r="Q66">
-        <v>-9.174355228160003</v>
+        <v>-4.895227676160012</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1596444275706974</v>
+        <v>0.1593892848698545</v>
       </c>
       <c r="T66">
-        <v>2.627511217684479</v>
+        <v>2.623309119396179</v>
       </c>
       <c r="U66">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05678179654334442</v>
+        <v>0.05918984559098413</v>
       </c>
       <c r="W66">
-        <v>0.231843034409646</v>
+        <v>0.221843034409646</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3889164146804412</v>
+        <v>0.4054099013081104</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6873,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2078515359476245</v>
+        <v>0.2012596845753211</v>
       </c>
       <c r="C67">
-        <v>-217.5934116738078</v>
+        <v>-210.2393071029291</v>
       </c>
       <c r="D67">
-        <v>176.2045883261922</v>
+        <v>183.5586928970709</v>
       </c>
       <c r="E67">
         <v>505.278</v>
@@ -6775,37 +6906,37 @@
         <v>47.9</v>
       </c>
       <c r="M67">
-        <v>125.0871284</v>
+        <v>119.9981484</v>
       </c>
       <c r="N67">
-        <v>-77.18712840000001</v>
+        <v>-72.09814839999999</v>
       </c>
       <c r="O67">
-        <v>-11.2693207464</v>
+        <v>-10.5263296664</v>
       </c>
       <c r="P67">
-        <v>-65.91780765360001</v>
+        <v>-61.57181873359999</v>
       </c>
       <c r="Q67">
-        <v>-10.81780765360001</v>
+        <v>-6.471818733599989</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1628971255012887</v>
+        <v>0.1626346930089932</v>
       </c>
       <c r="T67">
-        <v>2.702582966761179</v>
+        <v>2.698260808521784</v>
       </c>
       <c r="U67">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05590823044267759</v>
+        <v>0.05827923258189207</v>
       </c>
       <c r="W67">
-        <v>0.2320577569571899</v>
+        <v>0.2220577569571899</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.382933085223819</v>
+        <v>0.3991728259033704</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6955,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2098515359476245</v>
+        <v>0.203159684575321</v>
       </c>
       <c r="C68">
-        <v>-227.5707730708758</v>
+        <v>-220.2848404506075</v>
       </c>
       <c r="D68">
-        <v>174.0564269291243</v>
+        <v>181.3423595493925</v>
       </c>
       <c r="E68">
         <v>513.1072</v>
@@ -6857,37 +6988,37 @@
         <v>47.9</v>
       </c>
       <c r="M68">
-        <v>127.01154576</v>
+        <v>121.84427376</v>
       </c>
       <c r="N68">
-        <v>-79.11154576000001</v>
+        <v>-73.94427376000002</v>
       </c>
       <c r="O68">
-        <v>-11.55028568096</v>
+        <v>-10.79586396896</v>
       </c>
       <c r="P68">
-        <v>-67.56126007904001</v>
+        <v>-63.14840979104002</v>
       </c>
       <c r="Q68">
-        <v>-12.46126007904001</v>
+        <v>-8.048409791040015</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1663411586042678</v>
+        <v>0.1660710075092577</v>
       </c>
       <c r="T68">
-        <v>2.782070701077684</v>
+        <v>2.77762142053713</v>
       </c>
       <c r="U68">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05506113604203094</v>
+        <v>0.05739621390640885</v>
       </c>
       <c r="W68">
-        <v>0.2322659727608688</v>
+        <v>0.2222659727608688</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.377131068781034</v>
+        <v>0.3931247527836222</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +7037,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2118515359476245</v>
+        <v>0.205059684575321</v>
       </c>
       <c r="C69">
-        <v>-237.4963876079148</v>
+        <v>-230.2774911949853</v>
       </c>
       <c r="D69">
-        <v>171.9600123920853</v>
+        <v>179.1789088050148</v>
       </c>
       <c r="E69">
         <v>520.9364</v>
@@ -6939,37 +7070,37 @@
         <v>47.9</v>
       </c>
       <c r="M69">
-        <v>128.93596312</v>
+        <v>123.69039912</v>
       </c>
       <c r="N69">
-        <v>-81.03596312000002</v>
+        <v>-75.79039912000002</v>
       </c>
       <c r="O69">
-        <v>-11.83125061552</v>
+        <v>-11.06539827152</v>
       </c>
       <c r="P69">
-        <v>-69.20471250448001</v>
+        <v>-64.72500084848002</v>
       </c>
       <c r="Q69">
-        <v>-14.10471250448001</v>
+        <v>-9.62500084848002</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1699939209862154</v>
+        <v>0.1697155834943868</v>
       </c>
       <c r="T69">
-        <v>2.866375873837614</v>
+        <v>2.861791766614013</v>
       </c>
       <c r="U69">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05423932804140361</v>
+        <v>0.05653955399735796</v>
       </c>
       <c r="W69">
-        <v>0.232467973167423</v>
+        <v>0.222467973167423</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.371502246858929</v>
+        <v>0.3872572191599861</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +7119,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2138515359476245</v>
+        <v>0.206959684575321</v>
       </c>
       <c r="C70">
-        <v>-247.3721028203158</v>
+        <v>-240.2191297221927</v>
       </c>
       <c r="D70">
-        <v>169.9134971796842</v>
+        <v>177.0664702778072</v>
       </c>
       <c r="E70">
         <v>528.7655999999999</v>
@@ -7021,37 +7152,37 @@
         <v>47.9</v>
       </c>
       <c r="M70">
-        <v>130.86038048</v>
+        <v>125.53652448</v>
       </c>
       <c r="N70">
-        <v>-82.96038048</v>
+        <v>-77.63652447999999</v>
       </c>
       <c r="O70">
-        <v>-12.11221555008</v>
+        <v>-11.33493257408</v>
       </c>
       <c r="P70">
-        <v>-70.84816492992</v>
+        <v>-66.30159190591999</v>
       </c>
       <c r="Q70">
-        <v>-15.74816492992</v>
+        <v>-11.20159190591999</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1738749810170346</v>
+        <v>0.1735879454785864</v>
       </c>
       <c r="T70">
-        <v>2.955950119895039</v>
+        <v>2.951222759320702</v>
       </c>
       <c r="U70">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05344169086432416</v>
+        <v>0.05570808996798506</v>
       </c>
       <c r="W70">
-        <v>0.2326640323855491</v>
+        <v>0.2226640323855491</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3660389785227682</v>
+        <v>0.3815622600546923</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7201,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2158515359476245</v>
+        <v>0.2088596845753211</v>
       </c>
       <c r="C71">
-        <v>-257.1996793269767</v>
+        <v>-250.1115392420936</v>
       </c>
       <c r="D71">
-        <v>167.9151206730232</v>
+        <v>175.0032607579063</v>
       </c>
       <c r="E71">
         <v>536.5948</v>
@@ -7103,37 +7234,37 @@
         <v>47.9</v>
       </c>
       <c r="M71">
-        <v>132.78479784</v>
+        <v>127.38264984</v>
       </c>
       <c r="N71">
-        <v>-84.88479784</v>
+        <v>-79.48264983999999</v>
       </c>
       <c r="O71">
-        <v>-12.39318048464</v>
+        <v>-11.60446687664</v>
       </c>
       <c r="P71">
-        <v>-72.49161735536001</v>
+        <v>-67.87818296335999</v>
       </c>
       <c r="Q71">
-        <v>-17.39161735536</v>
+        <v>-12.77818296335999</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1780064320175841</v>
+        <v>0.1777101372682182</v>
       </c>
       <c r="T71">
-        <v>3.051303349569073</v>
+        <v>3.046423493492337</v>
       </c>
       <c r="U71">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05266717360542091</v>
+        <v>0.05490072634526064</v>
       </c>
       <c r="W71">
-        <v>0.2328544087277875</v>
+        <v>0.2228544087277876</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3607340657905542</v>
+        <v>0.3760323722278127</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7283,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2178515359476245</v>
+        <v>0.2107596845753211</v>
       </c>
       <c r="C72">
-        <v>-266.9807958820739</v>
+        <v>-259.9564208087506</v>
       </c>
       <c r="D72">
-        <v>165.9632041179261</v>
+        <v>172.9875791912494</v>
       </c>
       <c r="E72">
         <v>544.424</v>
@@ -7185,37 +7316,37 @@
         <v>47.9</v>
       </c>
       <c r="M72">
-        <v>134.7092152</v>
+        <v>129.2287752</v>
       </c>
       <c r="N72">
-        <v>-86.80921520000001</v>
+        <v>-81.3287752</v>
       </c>
       <c r="O72">
-        <v>-12.6741454192</v>
+        <v>-11.8740011792</v>
       </c>
       <c r="P72">
-        <v>-74.13506978080001</v>
+        <v>-69.4547740208</v>
       </c>
       <c r="Q72">
-        <v>-19.03506978080001</v>
+        <v>-14.3547740208</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1824133130848369</v>
+        <v>0.1821071418438255</v>
       </c>
       <c r="T72">
-        <v>3.153013461221375</v>
+        <v>3.147970943275415</v>
       </c>
       <c r="U72">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05191478541105775</v>
+        <v>0.05411643025461407</v>
       </c>
       <c r="W72">
-        <v>0.233039345745962</v>
+        <v>0.223039345745962</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3555807219935463</v>
+        <v>0.3706604811959868</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7365,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2198515359476245</v>
+        <v>0.2126596845753211</v>
       </c>
       <c r="C73">
-        <v>-276.7170540785366</v>
+        <v>-269.7553979978895</v>
       </c>
       <c r="D73">
-        <v>164.0561459214634</v>
+        <v>171.0178020021105</v>
       </c>
       <c r="E73">
         <v>552.2532</v>
@@ -7267,37 +7398,37 @@
         <v>47.9</v>
       </c>
       <c r="M73">
-        <v>136.63363256</v>
+        <v>131.07490056</v>
       </c>
       <c r="N73">
-        <v>-88.73363256000002</v>
+        <v>-83.17490056</v>
       </c>
       <c r="O73">
-        <v>-12.95511035376</v>
+        <v>-12.14353548176</v>
       </c>
       <c r="P73">
-        <v>-75.77852220624001</v>
+        <v>-71.03136507824</v>
       </c>
       <c r="Q73">
-        <v>-20.67852220624001</v>
+        <v>-15.93136507824</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.187124116984314</v>
+        <v>0.1868073881143022</v>
       </c>
       <c r="T73">
-        <v>3.261738063332457</v>
+        <v>3.256521665457325</v>
       </c>
       <c r="U73">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05118359125033862</v>
+        <v>0.05335422701159132</v>
       </c>
       <c r="W73">
-        <v>0.2332190732706668</v>
+        <v>0.2232190732706668</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3505725428105386</v>
+        <v>0.3654399110382969</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7447,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2218515359476245</v>
+        <v>0.214559684575321</v>
       </c>
       <c r="C74">
-        <v>-286.4099827309269</v>
+        <v>-279.5100212683921</v>
       </c>
       <c r="D74">
-        <v>162.192417269073</v>
+        <v>169.0923787316079</v>
       </c>
       <c r="E74">
         <v>560.0823999999999</v>
@@ -7349,37 +7480,37 @@
         <v>47.9</v>
       </c>
       <c r="M74">
-        <v>138.55804992</v>
+        <v>132.92102592</v>
       </c>
       <c r="N74">
-        <v>-90.65804991999997</v>
+        <v>-85.02102591999997</v>
       </c>
       <c r="O74">
-        <v>-13.23607528832</v>
+        <v>-12.41306978432</v>
       </c>
       <c r="P74">
-        <v>-77.42197463167997</v>
+        <v>-72.60795613567997</v>
       </c>
       <c r="Q74">
-        <v>-22.32197463167997</v>
+        <v>-17.50795613567997</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1921714068766109</v>
+        <v>0.1918433662612415</v>
       </c>
       <c r="T74">
-        <v>3.378228708451473</v>
+        <v>3.37282601065223</v>
       </c>
       <c r="U74">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05047270803852838</v>
+        <v>0.05261319608087479</v>
       </c>
       <c r="W74">
-        <v>0.2333938083641298</v>
+        <v>0.2233938083641297</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3457034797159478</v>
+        <v>0.3603643567183206</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7529,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2238515359476245</v>
+        <v>0.2164596845753211</v>
       </c>
       <c r="C75">
-        <v>-296.061041962928</v>
+        <v>-289.2217720324436</v>
       </c>
       <c r="D75">
-        <v>160.370558037072</v>
+        <v>167.2098279675564</v>
       </c>
       <c r="E75">
         <v>567.9115999999999</v>
@@ -7431,37 +7562,37 @@
         <v>47.9</v>
       </c>
       <c r="M75">
-        <v>140.48246728</v>
+        <v>134.76715128</v>
       </c>
       <c r="N75">
-        <v>-92.58246727999997</v>
+        <v>-86.86715127999997</v>
       </c>
       <c r="O75">
-        <v>-13.51704022288</v>
+        <v>-12.68260408688</v>
       </c>
       <c r="P75">
-        <v>-79.06542705711998</v>
+        <v>-74.18454719311998</v>
       </c>
       <c r="Q75">
-        <v>-23.96542705711997</v>
+        <v>-19.08454719311998</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1975925700942632</v>
+        <v>0.1972523798264727</v>
       </c>
       <c r="T75">
-        <v>3.503348290245972</v>
+        <v>3.497745492528238</v>
       </c>
       <c r="U75">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04978130107909649</v>
+        <v>0.05189246736743815</v>
       </c>
       <c r="W75">
-        <v>0.2335637561947581</v>
+        <v>0.2235637561947581</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3409678156102499</v>
+        <v>0.3554278586810833</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7611,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2258515359476245</v>
+        <v>0.218359684575321</v>
       </c>
       <c r="C76">
-        <v>-305.6716270224114</v>
+        <v>-298.8920664567885</v>
       </c>
       <c r="D76">
-        <v>158.5891729775885</v>
+        <v>165.3687335432114</v>
       </c>
       <c r="E76">
         <v>575.7407999999999</v>
@@ -7513,37 +7644,37 @@
         <v>47.9</v>
       </c>
       <c r="M76">
-        <v>142.40688464</v>
+        <v>136.61327664</v>
       </c>
       <c r="N76">
-        <v>-94.50688463999998</v>
+        <v>-88.71327663999998</v>
       </c>
       <c r="O76">
-        <v>-13.79800515744</v>
+        <v>-12.95213838944</v>
       </c>
       <c r="P76">
-        <v>-80.70887948255998</v>
+        <v>-75.76113825055998</v>
       </c>
       <c r="Q76">
-        <v>-25.60887948255998</v>
+        <v>-20.66113825055998</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2034307458671195</v>
+        <v>0.2030774713582601</v>
       </c>
       <c r="T76">
-        <v>3.638092455255432</v>
+        <v>3.632274165317785</v>
       </c>
       <c r="U76">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04910858079424383</v>
+        <v>0.05119121780841872</v>
       </c>
       <c r="W76">
-        <v>0.2337291108407749</v>
+        <v>0.2237291108407749</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3363601424263276</v>
+        <v>0.3506247795097173</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7693,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2278515359476245</v>
+        <v>0.220259684575321</v>
       </c>
       <c r="C77">
-        <v>-315.2430718450337</v>
+        <v>-308.5222590155963</v>
       </c>
       <c r="D77">
-        <v>156.8469281549663</v>
+        <v>163.5677409844036</v>
       </c>
       <c r="E77">
         <v>583.5699999999999</v>
@@ -7595,37 +7726,37 @@
         <v>47.9</v>
       </c>
       <c r="M77">
-        <v>144.331302</v>
+        <v>138.459402</v>
       </c>
       <c r="N77">
-        <v>-96.43130199999999</v>
+        <v>-90.55940199999998</v>
       </c>
       <c r="O77">
-        <v>-14.078970092</v>
+        <v>-13.221672692</v>
       </c>
       <c r="P77">
-        <v>-82.352331908</v>
+        <v>-77.33772930799998</v>
       </c>
       <c r="Q77">
-        <v>-27.252331908</v>
+        <v>-22.23772930799998</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2097359757018042</v>
+        <v>0.2093685702125905</v>
       </c>
       <c r="T77">
-        <v>3.78361615346565</v>
+        <v>3.777565131930497</v>
       </c>
       <c r="U77">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04845379971698724</v>
+        <v>0.0505086682376398</v>
       </c>
       <c r="W77">
-        <v>0.2338900560295646</v>
+        <v>0.2238900560295645</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3318753405273099</v>
+        <v>0.3459497824495877</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7775,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2298515359476245</v>
+        <v>0.222159684575321</v>
       </c>
       <c r="C78">
-        <v>-324.7766523854884</v>
+        <v>-318.113645813666</v>
       </c>
       <c r="D78">
-        <v>155.1425476145115</v>
+        <v>161.8055541863339</v>
       </c>
       <c r="E78">
         <v>591.3992</v>
@@ -7677,37 +7808,37 @@
         <v>47.9</v>
       </c>
       <c r="M78">
-        <v>146.25571936</v>
+        <v>140.30552736</v>
       </c>
       <c r="N78">
-        <v>-98.35571935999999</v>
+        <v>-92.40552735999998</v>
       </c>
       <c r="O78">
-        <v>-14.35993502656</v>
+        <v>-13.49120699456</v>
       </c>
       <c r="P78">
-        <v>-83.99578433344</v>
+        <v>-78.91432036543998</v>
       </c>
       <c r="Q78">
-        <v>-28.89578433344</v>
+        <v>-23.81432036543998</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2165666413560461</v>
+        <v>0.2161839273047818</v>
       </c>
       <c r="T78">
-        <v>3.941266826526719</v>
+        <v>3.934963679094269</v>
       </c>
       <c r="U78">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04781624972071109</v>
+        <v>0.04984408049767085</v>
       </c>
       <c r="W78">
-        <v>0.2340467658186492</v>
+        <v>0.2240467658186492</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.327508559730898</v>
+        <v>0.3413978116278826</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7857,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2318515359476245</v>
+        <v>0.224059684575321</v>
       </c>
       <c r="C79">
-        <v>-334.2735897338992</v>
+        <v>-327.6674676971078</v>
       </c>
       <c r="D79">
-        <v>153.4748102661008</v>
+        <v>160.0809323028921</v>
       </c>
       <c r="E79">
         <v>599.2284</v>
@@ -7759,37 +7890,37 @@
         <v>47.9</v>
       </c>
       <c r="M79">
-        <v>148.18013672</v>
+        <v>142.15165272</v>
       </c>
       <c r="N79">
-        <v>-100.28013672</v>
+        <v>-94.25165271999998</v>
       </c>
       <c r="O79">
-        <v>-14.64089996112</v>
+        <v>-13.76074129712</v>
       </c>
       <c r="P79">
-        <v>-85.63923675888</v>
+        <v>-80.49091142287999</v>
       </c>
       <c r="Q79">
-        <v>-30.53923675888</v>
+        <v>-25.39091142287999</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2239912779367438</v>
+        <v>0.2235919241441202</v>
       </c>
       <c r="T79">
-        <v>4.112626253767012</v>
+        <v>4.106049056446193</v>
       </c>
       <c r="U79">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04719525946459795</v>
+        <v>0.04919675477692188</v>
       </c>
       <c r="W79">
-        <v>0.2341994052236019</v>
+        <v>0.2241994052236018</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3232552018123148</v>
+        <v>0.3369640738145335</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7939,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2338515359476245</v>
+        <v>0.225959684575321</v>
       </c>
       <c r="C80">
-        <v>-343.7350530333475</v>
+        <v>-337.1849131671888</v>
       </c>
       <c r="D80">
-        <v>151.8425469666525</v>
+        <v>158.3926868328112</v>
       </c>
       <c r="E80">
         <v>607.0576</v>
@@ -7841,37 +7972,37 @@
         <v>47.9</v>
       </c>
       <c r="M80">
-        <v>150.10455408</v>
+        <v>143.99777808</v>
       </c>
       <c r="N80">
-        <v>-102.20455408</v>
+        <v>-96.09777807999998</v>
       </c>
       <c r="O80">
-        <v>-14.92186489568</v>
+        <v>-14.03027559968</v>
       </c>
       <c r="P80">
-        <v>-87.28268918432001</v>
+        <v>-82.06750248031999</v>
       </c>
       <c r="Q80">
-        <v>-32.18268918432</v>
+        <v>-26.96750248031999</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.232090881479323</v>
+        <v>0.2316733752415802</v>
       </c>
       <c r="T80">
-        <v>4.299563810756421</v>
+        <v>4.29268764992102</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04659019203556464</v>
+        <v>0.04856602715157673</v>
       </c>
       <c r="W80">
-        <v>0.2343481307976582</v>
+        <v>0.2243481307976582</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3191109043531826</v>
+        <v>0.332644021586142</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +8021,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2358515359476245</v>
+        <v>0.2278596845753211</v>
       </c>
       <c r="C81">
-        <v>-353.162162213187</v>
+        <v>-346.6671211117227</v>
       </c>
       <c r="D81">
-        <v>150.244637786813</v>
+        <v>156.7396788882773</v>
       </c>
       <c r="E81">
         <v>614.8868</v>
@@ -7923,37 +8054,37 @@
         <v>47.9</v>
       </c>
       <c r="M81">
-        <v>152.02897144</v>
+        <v>145.84390344</v>
       </c>
       <c r="N81">
-        <v>-104.12897144</v>
+        <v>-97.94390344000001</v>
       </c>
       <c r="O81">
-        <v>-15.20282983024</v>
+        <v>-14.29980990224</v>
       </c>
       <c r="P81">
-        <v>-88.92614160976001</v>
+        <v>-83.64409353776001</v>
       </c>
       <c r="Q81">
-        <v>-33.82614160976001</v>
+        <v>-28.54409353776001</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2409618758354813</v>
+        <v>0.2405244883483221</v>
       </c>
       <c r="T81">
-        <v>4.504304944601965</v>
+        <v>4.497101347536308</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04600044276929167</v>
+        <v>0.04795126731421498</v>
       </c>
       <c r="W81">
-        <v>0.2344930911673081</v>
+        <v>0.2244930911673081</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3150715258170663</v>
+        <v>0.3284333377685958</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +8103,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2378515359476245</v>
+        <v>0.2297596845753211</v>
       </c>
       <c r="C82">
-        <v>-362.5559905515699</v>
+        <v>-356.1151833671959</v>
       </c>
       <c r="D82">
-        <v>148.6800094484301</v>
+        <v>155.1208166328042</v>
       </c>
       <c r="E82">
         <v>622.716</v>
@@ -8005,37 +8136,37 @@
         <v>47.9</v>
       </c>
       <c r="M82">
-        <v>153.9533888</v>
+        <v>147.6900288</v>
       </c>
       <c r="N82">
-        <v>-106.0533888</v>
+        <v>-99.79002880000002</v>
       </c>
       <c r="O82">
-        <v>-15.4837947648</v>
+        <v>-14.5693442048</v>
       </c>
       <c r="P82">
-        <v>-90.56959403520003</v>
+        <v>-85.22068459520001</v>
       </c>
       <c r="Q82">
-        <v>-35.46959403520002</v>
+        <v>-30.12068459520001</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2507199696272553</v>
+        <v>0.2502607127657382</v>
       </c>
       <c r="T82">
-        <v>4.729520191832063</v>
+        <v>4.721956414913122</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04542543723467552</v>
+        <v>0.0473518764727873</v>
       </c>
       <c r="W82">
-        <v>0.2346344275277168</v>
+        <v>0.2246344275277168</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.311133131744353</v>
+        <v>0.3243279210464884</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8185,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2398515359476245</v>
+        <v>0.231659684575321</v>
       </c>
       <c r="C83">
-        <v>-371.9175670795101</v>
+        <v>-365.5301471237403</v>
       </c>
       <c r="D83">
-        <v>147.1476329204899</v>
+        <v>153.5350528762598</v>
       </c>
       <c r="E83">
         <v>630.5452</v>
@@ -8087,37 +8218,37 @@
         <v>47.9</v>
       </c>
       <c r="M83">
-        <v>155.87780616</v>
+        <v>149.53615416</v>
       </c>
       <c r="N83">
-        <v>-107.97780616</v>
+        <v>-101.63615416</v>
       </c>
       <c r="O83">
-        <v>-15.76475969936</v>
+        <v>-14.83887850736</v>
       </c>
       <c r="P83">
-        <v>-92.21304646064</v>
+        <v>-86.79727565264001</v>
       </c>
       <c r="Q83">
-        <v>-37.11304646064</v>
+        <v>-31.69727565264001</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2615052311865845</v>
+        <v>0.2610218029113034</v>
       </c>
       <c r="T83">
-        <v>4.978442307191646</v>
+        <v>4.970480436750656</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04486462936758077</v>
+        <v>0.04676728540522202</v>
       </c>
       <c r="W83">
-        <v>0.2347722741014487</v>
+        <v>0.2247722741014486</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3072919819697314</v>
+        <v>0.320323872638507</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8267,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2418515359476245</v>
+        <v>0.2335596845753211</v>
       </c>
       <c r="C84">
-        <v>-381.2478788377959</v>
+        <v>-374.9130171840875</v>
       </c>
       <c r="D84">
-        <v>145.6465211622042</v>
+        <v>151.9813828159126</v>
       </c>
       <c r="E84">
         <v>638.3744</v>
@@ -8169,37 +8300,37 @@
         <v>47.9</v>
       </c>
       <c r="M84">
-        <v>157.80222352</v>
+        <v>151.38227952</v>
       </c>
       <c r="N84">
-        <v>-109.90222352</v>
+        <v>-103.48227952</v>
       </c>
       <c r="O84">
-        <v>-16.04572463392</v>
+        <v>-15.10841280992</v>
       </c>
       <c r="P84">
-        <v>-93.85649888608</v>
+        <v>-88.37386671008002</v>
       </c>
       <c r="Q84">
-        <v>-38.75649888608</v>
+        <v>-33.27386671008002</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2734888551413948</v>
+        <v>0.2729785697397092</v>
       </c>
       <c r="T84">
-        <v>5.25502243536896</v>
+        <v>5.24661823879236</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04431749974114686</v>
+        <v>0.04619695265637785</v>
       </c>
       <c r="W84">
-        <v>0.2349067585636261</v>
+        <v>0.2249067585636261</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3035445187749786</v>
+        <v>0.3164174839477936</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8349,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2438515359476245</v>
+        <v>0.2354596845753211</v>
       </c>
       <c r="C85">
-        <v>-390.5478729971578</v>
+        <v>-384.2647580867406</v>
       </c>
       <c r="D85">
-        <v>144.1757270028423</v>
+        <v>150.4588419132594</v>
       </c>
       <c r="E85">
         <v>646.2036000000001</v>
@@ -8251,37 +8382,37 @@
         <v>47.9</v>
       </c>
       <c r="M85">
-        <v>159.72664088</v>
+        <v>153.22840488</v>
       </c>
       <c r="N85">
-        <v>-111.82664088</v>
+        <v>-105.32840488</v>
       </c>
       <c r="O85">
-        <v>-16.32668956848</v>
+        <v>-15.37794711248</v>
       </c>
       <c r="P85">
-        <v>-95.49995131152001</v>
+        <v>-89.95045776752002</v>
       </c>
       <c r="Q85">
-        <v>-40.39995131152001</v>
+        <v>-34.85045776752002</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2868823172085357</v>
+        <v>0.2863420150185155</v>
       </c>
       <c r="T85">
-        <v>5.564141402155369</v>
+        <v>5.555242841074262</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04378355396113304</v>
+        <v>0.04564036286533715</v>
       </c>
       <c r="W85">
-        <v>0.2350380024363535</v>
+        <v>0.2250380024363535</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2998873558981716</v>
+        <v>0.3126052251050491</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8431,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2458515359476245</v>
+        <v>0.237359684575321</v>
       </c>
       <c r="C86">
-        <v>-399.8184588512567</v>
+        <v>-393.5862961027952</v>
       </c>
       <c r="D86">
-        <v>142.7343411487433</v>
+        <v>148.9665038972047</v>
       </c>
       <c r="E86">
         <v>654.0328</v>
@@ -8333,37 +8464,37 @@
         <v>47.9</v>
       </c>
       <c r="M86">
-        <v>161.65105824</v>
+        <v>155.07453024</v>
       </c>
       <c r="N86">
-        <v>-113.75105824</v>
+        <v>-107.17453024</v>
       </c>
       <c r="O86">
-        <v>-16.60765450304</v>
+        <v>-15.64748141504</v>
       </c>
       <c r="P86">
-        <v>-97.14340373696</v>
+        <v>-91.52704882495999</v>
       </c>
       <c r="Q86">
-        <v>-42.04340373695999</v>
+        <v>-36.42704882495999</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3019499620340691</v>
+        <v>0.3013758909571727</v>
       </c>
       <c r="T86">
-        <v>5.911900239790077</v>
+        <v>5.902445518641402</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04326232117588146</v>
+        <v>0.04509702521217838</v>
       </c>
       <c r="W86">
-        <v>0.2351661214549683</v>
+        <v>0.2251661214549683</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2963172683279552</v>
+        <v>0.3088837343299889</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8513,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2478515359476245</v>
+        <v>0.239259684575321</v>
       </c>
       <c r="C87">
-        <v>-409.0605096913092</v>
+        <v>-402.8785211150918</v>
       </c>
       <c r="D87">
-        <v>141.3214903086908</v>
+        <v>147.5034788849082</v>
       </c>
       <c r="E87">
         <v>661.862</v>
@@ -8415,37 +8546,37 @@
         <v>47.9</v>
       </c>
       <c r="M87">
-        <v>163.5754756</v>
+        <v>156.9206556</v>
       </c>
       <c r="N87">
-        <v>-115.6754756</v>
+        <v>-109.0206556</v>
       </c>
       <c r="O87">
-        <v>-16.8886194376</v>
+        <v>-15.9170157176</v>
       </c>
       <c r="P87">
-        <v>-98.7868561624</v>
+        <v>-93.1036398824</v>
       </c>
       <c r="Q87">
-        <v>-43.6868561624</v>
+        <v>-38.0036398824</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3190266261696738</v>
+        <v>0.3184142836876508</v>
       </c>
       <c r="T87">
-        <v>6.30602692244275</v>
+        <v>6.295941886550828</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04275335269145933</v>
+        <v>0.04456647197438805</v>
       </c>
       <c r="W87">
-        <v>0.2352912259084393</v>
+        <v>0.2252912259084393</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2928311828182146</v>
+        <v>0.3052498080437538</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8595,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2498515359476245</v>
+        <v>0.2411596845753211</v>
       </c>
       <c r="C88">
-        <v>-418.2748645704664</v>
+        <v>-412.1422883877128</v>
       </c>
       <c r="D88">
-        <v>139.9363354295336</v>
+        <v>146.0689116122872</v>
       </c>
       <c r="E88">
         <v>669.6912</v>
@@ -8497,37 +8628,37 @@
         <v>47.9</v>
       </c>
       <c r="M88">
-        <v>165.49989296</v>
+        <v>158.76678096</v>
       </c>
       <c r="N88">
-        <v>-117.59989296</v>
+        <v>-110.86678096</v>
       </c>
       <c r="O88">
-        <v>-17.16958437216</v>
+        <v>-16.18655002016</v>
       </c>
       <c r="P88">
-        <v>-100.43030858784</v>
+        <v>-94.68023093984</v>
       </c>
       <c r="Q88">
-        <v>-45.33030858784</v>
+        <v>-39.58023093984</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3385428137532218</v>
+        <v>0.3378867325224831</v>
       </c>
       <c r="T88">
-        <v>6.756457416902946</v>
+        <v>6.745652021304459</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0422562206834191</v>
+        <v>0.04404825718398819</v>
       </c>
       <c r="W88">
-        <v>0.2354134209560156</v>
+        <v>0.2254134209560156</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2894261690645145</v>
+        <v>0.301700391671152</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8677,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2518515359476245</v>
+        <v>0.243059684575321</v>
       </c>
       <c r="C89">
-        <v>-427.4623299654412</v>
+        <v>-421.3784202332181</v>
       </c>
       <c r="D89">
-        <v>138.5780700345588</v>
+        <v>144.6619797667819</v>
       </c>
       <c r="E89">
         <v>677.5204</v>
@@ -8579,37 +8710,37 @@
         <v>47.9</v>
       </c>
       <c r="M89">
-        <v>167.42431032</v>
+        <v>160.61290632</v>
       </c>
       <c r="N89">
-        <v>-119.52431032</v>
+        <v>-112.71290632</v>
       </c>
       <c r="O89">
-        <v>-17.45054930672</v>
+        <v>-16.45608432272</v>
       </c>
       <c r="P89">
-        <v>-102.07376101328</v>
+        <v>-96.25682199728</v>
       </c>
       <c r="Q89">
-        <v>-46.97376101328</v>
+        <v>-41.15682199728</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3610614917342389</v>
+        <v>0.3603549427165202</v>
       </c>
       <c r="T89">
-        <v>7.276184910510865</v>
+        <v>7.264548330635572</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04177051699740279</v>
+        <v>0.04354195537727568</v>
       </c>
       <c r="W89">
-        <v>0.2355328069220384</v>
+        <v>0.2255328069220384</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2860994314890603</v>
+        <v>0.2982325710772308</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8759,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2538515359476245</v>
+        <v>0.2449596845753211</v>
       </c>
       <c r="C90">
-        <v>-436.6236813422947</v>
+        <v>-430.5877075844458</v>
       </c>
       <c r="D90">
-        <v>137.2459186577053</v>
+        <v>143.2818924155542</v>
       </c>
       <c r="E90">
         <v>685.3496</v>
@@ -8661,37 +8792,37 @@
         <v>47.9</v>
       </c>
       <c r="M90">
-        <v>169.34872768</v>
+        <v>162.45903168</v>
       </c>
       <c r="N90">
-        <v>-121.44872768</v>
+        <v>-114.55903168</v>
       </c>
       <c r="O90">
-        <v>-17.73151424128</v>
+        <v>-16.72561862528</v>
       </c>
       <c r="P90">
-        <v>-103.71721343872</v>
+        <v>-97.83341305472001</v>
       </c>
       <c r="Q90">
-        <v>-48.61721343872002</v>
+        <v>-42.73341305472001</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3873332827120922</v>
+        <v>0.3865678546095637</v>
       </c>
       <c r="T90">
-        <v>7.882533653053438</v>
+        <v>7.869927358188537</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04129585203152321</v>
+        <v>0.04304716042980664</v>
       </c>
       <c r="W90">
-        <v>0.2356494795706516</v>
+        <v>0.2256494795706516</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2828483015857755</v>
+        <v>0.2948435645877168</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8841,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2558515359476244</v>
+        <v>0.246859684575321</v>
       </c>
       <c r="C91">
-        <v>-445.7596646327719</v>
+        <v>-439.7709114771932</v>
       </c>
       <c r="D91">
-        <v>135.9391353672282</v>
+        <v>141.9278885228068</v>
       </c>
       <c r="E91">
         <v>693.1788</v>
@@ -8743,37 +8874,37 @@
         <v>47.9</v>
       </c>
       <c r="M91">
-        <v>171.27314504</v>
+        <v>164.30515704</v>
       </c>
       <c r="N91">
-        <v>-123.37314504</v>
+        <v>-116.40515704</v>
       </c>
       <c r="O91">
-        <v>-18.01247917584</v>
+        <v>-16.99515292784</v>
       </c>
       <c r="P91">
-        <v>-105.36066586416</v>
+        <v>-99.41000411216001</v>
       </c>
       <c r="Q91">
-        <v>-50.26066586416002</v>
+        <v>-44.31000411216001</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.418381762958646</v>
+        <v>0.4175467504831603</v>
       </c>
       <c r="T91">
-        <v>8.599127621512842</v>
+        <v>8.58537529984204</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04083185369409036</v>
+        <v>0.04256348446992117</v>
       </c>
       <c r="W91">
-        <v>0.2357635303619926</v>
+        <v>0.2257635303619926</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2796702307814409</v>
+        <v>0.2915307155474053</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8923,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2578515359476245</v>
+        <v>0.248759684575321</v>
       </c>
       <c r="C92">
-        <v>-454.8709976270908</v>
+        <v>-448.9287644496176</v>
       </c>
       <c r="D92">
-        <v>134.6570023729092</v>
+        <v>140.5992355503824</v>
       </c>
       <c r="E92">
         <v>701.0079999999999</v>
@@ -8825,37 +8956,37 @@
         <v>47.9</v>
       </c>
       <c r="M92">
-        <v>173.1975624</v>
+        <v>166.1512824</v>
       </c>
       <c r="N92">
-        <v>-125.2975624</v>
+        <v>-118.2512824</v>
       </c>
       <c r="O92">
-        <v>-18.2934441104</v>
+        <v>-17.2646872304</v>
       </c>
       <c r="P92">
-        <v>-107.0041182896</v>
+        <v>-100.9865951696</v>
       </c>
       <c r="Q92">
-        <v>-51.9041182896</v>
+        <v>-45.88659516959998</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4556399392545106</v>
+        <v>0.4547214255314764</v>
       </c>
       <c r="T92">
-        <v>9.459040383664126</v>
+        <v>9.443912829826244</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0403781664308227</v>
+        <v>0.04209055686469983</v>
       </c>
       <c r="W92">
-        <v>0.2358750466913038</v>
+        <v>0.2258750466913038</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2765627837727582</v>
+        <v>0.2882914853746564</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +9005,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2598515359476245</v>
+        <v>0.2506596845753211</v>
       </c>
       <c r="C93">
-        <v>-463.9583712886511</v>
+        <v>-458.0619718637631</v>
       </c>
       <c r="D93">
-        <v>133.3988287113489</v>
+        <v>139.2952281362368</v>
       </c>
       <c r="E93">
         <v>708.8371999999999</v>
@@ -8907,37 +9038,37 @@
         <v>47.9</v>
       </c>
       <c r="M93">
-        <v>175.12197976</v>
+        <v>167.99740776</v>
       </c>
       <c r="N93">
-        <v>-127.22197976</v>
+        <v>-120.09740776</v>
       </c>
       <c r="O93">
-        <v>-18.57440904496</v>
+        <v>-17.53422153296</v>
       </c>
       <c r="P93">
-        <v>-108.64757071504</v>
+        <v>-102.56318622704</v>
       </c>
       <c r="Q93">
-        <v>-53.54757071503999</v>
+        <v>-47.46318622703998</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.5011777102827897</v>
+        <v>0.5001571394794182</v>
       </c>
       <c r="T93">
-        <v>10.51004487073792</v>
+        <v>10.49323647758472</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03993445031619827</v>
+        <v>0.04162802327278005</v>
       </c>
       <c r="W93">
-        <v>0.2359841121122785</v>
+        <v>0.2259841121122785</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2735236323027279</v>
+        <v>0.2851234470738361</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +9087,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2618515359476245</v>
+        <v>0.2525596845753211</v>
       </c>
       <c r="C94">
-        <v>-473.0224509957195</v>
+        <v>-467.1712131542229</v>
       </c>
       <c r="D94">
-        <v>132.1639490042805</v>
+        <v>138.0151868457771</v>
       </c>
       <c r="E94">
         <v>716.6664</v>
@@ -8989,37 +9120,37 @@
         <v>47.9</v>
       </c>
       <c r="M94">
-        <v>177.04639712</v>
+        <v>169.84353312</v>
       </c>
       <c r="N94">
-        <v>-129.14639712</v>
+        <v>-121.94353312</v>
       </c>
       <c r="O94">
-        <v>-18.85537397952</v>
+        <v>-17.80375583552</v>
       </c>
       <c r="P94">
-        <v>-110.29102314048</v>
+        <v>-104.13977728448</v>
       </c>
       <c r="Q94">
-        <v>-55.19102314047999</v>
+        <v>-49.03977728447999</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5580999240681385</v>
+        <v>0.5569517819143457</v>
       </c>
       <c r="T94">
-        <v>11.82380047958016</v>
+        <v>11.80489103728281</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03950038020406568</v>
+        <v>0.04117554475894548</v>
       </c>
       <c r="W94">
-        <v>0.2360908065458407</v>
+        <v>0.2260908065458407</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2705505493429157</v>
+        <v>0.2820242791708596</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9169,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2638515359476244</v>
+        <v>0.2544596845753211</v>
       </c>
       <c r="C95">
-        <v>-482.0638777147831</v>
+        <v>-476.2571430085821</v>
       </c>
       <c r="D95">
-        <v>130.9517222852169</v>
+        <v>136.7584569914179</v>
       </c>
       <c r="E95">
         <v>724.4956</v>
@@ -9071,37 +9202,37 @@
         <v>47.9</v>
       </c>
       <c r="M95">
-        <v>178.97081448</v>
+        <v>171.68965848</v>
       </c>
       <c r="N95">
-        <v>-131.07081448</v>
+        <v>-123.78965848</v>
       </c>
       <c r="O95">
-        <v>-19.13633891408</v>
+        <v>-18.07329013808</v>
       </c>
       <c r="P95">
-        <v>-111.93447556592</v>
+        <v>-105.71636834192</v>
       </c>
       <c r="Q95">
-        <v>-56.83447556591999</v>
+        <v>-50.61636834191999</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.631285627506444</v>
+        <v>0.6299734650449665</v>
       </c>
       <c r="T95">
-        <v>13.5129148338059</v>
+        <v>13.49130404260893</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03907564493305422</v>
+        <v>0.04073279696583854</v>
       </c>
       <c r="W95">
-        <v>0.2361952064754553</v>
+        <v>0.2261952064754553</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2676414036510564</v>
+        <v>0.27899176003999</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9251,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2658515359476245</v>
+        <v>0.256359684575321</v>
       </c>
       <c r="C96">
-        <v>-491.0832691099151</v>
+        <v>-485.3203924839495</v>
       </c>
       <c r="D96">
-        <v>129.7615308900849</v>
+        <v>135.5244075160505</v>
       </c>
       <c r="E96">
         <v>732.3248</v>
@@ -9153,37 +9284,37 @@
         <v>47.9</v>
       </c>
       <c r="M96">
-        <v>180.89523184</v>
+        <v>173.53578384</v>
       </c>
       <c r="N96">
-        <v>-132.99523184</v>
+        <v>-125.63578384</v>
       </c>
       <c r="O96">
-        <v>-19.41730384864</v>
+        <v>-18.34282444064</v>
       </c>
       <c r="P96">
-        <v>-113.57792799136</v>
+        <v>-107.29295939936</v>
       </c>
       <c r="Q96">
-        <v>-58.47792799136</v>
+        <v>-52.19295939935999</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7288665654241849</v>
+        <v>0.7273357092191278</v>
       </c>
       <c r="T96">
-        <v>15.76506730610689</v>
+        <v>15.73985471637709</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03865994658270258</v>
+        <v>0.04029946933854239</v>
       </c>
       <c r="W96">
-        <v>0.2362973851299717</v>
+        <v>0.2262973851299717</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2647941546760452</v>
+        <v>0.2760237625927562</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9333,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2678515359476245</v>
+        <v>0.2582596845753211</v>
       </c>
       <c r="C97">
-        <v>-500.0812205921899</v>
+        <v>-494.3615700635793</v>
       </c>
       <c r="D97">
-        <v>128.5927794078102</v>
+        <v>134.3124299364208</v>
       </c>
       <c r="E97">
         <v>740.154</v>
@@ -9235,37 +9366,37 @@
         <v>47.9</v>
       </c>
       <c r="M97">
-        <v>182.8196492</v>
+        <v>175.3819092</v>
       </c>
       <c r="N97">
-        <v>-134.9196492</v>
+        <v>-127.4819092</v>
       </c>
       <c r="O97">
-        <v>-19.6982687832</v>
+        <v>-18.6123587432</v>
       </c>
       <c r="P97">
-        <v>-115.2213804168</v>
+        <v>-108.8695504568</v>
       </c>
       <c r="Q97">
-        <v>-60.1213804168</v>
+        <v>-53.7695504568</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8654798785090223</v>
+        <v>0.8636428510629538</v>
       </c>
       <c r="T97">
-        <v>18.91808076732828</v>
+        <v>18.88782565965251</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03825299977656887</v>
+        <v>0.03987526439813668</v>
       </c>
       <c r="W97">
-        <v>0.2363974126549194</v>
+        <v>0.2263974126549194</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2620068477847183</v>
+        <v>0.2731182493023061</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9415,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2698515359476245</v>
+        <v>0.2601596845753211</v>
       </c>
       <c r="C98">
-        <v>-509.0583063128917</v>
+        <v>-503.3812626572997</v>
       </c>
       <c r="D98">
-        <v>127.4448936871082</v>
+        <v>133.1219373427002</v>
       </c>
       <c r="E98">
         <v>747.9831999999999</v>
@@ -9317,37 +9448,37 @@
         <v>47.9</v>
       </c>
       <c r="M98">
-        <v>184.74406656</v>
+        <v>177.22803456</v>
       </c>
       <c r="N98">
-        <v>-136.84406656</v>
+        <v>-129.32803456</v>
       </c>
       <c r="O98">
-        <v>-19.97923371776</v>
+        <v>-18.88189304576</v>
       </c>
       <c r="P98">
-        <v>-116.86483284224</v>
+        <v>-110.44614151424</v>
       </c>
       <c r="Q98">
-        <v>-61.76483284223999</v>
+        <v>-55.34614151424</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.070399848136276</v>
+        <v>1.06810356382869</v>
       </c>
       <c r="T98">
-        <v>23.64760095916029</v>
+        <v>23.60978207456559</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03785453102889628</v>
+        <v>0.03945989706065609</v>
       </c>
       <c r="W98">
-        <v>0.2364953562730973</v>
+        <v>0.2264953562730973</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2592776097869609</v>
+        <v>0.2702732675387404</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9497,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2718515359476245</v>
+        <v>0.262059684575321</v>
       </c>
       <c r="C99">
-        <v>-518.0150801039996</v>
+        <v>-512.3800365492058</v>
       </c>
       <c r="D99">
-        <v>126.3173198960003</v>
+        <v>131.9523634507942</v>
       </c>
       <c r="E99">
         <v>755.8123999999999</v>
@@ -9399,37 +9530,37 @@
         <v>47.9</v>
       </c>
       <c r="M99">
-        <v>186.66848392</v>
+        <v>179.07415992</v>
       </c>
       <c r="N99">
-        <v>-138.76848392</v>
+        <v>-131.17415992</v>
       </c>
       <c r="O99">
-        <v>-20.26019865232</v>
+        <v>-19.15142734832</v>
       </c>
       <c r="P99">
-        <v>-118.50828526768</v>
+        <v>-112.02273257168</v>
       </c>
       <c r="Q99">
-        <v>-63.40828526767999</v>
+        <v>-56.92273257167999</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.411933130848368</v>
+        <v>1.408871418438253</v>
       </c>
       <c r="T99">
-        <v>31.53013461221373</v>
+        <v>31.47970943275412</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03746427813169117</v>
+        <v>0.0390530939981751</v>
       </c>
       <c r="W99">
-        <v>0.2365912804352303</v>
+        <v>0.2265912804352303</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2566046447376108</v>
+        <v>0.2674869451929802</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9579,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2738515359476245</v>
+        <v>0.263959684575321</v>
       </c>
       <c r="C100">
-        <v>-526.9520763691825</v>
+        <v>-521.358438295828</v>
       </c>
       <c r="D100">
-        <v>125.2095236308175</v>
+        <v>130.8031617041719</v>
       </c>
       <c r="E100">
         <v>763.6415999999999</v>
@@ -9481,37 +9612,37 @@
         <v>47.9</v>
       </c>
       <c r="M100">
-        <v>188.59290128</v>
+        <v>180.92028528</v>
       </c>
       <c r="N100">
-        <v>-140.69290128</v>
+        <v>-133.02028528</v>
       </c>
       <c r="O100">
-        <v>-20.54116358688</v>
+        <v>-19.42096165088</v>
       </c>
       <c r="P100">
-        <v>-120.15173769312</v>
+        <v>-113.59932362912</v>
       </c>
       <c r="Q100">
-        <v>-65.05173769312</v>
+        <v>-58.49932362911999</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.094999696272551</v>
+        <v>2.09040712765738</v>
       </c>
       <c r="T100">
-        <v>47.29520191832059</v>
+        <v>47.21956414913118</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03708198957932696</v>
+        <v>0.03865459303901005</v>
       </c>
       <c r="W100">
-        <v>0.2366852469614014</v>
+        <v>0.2266852469614014</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,7 +9650,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2539862299953902</v>
+        <v>0.264757486568562</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9661,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2758515359476245</v>
+        <v>0.2658596845753211</v>
       </c>
       <c r="C101">
-        <v>-535.8698109283199</v>
+        <v>-530.3169955777742</v>
       </c>
       <c r="D101">
-        <v>124.1209890716801</v>
+        <v>129.6738044222257</v>
       </c>
       <c r="E101">
         <v>771.4707999999999</v>
@@ -9563,37 +9694,37 @@
         <v>47.9</v>
       </c>
       <c r="M101">
-        <v>190.51731864</v>
+        <v>182.76641064</v>
       </c>
       <c r="N101">
-        <v>-142.61731864</v>
+        <v>-134.86641064</v>
       </c>
       <c r="O101">
-        <v>-20.82212852144</v>
+        <v>-19.69049595344</v>
       </c>
       <c r="P101">
-        <v>-121.79519011856</v>
+        <v>-115.17591468656</v>
       </c>
       <c r="Q101">
-        <v>-66.69519011856002</v>
+        <v>-60.07591468655999</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.144199392545103</v>
+        <v>4.13501425531476</v>
       </c>
       <c r="T101">
-        <v>94.59040383664117</v>
+        <v>94.43912829826236</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.03670742402802063</v>
+        <v>0.03826414260427257</v>
       </c>
       <c r="W101">
-        <v>0.2367773151739125</v>
+        <v>0.2267773151739125</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9601,7 +9732,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2514207125206893</v>
+        <v>0.2620831685224149</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/switzerland/switzerland_steel.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_steel.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08830218928668868</v>
+        <v>0.0882116980903301</v>
       </c>
       <c r="C2">
-        <v>786.5001555626711</v>
+        <v>780.1034802209106</v>
       </c>
       <c r="D2">
-        <v>671.4001555626711</v>
+        <v>672.8326802209106</v>
       </c>
       <c r="E2">
-        <v>-3.62</v>
+        <v>4.2092</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.8292</v>
       </c>
       <c r="G2">
         <v>115.1</v>
@@ -1576,28 +1576,28 @@
         <v>47.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.39380876</v>
       </c>
       <c r="N2">
-        <v>47.9</v>
+        <v>47.50619124</v>
       </c>
       <c r="O2">
-        <v>6.993399999999999</v>
+        <v>6.93590392104</v>
       </c>
       <c r="P2">
-        <v>40.9066</v>
+        <v>40.57028731896</v>
       </c>
       <c r="Q2">
-        <v>96.00659999999999</v>
+        <v>95.67028731895999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08830218928668868</v>
+        <v>0.08866882433366677</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161358</v>
+        <v>0.9900421324172466</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>121.6326421992238</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0882116980903301</v>
+        <v>0.08812120689397154</v>
       </c>
       <c r="C3">
-        <v>780.1034802209106</v>
+        <v>773.7129309270415</v>
       </c>
       <c r="D3">
-        <v>672.8326802209106</v>
+        <v>674.2713309270415</v>
       </c>
       <c r="E3">
-        <v>4.2092</v>
+        <v>12.0384</v>
       </c>
       <c r="F3">
-        <v>7.8292</v>
+        <v>15.6584</v>
       </c>
       <c r="G3">
         <v>115.1</v>
@@ -1658,28 +1658,28 @@
         <v>47.9</v>
       </c>
       <c r="M3">
-        <v>0.39380876</v>
+        <v>0.7876175200000001</v>
       </c>
       <c r="N3">
-        <v>47.50619124</v>
+        <v>47.11238248</v>
       </c>
       <c r="O3">
-        <v>6.93590392104</v>
+        <v>6.87840784208</v>
       </c>
       <c r="P3">
-        <v>40.57028731896</v>
+        <v>40.23397463792</v>
       </c>
       <c r="Q3">
-        <v>95.67028731895999</v>
+        <v>95.33397463791999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08866882433366677</v>
+        <v>0.08904294172854239</v>
       </c>
       <c r="T3">
-        <v>0.9900421324172466</v>
+        <v>0.998682257010217</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>121.6326421992238</v>
+        <v>60.8163210996119</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08812120689397154</v>
+        <v>0.08803071569761296</v>
       </c>
       <c r="C4">
-        <v>773.7129309270415</v>
+        <v>767.3285470614109</v>
       </c>
       <c r="D4">
-        <v>674.2713309270415</v>
+        <v>675.7161470614109</v>
       </c>
       <c r="E4">
-        <v>12.0384</v>
+        <v>19.8676</v>
       </c>
       <c r="F4">
-        <v>15.6584</v>
+        <v>23.4876</v>
       </c>
       <c r="G4">
         <v>115.1</v>
@@ -1740,28 +1740,28 @@
         <v>47.9</v>
       </c>
       <c r="M4">
-        <v>0.7876175200000001</v>
+        <v>1.18142628</v>
       </c>
       <c r="N4">
-        <v>47.11238248</v>
+        <v>46.71857372</v>
       </c>
       <c r="O4">
-        <v>6.87840784208</v>
+        <v>6.82091176312</v>
       </c>
       <c r="P4">
-        <v>40.23397463792</v>
+        <v>39.89766195688</v>
       </c>
       <c r="Q4">
-        <v>95.33397463791999</v>
+        <v>94.99766195687999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08904294172854239</v>
+        <v>0.08942477288413708</v>
       </c>
       <c r="T4">
-        <v>0.998682257010217</v>
+        <v>1.007500528502011</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.8163210996119</v>
+        <v>40.54421406640794</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08803071569761296</v>
+        <v>0.08794022450125441</v>
       </c>
       <c r="C5">
-        <v>767.3285470614109</v>
+        <v>760.9503683426231</v>
       </c>
       <c r="D5">
-        <v>675.7161470614109</v>
+        <v>677.1671683426231</v>
       </c>
       <c r="E5">
-        <v>19.8676</v>
+        <v>27.6968</v>
       </c>
       <c r="F5">
-        <v>23.4876</v>
+        <v>31.3168</v>
       </c>
       <c r="G5">
         <v>115.1</v>
@@ -1822,28 +1822,28 @@
         <v>47.9</v>
       </c>
       <c r="M5">
-        <v>1.18142628</v>
+        <v>1.57523504</v>
       </c>
       <c r="N5">
-        <v>46.71857372</v>
+        <v>46.32476496</v>
       </c>
       <c r="O5">
-        <v>6.82091176312</v>
+        <v>6.763415684159999</v>
       </c>
       <c r="P5">
-        <v>39.89766195688</v>
+        <v>39.56134927583999</v>
       </c>
       <c r="Q5">
-        <v>94.99766195687999</v>
+        <v>94.66134927584</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08942477288413708</v>
+        <v>0.08981455885547335</v>
       </c>
       <c r="T5">
-        <v>1.007500528502011</v>
+        <v>1.016502513983218</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.54421406640794</v>
+        <v>30.40816054980595</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08794022450125441</v>
+        <v>0.08784973330489584</v>
       </c>
       <c r="C6">
-        <v>760.9503683426231</v>
+        <v>754.578434831182</v>
       </c>
       <c r="D6">
-        <v>677.1671683426231</v>
+        <v>678.6244348311819</v>
       </c>
       <c r="E6">
-        <v>27.6968</v>
+        <v>35.526</v>
       </c>
       <c r="F6">
-        <v>31.3168</v>
+        <v>39.146</v>
       </c>
       <c r="G6">
         <v>115.1</v>
@@ -1904,28 +1904,28 @@
         <v>47.9</v>
       </c>
       <c r="M6">
-        <v>1.57523504</v>
+        <v>1.9690438</v>
       </c>
       <c r="N6">
-        <v>46.32476496</v>
+        <v>45.9309562</v>
       </c>
       <c r="O6">
-        <v>6.763415684159999</v>
+        <v>6.705919605199999</v>
       </c>
       <c r="P6">
-        <v>39.56134927583999</v>
+        <v>39.2250365948</v>
       </c>
       <c r="Q6">
-        <v>94.66134927584</v>
+        <v>94.3250365948</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08981455885547335</v>
+        <v>0.09021255084725879</v>
       </c>
       <c r="T6">
-        <v>1.016502513983218</v>
+        <v>1.02569401494824</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.40816054980595</v>
+        <v>24.32652843984476</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08784973330489584</v>
+        <v>0.08775924210853728</v>
       </c>
       <c r="C7">
-        <v>754.578434831182</v>
+        <v>748.2127869331762</v>
       </c>
       <c r="D7">
-        <v>678.6244348311819</v>
+        <v>680.0879869331761</v>
       </c>
       <c r="E7">
-        <v>35.526</v>
+        <v>43.3552</v>
       </c>
       <c r="F7">
-        <v>39.146</v>
+        <v>46.9752</v>
       </c>
       <c r="G7">
         <v>115.1</v>
@@ -1986,28 +1986,28 @@
         <v>47.9</v>
       </c>
       <c r="M7">
-        <v>1.9690438</v>
+        <v>2.36285256</v>
       </c>
       <c r="N7">
-        <v>45.9309562</v>
+        <v>45.53714744</v>
       </c>
       <c r="O7">
-        <v>6.705919605199999</v>
+        <v>6.648423526239999</v>
       </c>
       <c r="P7">
-        <v>39.2250365948</v>
+        <v>38.88872391376</v>
       </c>
       <c r="Q7">
-        <v>94.3250365948</v>
+        <v>93.98872391376</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09021255084725879</v>
+        <v>0.09061901075376308</v>
       </c>
       <c r="T7">
-        <v>1.02569401494824</v>
+        <v>1.035081079763581</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.32652843984476</v>
+        <v>20.27210703320397</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08775924210853728</v>
+        <v>0.08766875091217873</v>
       </c>
       <c r="C8">
-        <v>748.2127869331762</v>
+        <v>741.8534654040135</v>
       </c>
       <c r="D8">
-        <v>680.0879869331761</v>
+        <v>681.5578654040135</v>
       </c>
       <c r="E8">
-        <v>43.3552</v>
+        <v>51.1844</v>
       </c>
       <c r="F8">
-        <v>46.97519999999999</v>
+        <v>54.80439999999999</v>
       </c>
       <c r="G8">
         <v>115.1</v>
@@ -2068,28 +2068,28 @@
         <v>47.9</v>
       </c>
       <c r="M8">
-        <v>2.36285256</v>
+        <v>2.75666132</v>
       </c>
       <c r="N8">
-        <v>45.53714744</v>
+        <v>45.14333868</v>
       </c>
       <c r="O8">
-        <v>6.648423526239999</v>
+        <v>6.590927447279999</v>
       </c>
       <c r="P8">
-        <v>38.88872391376</v>
+        <v>38.55241123272</v>
       </c>
       <c r="Q8">
-        <v>93.98872391376</v>
+        <v>93.65241123272</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09061901075376308</v>
+        <v>0.09103421173352551</v>
       </c>
       <c r="T8">
-        <v>1.035081079763581</v>
+        <v>1.044670016940543</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.27210703320397</v>
+        <v>17.37609174274626</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08766875091217873</v>
+        <v>0.08757825971582014</v>
       </c>
       <c r="C9">
-        <v>741.8534654040135</v>
+        <v>735.5005113522059</v>
       </c>
       <c r="D9">
-        <v>681.5578654040135</v>
+        <v>683.0341113522059</v>
       </c>
       <c r="E9">
-        <v>51.1844</v>
+        <v>59.0136</v>
       </c>
       <c r="F9">
-        <v>54.8044</v>
+        <v>62.6336</v>
       </c>
       <c r="G9">
         <v>115.1</v>
@@ -2150,28 +2150,28 @@
         <v>47.9</v>
       </c>
       <c r="M9">
-        <v>2.75666132</v>
+        <v>3.15047008</v>
       </c>
       <c r="N9">
-        <v>45.14333868</v>
+        <v>44.74952992</v>
       </c>
       <c r="O9">
-        <v>6.590927447279999</v>
+        <v>6.53343136832</v>
       </c>
       <c r="P9">
-        <v>38.55241123272</v>
+        <v>38.21609855168</v>
       </c>
       <c r="Q9">
-        <v>93.65241123272</v>
+        <v>93.31609855168</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09103421173352551</v>
+        <v>0.09145843882154364</v>
       </c>
       <c r="T9">
-        <v>1.044670016940543</v>
+        <v>1.054467409273525</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.37609174274626</v>
+        <v>15.20408027490297</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08757825971582014</v>
+        <v>0.08748776851946159</v>
       </c>
       <c r="C10">
-        <v>735.5005113522059</v>
+        <v>729.153966243199</v>
       </c>
       <c r="D10">
-        <v>683.0341113522059</v>
+        <v>684.516766243199</v>
       </c>
       <c r="E10">
-        <v>59.0136</v>
+        <v>66.84279999999998</v>
       </c>
       <c r="F10">
-        <v>62.6336</v>
+        <v>70.46279999999999</v>
       </c>
       <c r="G10">
         <v>115.1</v>
@@ -2232,28 +2232,28 @@
         <v>47.9</v>
       </c>
       <c r="M10">
-        <v>3.15047008</v>
+        <v>3.54427884</v>
       </c>
       <c r="N10">
-        <v>44.74952992</v>
+        <v>44.35572116</v>
       </c>
       <c r="O10">
-        <v>6.53343136832</v>
+        <v>6.47593528936</v>
       </c>
       <c r="P10">
-        <v>38.21609855168</v>
+        <v>37.87978587064</v>
       </c>
       <c r="Q10">
-        <v>93.31609855168</v>
+        <v>92.97978587064</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09145843882154364</v>
+        <v>0.09189198958182591</v>
       </c>
       <c r="T10">
-        <v>1.054467409273525</v>
+        <v>1.064480128910529</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.20408027490297</v>
+        <v>13.51473802213598</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08748776851946159</v>
+        <v>0.08752537732310303</v>
       </c>
       <c r="C11">
-        <v>729.153966243199</v>
+        <v>720.7077830472995</v>
       </c>
       <c r="D11">
-        <v>684.516766243199</v>
+        <v>683.8997830472995</v>
       </c>
       <c r="E11">
-        <v>66.84279999999998</v>
+        <v>74.67199999999998</v>
       </c>
       <c r="F11">
-        <v>70.46279999999999</v>
+        <v>78.29199999999999</v>
       </c>
       <c r="G11">
         <v>115.1</v>
@@ -2314,45 +2314,45 @@
         <v>47.9</v>
       </c>
       <c r="M11">
-        <v>3.54427884</v>
+        <v>4.0555256</v>
       </c>
       <c r="N11">
-        <v>44.35572116</v>
+        <v>43.8444744</v>
       </c>
       <c r="O11">
-        <v>6.47593528936</v>
+        <v>6.401293262399999</v>
       </c>
       <c r="P11">
-        <v>37.87978587064</v>
+        <v>37.44318113759999</v>
       </c>
       <c r="Q11">
-        <v>92.97978587064</v>
+        <v>92.54318113759999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09189198958182591</v>
+        <v>0.0923351748034478</v>
       </c>
       <c r="T11">
-        <v>1.064480128910529</v>
+        <v>1.074715353428356</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V11">
         <v>0.146</v>
       </c>
       <c r="W11">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.51473802213598</v>
+        <v>11.8110461440559</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08752537732310303</v>
+        <v>0.08744769612674447</v>
       </c>
       <c r="C12">
-        <v>720.7077830472995</v>
+        <v>714.1541915029221</v>
       </c>
       <c r="D12">
-        <v>683.8997830472995</v>
+        <v>685.1753915029221</v>
       </c>
       <c r="E12">
-        <v>74.672</v>
+        <v>82.5012</v>
       </c>
       <c r="F12">
-        <v>78.292</v>
+        <v>86.1212</v>
       </c>
       <c r="G12">
         <v>115.1</v>
@@ -2396,28 +2396,28 @@
         <v>47.9</v>
       </c>
       <c r="M12">
-        <v>4.0555256</v>
+        <v>4.46107816</v>
       </c>
       <c r="N12">
-        <v>43.8444744</v>
+        <v>43.43892184</v>
       </c>
       <c r="O12">
-        <v>6.401293262399999</v>
+        <v>6.342082588639999</v>
       </c>
       <c r="P12">
-        <v>37.44318113759999</v>
+        <v>37.09683925136</v>
       </c>
       <c r="Q12">
-        <v>92.54318113759999</v>
+        <v>92.19683925136</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0923351748034478</v>
+        <v>0.0927883192435331</v>
       </c>
       <c r="T12">
-        <v>1.074715353428356</v>
+        <v>1.085180582991527</v>
       </c>
       <c r="U12">
         <v>0.05180000000000001</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.8110461440559</v>
+        <v>10.73731467641445</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08744769612674447</v>
+        <v>0.08737001493038589</v>
       </c>
       <c r="C13">
-        <v>714.1541915029221</v>
+        <v>707.6053673752075</v>
       </c>
       <c r="D13">
-        <v>685.1753915029221</v>
+        <v>686.4557673752074</v>
       </c>
       <c r="E13">
-        <v>82.5012</v>
+        <v>90.33039999999998</v>
       </c>
       <c r="F13">
-        <v>86.1212</v>
+        <v>93.95039999999999</v>
       </c>
       <c r="G13">
         <v>115.1</v>
@@ -2478,28 +2478,28 @@
         <v>47.9</v>
       </c>
       <c r="M13">
-        <v>4.46107816</v>
+        <v>4.86663072</v>
       </c>
       <c r="N13">
-        <v>43.43892184</v>
+        <v>43.03336928</v>
       </c>
       <c r="O13">
-        <v>6.342082588639999</v>
+        <v>6.28287191488</v>
       </c>
       <c r="P13">
-        <v>37.09683925136</v>
+        <v>36.75049736512</v>
       </c>
       <c r="Q13">
-        <v>92.19683925136</v>
+        <v>91.85049736512001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0927883192435331</v>
+        <v>0.09325176242089306</v>
       </c>
       <c r="T13">
-        <v>1.085180582991527</v>
+        <v>1.095883658681133</v>
       </c>
       <c r="U13">
         <v>0.05180000000000001</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.73731467641445</v>
+        <v>9.84253845337992</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08737001493038589</v>
+        <v>0.08748106773402733</v>
       </c>
       <c r="C14">
-        <v>707.6053673752075</v>
+        <v>697.9472114082129</v>
       </c>
       <c r="D14">
-        <v>686.4557673752074</v>
+        <v>684.6268114082128</v>
       </c>
       <c r="E14">
-        <v>90.33039999999998</v>
+        <v>98.1596</v>
       </c>
       <c r="F14">
-        <v>93.95039999999999</v>
+        <v>101.7796</v>
       </c>
       <c r="G14">
         <v>115.1</v>
@@ -2560,45 +2560,45 @@
         <v>47.9</v>
       </c>
       <c r="M14">
-        <v>4.86663072</v>
+        <v>5.445208600000001</v>
       </c>
       <c r="N14">
-        <v>43.03336928</v>
+        <v>42.4547914</v>
       </c>
       <c r="O14">
-        <v>6.28287191488</v>
+        <v>6.198399544399999</v>
       </c>
       <c r="P14">
-        <v>36.75049736512</v>
+        <v>36.2563918556</v>
       </c>
       <c r="Q14">
-        <v>91.85049736512001</v>
+        <v>91.35639185560001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09325176242089306</v>
+        <v>0.09372585946439922</v>
       </c>
       <c r="T14">
-        <v>1.095883658681133</v>
+        <v>1.106832782087742</v>
       </c>
       <c r="U14">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V14">
         <v>0.146</v>
       </c>
       <c r="W14">
-        <v>0.0442372</v>
+        <v>0.04568900000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>9.84253845337992</v>
+        <v>8.796724518506048</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08748106773402733</v>
+        <v>0.08741790453766876</v>
       </c>
       <c r="C15">
-        <v>697.9472114082129</v>
+        <v>691.1570646282562</v>
       </c>
       <c r="D15">
-        <v>684.6268114082128</v>
+        <v>685.6658646282561</v>
       </c>
       <c r="E15">
-        <v>98.1596</v>
+        <v>105.9888</v>
       </c>
       <c r="F15">
-        <v>101.7796</v>
+        <v>109.6088</v>
       </c>
       <c r="G15">
         <v>115.1</v>
@@ -2642,28 +2642,28 @@
         <v>47.9</v>
       </c>
       <c r="M15">
-        <v>5.445208600000001</v>
+        <v>5.8640708</v>
       </c>
       <c r="N15">
-        <v>42.4547914</v>
+        <v>42.0359292</v>
       </c>
       <c r="O15">
-        <v>6.198399544399999</v>
+        <v>6.137245663199999</v>
       </c>
       <c r="P15">
-        <v>36.2563918556</v>
+        <v>35.8986835368</v>
       </c>
       <c r="Q15">
-        <v>91.35639185560001</v>
+        <v>90.9986835368</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09372585946439922</v>
+        <v>0.09421098202054506</v>
       </c>
       <c r="T15">
-        <v>1.106832782087742</v>
+        <v>1.118036536271249</v>
       </c>
       <c r="U15">
         <v>0.05350000000000001</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.796724518506048</v>
+        <v>8.168387052898474</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08741790453766876</v>
+        <v>0.0873547413413102</v>
       </c>
       <c r="C16">
-        <v>691.1570646282562</v>
+        <v>684.370076569564</v>
       </c>
       <c r="D16">
-        <v>685.6658646282561</v>
+        <v>686.708076569564</v>
       </c>
       <c r="E16">
-        <v>105.9888</v>
+        <v>113.818</v>
       </c>
       <c r="F16">
-        <v>109.6088</v>
+        <v>117.438</v>
       </c>
       <c r="G16">
         <v>115.1</v>
@@ -2724,28 +2724,28 @@
         <v>47.9</v>
       </c>
       <c r="M16">
-        <v>5.8640708</v>
+        <v>6.282933000000002</v>
       </c>
       <c r="N16">
-        <v>42.0359292</v>
+        <v>41.617067</v>
       </c>
       <c r="O16">
-        <v>6.137245663199999</v>
+        <v>6.076091782</v>
       </c>
       <c r="P16">
-        <v>35.8986835368</v>
+        <v>35.540975218</v>
       </c>
       <c r="Q16">
-        <v>90.9986835368</v>
+        <v>90.64097521799999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09421098202054506</v>
+        <v>0.09470751922507083</v>
       </c>
       <c r="T16">
-        <v>1.118036536271249</v>
+        <v>1.12950390820025</v>
       </c>
       <c r="U16">
         <v>0.05350000000000001</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.168387052898474</v>
+        <v>7.623827916038574</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08735474134131019</v>
+        <v>0.08740089014495163</v>
       </c>
       <c r="C17">
-        <v>684.3700765695644</v>
+        <v>675.779095846263</v>
       </c>
       <c r="D17">
-        <v>686.7080765695644</v>
+        <v>685.946295846263</v>
       </c>
       <c r="E17">
-        <v>113.818</v>
+        <v>121.6472</v>
       </c>
       <c r="F17">
-        <v>117.438</v>
+        <v>125.2672</v>
       </c>
       <c r="G17">
         <v>115.1</v>
@@ -2806,45 +2806,45 @@
         <v>47.9</v>
       </c>
       <c r="M17">
-        <v>6.282933</v>
+        <v>6.802008960000001</v>
       </c>
       <c r="N17">
-        <v>41.617067</v>
+        <v>41.09799104</v>
       </c>
       <c r="O17">
-        <v>6.076091782</v>
+        <v>6.000306691839999</v>
       </c>
       <c r="P17">
-        <v>35.540975218</v>
+        <v>35.09768434816</v>
       </c>
       <c r="Q17">
-        <v>90.64097521799999</v>
+        <v>90.19768434816001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09470751922507083</v>
+        <v>0.09521587874399004</v>
       </c>
       <c r="T17">
-        <v>1.12950390820025</v>
+        <v>1.141244312794227</v>
       </c>
       <c r="U17">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V17">
         <v>0.146</v>
       </c>
       <c r="W17">
-        <v>0.04568900000000001</v>
+        <v>0.04637220000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.623827916038576</v>
+        <v>7.042037180733145</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08740089014495163</v>
+        <v>0.08734455894859305</v>
       </c>
       <c r="C18">
-        <v>675.779095846263</v>
+        <v>668.8799857656328</v>
       </c>
       <c r="D18">
-        <v>685.946295846263</v>
+        <v>686.8763857656328</v>
       </c>
       <c r="E18">
-        <v>121.6472</v>
+        <v>129.4764</v>
       </c>
       <c r="F18">
-        <v>125.2672</v>
+        <v>133.0964</v>
       </c>
       <c r="G18">
         <v>115.1</v>
@@ -2888,28 +2888,28 @@
         <v>47.9</v>
       </c>
       <c r="M18">
-        <v>6.802008960000001</v>
+        <v>7.227134520000001</v>
       </c>
       <c r="N18">
-        <v>41.09799104</v>
+        <v>40.67286548</v>
       </c>
       <c r="O18">
-        <v>6.000306691839999</v>
+        <v>5.93823836008</v>
       </c>
       <c r="P18">
-        <v>35.09768434816</v>
+        <v>34.73462711992</v>
       </c>
       <c r="Q18">
-        <v>90.19768434816001</v>
+        <v>89.83462711992</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09521587874399004</v>
+        <v>0.09573648788987116</v>
       </c>
       <c r="T18">
-        <v>1.141244312794227</v>
+        <v>1.153267618703722</v>
       </c>
       <c r="U18">
         <v>0.05430000000000001</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.042037180733145</v>
+        <v>6.627799699513549</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08734455894859305</v>
+        <v>0.08728822775223449</v>
       </c>
       <c r="C19">
-        <v>668.8799857656328</v>
+        <v>661.9834013690684</v>
       </c>
       <c r="D19">
-        <v>686.8763857656328</v>
+        <v>687.8090013690684</v>
       </c>
       <c r="E19">
-        <v>129.4764</v>
+        <v>137.3056</v>
       </c>
       <c r="F19">
-        <v>133.0964</v>
+        <v>140.9256</v>
       </c>
       <c r="G19">
         <v>115.1</v>
@@ -2970,28 +2970,28 @@
         <v>47.9</v>
       </c>
       <c r="M19">
-        <v>7.227134520000001</v>
+        <v>7.652260080000001</v>
       </c>
       <c r="N19">
-        <v>40.67286548</v>
+        <v>40.24773992</v>
       </c>
       <c r="O19">
-        <v>5.93823836008</v>
+        <v>5.87617002832</v>
       </c>
       <c r="P19">
-        <v>34.73462711992</v>
+        <v>34.37156989168</v>
       </c>
       <c r="Q19">
-        <v>89.83462711992</v>
+        <v>89.47156989168001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09573648788987116</v>
+        <v>0.09626979481979817</v>
       </c>
       <c r="T19">
-        <v>1.153267618703722</v>
+        <v>1.165584175976863</v>
       </c>
       <c r="U19">
         <v>0.05430000000000001</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.627799699513549</v>
+        <v>6.25958860509613</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08728822775223449</v>
+        <v>0.08739415655587596</v>
       </c>
       <c r="C20">
-        <v>661.9834013690684</v>
+        <v>652.4025422255304</v>
       </c>
       <c r="D20">
-        <v>687.8090013690684</v>
+        <v>686.0573422255303</v>
       </c>
       <c r="E20">
-        <v>137.3056</v>
+        <v>145.1348</v>
       </c>
       <c r="F20">
-        <v>140.9256</v>
+        <v>148.7548</v>
       </c>
       <c r="G20">
         <v>115.1</v>
@@ -3052,45 +3052,45 @@
         <v>47.9</v>
       </c>
       <c r="M20">
-        <v>7.65226008</v>
+        <v>8.22614044</v>
       </c>
       <c r="N20">
-        <v>40.24773992</v>
+        <v>39.67385956</v>
       </c>
       <c r="O20">
-        <v>5.87617002832</v>
+        <v>5.792383495759999</v>
       </c>
       <c r="P20">
-        <v>34.37156989168</v>
+        <v>33.88147606424</v>
       </c>
       <c r="Q20">
-        <v>89.47156989168001</v>
+        <v>88.98147606424</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09626979481979817</v>
+        <v>0.09681626982206906</v>
       </c>
       <c r="T20">
-        <v>1.165584175976863</v>
+        <v>1.178204845775267</v>
       </c>
       <c r="U20">
-        <v>0.05430000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V20">
         <v>0.146</v>
       </c>
       <c r="W20">
-        <v>0.04637220000000001</v>
+        <v>0.04722620000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.25958860509613</v>
+        <v>5.822900830513902</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08739415655587596</v>
+        <v>0.08734636535951738</v>
       </c>
       <c r="C21">
-        <v>652.4025422255304</v>
+        <v>645.3625207943851</v>
       </c>
       <c r="D21">
-        <v>686.0573422255303</v>
+        <v>686.846520794385</v>
       </c>
       <c r="E21">
-        <v>145.1348</v>
+        <v>152.964</v>
       </c>
       <c r="F21">
-        <v>148.7548</v>
+        <v>156.584</v>
       </c>
       <c r="G21">
         <v>115.1</v>
@@ -3134,28 +3134,28 @@
         <v>47.9</v>
       </c>
       <c r="M21">
-        <v>8.22614044</v>
+        <v>8.659095200000001</v>
       </c>
       <c r="N21">
-        <v>39.67385956</v>
+        <v>39.2409048</v>
       </c>
       <c r="O21">
-        <v>5.792383495759999</v>
+        <v>5.729172100799999</v>
       </c>
       <c r="P21">
-        <v>33.88147606424</v>
+        <v>33.5117326992</v>
       </c>
       <c r="Q21">
-        <v>88.98147606424</v>
+        <v>88.61173269919999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09681626982206906</v>
+        <v>0.09737640669939671</v>
       </c>
       <c r="T21">
-        <v>1.178204845775267</v>
+        <v>1.191141032318631</v>
       </c>
       <c r="U21">
         <v>0.05530000000000001</v>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.822900830513902</v>
+        <v>5.531755788988207</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08734636535951738</v>
+        <v>0.08729857416315881</v>
       </c>
       <c r="C22">
-        <v>645.3625207943851</v>
+        <v>638.3243170540259</v>
       </c>
       <c r="D22">
-        <v>686.846520794385</v>
+        <v>687.6375170540259</v>
       </c>
       <c r="E22">
-        <v>152.964</v>
+        <v>160.7932</v>
       </c>
       <c r="F22">
-        <v>156.584</v>
+        <v>164.4132</v>
       </c>
       <c r="G22">
         <v>115.1</v>
@@ -3216,28 +3216,28 @@
         <v>47.9</v>
       </c>
       <c r="M22">
-        <v>8.659095200000001</v>
+        <v>9.092049960000002</v>
       </c>
       <c r="N22">
-        <v>39.2409048</v>
+        <v>38.80795003999999</v>
       </c>
       <c r="O22">
-        <v>5.729172100799999</v>
+        <v>5.665960705839999</v>
       </c>
       <c r="P22">
-        <v>33.5117326992</v>
+        <v>33.14198933415999</v>
       </c>
       <c r="Q22">
-        <v>88.61173269919999</v>
+        <v>88.24198933416</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09737640669939671</v>
+        <v>0.09795072425716303</v>
       </c>
       <c r="T22">
-        <v>1.191141032318631</v>
+        <v>1.204404717255497</v>
       </c>
       <c r="U22">
         <v>0.05530000000000001</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.531755788988207</v>
+        <v>5.268338846655434</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08729857416315881</v>
+        <v>0.08725078296680025</v>
       </c>
       <c r="C23">
-        <v>638.324317054026</v>
+        <v>631.2879372916403</v>
       </c>
       <c r="D23">
-        <v>687.6375170540259</v>
+        <v>688.4303372916403</v>
       </c>
       <c r="E23">
-        <v>160.7932</v>
+        <v>168.6224</v>
       </c>
       <c r="F23">
-        <v>164.4132</v>
+        <v>172.2424</v>
       </c>
       <c r="G23">
         <v>115.1</v>
@@ -3298,28 +3298,28 @@
         <v>47.9</v>
       </c>
       <c r="M23">
-        <v>9.092049960000001</v>
+        <v>9.525004720000002</v>
       </c>
       <c r="N23">
-        <v>38.80795003999999</v>
+        <v>38.37499527999999</v>
       </c>
       <c r="O23">
-        <v>5.665960705839999</v>
+        <v>5.602749310879998</v>
       </c>
       <c r="P23">
-        <v>33.14198933415999</v>
+        <v>32.77224596911999</v>
       </c>
       <c r="Q23">
-        <v>88.24198933416</v>
+        <v>87.87224596912</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09795072425716303</v>
+        <v>0.09853976790615415</v>
       </c>
       <c r="T23">
-        <v>1.204404717255497</v>
+        <v>1.218008496677925</v>
       </c>
       <c r="U23">
         <v>0.05530000000000001</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.268338846655435</v>
+        <v>5.028868899080187</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08725078296680025</v>
+        <v>0.08720299177044168</v>
       </c>
       <c r="C24">
-        <v>631.2879372916403</v>
+        <v>624.2533878234455</v>
       </c>
       <c r="D24">
-        <v>688.4303372916403</v>
+        <v>689.2249878234454</v>
       </c>
       <c r="E24">
-        <v>168.6224</v>
+        <v>176.4516</v>
       </c>
       <c r="F24">
-        <v>172.2424</v>
+        <v>180.0716</v>
       </c>
       <c r="G24">
         <v>115.1</v>
@@ -3380,28 +3380,28 @@
         <v>47.9</v>
       </c>
       <c r="M24">
-        <v>9.525004720000002</v>
+        <v>9.957959480000001</v>
       </c>
       <c r="N24">
-        <v>38.37499527999999</v>
+        <v>37.94204052</v>
       </c>
       <c r="O24">
-        <v>5.602749310879998</v>
+        <v>5.53953791592</v>
       </c>
       <c r="P24">
-        <v>32.77224596911999</v>
+        <v>32.40250260408</v>
       </c>
       <c r="Q24">
-        <v>87.87224596912</v>
+        <v>87.50250260408001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09853976790615415</v>
+        <v>0.09914411139018399</v>
       </c>
       <c r="T24">
-        <v>1.218008496677925</v>
+        <v>1.231965621020416</v>
       </c>
       <c r="U24">
         <v>0.05530000000000001</v>
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.028868899080187</v>
+        <v>4.810222425207137</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08720299177044168</v>
+        <v>0.0871552005740831</v>
       </c>
       <c r="C25">
-        <v>624.2533878234455</v>
+        <v>617.2206749948544</v>
       </c>
       <c r="D25">
-        <v>689.2249878234454</v>
+        <v>690.0214749948544</v>
       </c>
       <c r="E25">
-        <v>176.4516</v>
+        <v>184.2808</v>
       </c>
       <c r="F25">
-        <v>180.0716</v>
+        <v>187.9008</v>
       </c>
       <c r="G25">
         <v>115.1</v>
@@ -3462,28 +3462,28 @@
         <v>47.9</v>
       </c>
       <c r="M25">
-        <v>9.957959480000001</v>
+        <v>10.39091424</v>
       </c>
       <c r="N25">
-        <v>37.94204052</v>
+        <v>37.50908576</v>
       </c>
       <c r="O25">
-        <v>5.53953791592</v>
+        <v>5.476326520959999</v>
       </c>
       <c r="P25">
-        <v>32.40250260408</v>
+        <v>32.03275923904</v>
       </c>
       <c r="Q25">
-        <v>87.50250260408001</v>
+        <v>87.13275923904</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09914411139018399</v>
+        <v>0.09976435865010935</v>
       </c>
       <c r="T25">
-        <v>1.231965621020416</v>
+        <v>1.246290038108761</v>
       </c>
       <c r="U25">
         <v>0.05530000000000001</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.810222425207137</v>
+        <v>4.609796490823506</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0871552005740831</v>
+        <v>0.08764115937772454</v>
       </c>
       <c r="C26">
-        <v>617.2206749948544</v>
+        <v>601.3773086700579</v>
       </c>
       <c r="D26">
-        <v>690.0214749948544</v>
+        <v>682.0073086700579</v>
       </c>
       <c r="E26">
-        <v>184.2808</v>
+        <v>192.11</v>
       </c>
       <c r="F26">
-        <v>187.9008</v>
+        <v>195.73</v>
       </c>
       <c r="G26">
         <v>115.1</v>
@@ -3544,45 +3544,45 @@
         <v>47.9</v>
       </c>
       <c r="M26">
-        <v>10.39091424</v>
+        <v>11.313194</v>
       </c>
       <c r="N26">
-        <v>37.50908576</v>
+        <v>36.586806</v>
       </c>
       <c r="O26">
-        <v>5.476326520959999</v>
+        <v>5.341673675999999</v>
       </c>
       <c r="P26">
-        <v>32.03275923904</v>
+        <v>31.245132324</v>
       </c>
       <c r="Q26">
-        <v>87.13275923904</v>
+        <v>86.34513232399999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09976435865010935</v>
+        <v>0.100401145836966</v>
       </c>
       <c r="T26">
-        <v>1.246290038108761</v>
+        <v>1.260996439652796</v>
       </c>
       <c r="U26">
-        <v>0.05530000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.146</v>
       </c>
       <c r="W26">
-        <v>0.04722620000000001</v>
+        <v>0.0493612</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.609796490823506</v>
+        <v>4.233994396277478</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08764115937772454</v>
+        <v>0.08761471818136597</v>
       </c>
       <c r="C27">
-        <v>601.3773086700579</v>
+        <v>593.9793704350735</v>
       </c>
       <c r="D27">
-        <v>682.0073086700579</v>
+        <v>682.4385704350735</v>
       </c>
       <c r="E27">
-        <v>192.11</v>
+        <v>199.9392</v>
       </c>
       <c r="F27">
-        <v>195.73</v>
+        <v>203.5592</v>
       </c>
       <c r="G27">
         <v>115.1</v>
@@ -3626,28 +3626,28 @@
         <v>47.9</v>
       </c>
       <c r="M27">
-        <v>11.313194</v>
+        <v>11.76572176</v>
       </c>
       <c r="N27">
-        <v>36.586806</v>
+        <v>36.13427824</v>
       </c>
       <c r="O27">
-        <v>5.341673675999999</v>
+        <v>5.27560462304</v>
       </c>
       <c r="P27">
-        <v>31.245132324</v>
+        <v>30.85867361696</v>
       </c>
       <c r="Q27">
-        <v>86.34513232399999</v>
+        <v>85.95867361696</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.100401145836966</v>
+        <v>0.1010551434883324</v>
       </c>
       <c r="T27">
-        <v>1.260996439652796</v>
+        <v>1.276100311508831</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.233994396277478</v>
+        <v>4.071148457959114</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08761471818136597</v>
+        <v>0.08839530698500742</v>
       </c>
       <c r="C28">
-        <v>593.9793704350735</v>
+        <v>573.644006142322</v>
       </c>
       <c r="D28">
-        <v>682.4385704350735</v>
+        <v>669.932406142322</v>
       </c>
       <c r="E28">
-        <v>199.9392</v>
+        <v>207.7684</v>
       </c>
       <c r="F28">
-        <v>203.5592</v>
+        <v>211.3884</v>
       </c>
       <c r="G28">
         <v>115.1</v>
@@ -3708,45 +3708,45 @@
         <v>47.9</v>
       </c>
       <c r="M28">
-        <v>11.76572176</v>
+        <v>12.95810892</v>
       </c>
       <c r="N28">
-        <v>36.13427824</v>
+        <v>34.94189108</v>
       </c>
       <c r="O28">
-        <v>5.27560462304</v>
+        <v>5.101516097679999</v>
       </c>
       <c r="P28">
-        <v>30.85867361696</v>
+        <v>29.84037498232</v>
       </c>
       <c r="Q28">
-        <v>85.95867361696</v>
+        <v>84.94037498232001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1010551434883324</v>
+        <v>0.1017270588835718</v>
       </c>
       <c r="T28">
-        <v>1.276100311508831</v>
+        <v>1.291617988073252</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V28">
         <v>0.146</v>
       </c>
       <c r="W28">
-        <v>0.0493612</v>
+        <v>0.05235020000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.071148457959114</v>
+        <v>3.696527039224794</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08839530698500742</v>
+        <v>0.08839875578864885</v>
       </c>
       <c r="C29">
-        <v>573.644006142322</v>
+        <v>565.7605682830456</v>
       </c>
       <c r="D29">
-        <v>669.932406142322</v>
+        <v>669.8781682830455</v>
       </c>
       <c r="E29">
-        <v>207.7684</v>
+        <v>215.5976</v>
       </c>
       <c r="F29">
-        <v>211.3884</v>
+        <v>219.2176</v>
       </c>
       <c r="G29">
         <v>115.1</v>
@@ -3790,28 +3790,28 @@
         <v>47.9</v>
       </c>
       <c r="M29">
-        <v>12.95810892</v>
+        <v>13.43803888</v>
       </c>
       <c r="N29">
-        <v>34.94189108</v>
+        <v>34.46196112</v>
       </c>
       <c r="O29">
-        <v>5.101516097679999</v>
+        <v>5.031446323519999</v>
       </c>
       <c r="P29">
-        <v>29.84037498232</v>
+        <v>29.43051479648</v>
       </c>
       <c r="Q29">
-        <v>84.94037498232001</v>
+        <v>84.53051479647999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1017270588835718</v>
+        <v>0.1024176385953456</v>
       </c>
       <c r="T29">
-        <v>1.291617988073252</v>
+        <v>1.307566711208906</v>
       </c>
       <c r="U29">
         <v>0.06130000000000001</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.696527039224794</v>
+        <v>3.564508216395337</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08839875578864885</v>
+        <v>0.08909565259229027</v>
       </c>
       <c r="C30">
-        <v>565.7605682830456</v>
+        <v>547.1488548814862</v>
       </c>
       <c r="D30">
-        <v>669.8781682830455</v>
+        <v>659.0956548814862</v>
       </c>
       <c r="E30">
-        <v>215.5976</v>
+        <v>223.4268</v>
       </c>
       <c r="F30">
-        <v>219.2176</v>
+        <v>227.0468</v>
       </c>
       <c r="G30">
         <v>115.1</v>
@@ -3872,45 +3872,45 @@
         <v>47.9</v>
       </c>
       <c r="M30">
-        <v>13.43803888</v>
+        <v>14.55369988</v>
       </c>
       <c r="N30">
-        <v>34.46196112</v>
+        <v>33.34630012</v>
       </c>
       <c r="O30">
-        <v>5.031446323519999</v>
+        <v>4.868559817519999</v>
       </c>
       <c r="P30">
-        <v>29.43051479648</v>
+        <v>28.47774030248</v>
       </c>
       <c r="Q30">
-        <v>84.53051479647999</v>
+        <v>83.57774030248</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1024176385953456</v>
+        <v>0.1031276712567469</v>
       </c>
       <c r="T30">
-        <v>1.307566711208906</v>
+        <v>1.323964694151198</v>
       </c>
       <c r="U30">
-        <v>0.06130000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.05235020000000001</v>
+        <v>0.0547414</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.564508216395337</v>
+        <v>3.291259294540296</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08909565259229027</v>
+        <v>0.08912301339593171</v>
       </c>
       <c r="C31">
-        <v>547.1488548814863</v>
+        <v>538.9034006696814</v>
       </c>
       <c r="D31">
-        <v>659.0956548814862</v>
+        <v>658.6794006696814</v>
       </c>
       <c r="E31">
-        <v>223.4268</v>
+        <v>231.256</v>
       </c>
       <c r="F31">
-        <v>227.0468</v>
+        <v>234.876</v>
       </c>
       <c r="G31">
         <v>115.1</v>
@@ -3954,28 +3954,28 @@
         <v>47.9</v>
       </c>
       <c r="M31">
-        <v>14.55369988</v>
+        <v>15.0555516</v>
       </c>
       <c r="N31">
-        <v>33.34630012</v>
+        <v>32.8444484</v>
       </c>
       <c r="O31">
-        <v>4.86855981752</v>
+        <v>4.795289466399999</v>
       </c>
       <c r="P31">
-        <v>28.47774030248</v>
+        <v>28.0491589336</v>
       </c>
       <c r="Q31">
-        <v>83.57774030248001</v>
+        <v>83.14915893360001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1031276712567469</v>
+        <v>0.1038579905656167</v>
       </c>
       <c r="T31">
-        <v>1.323964694151198</v>
+        <v>1.340831190891842</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.291259294540297</v>
+        <v>3.181550651388954</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08912301339593171</v>
+        <v>0.08915037419957315</v>
       </c>
       <c r="C32">
-        <v>538.9034006696814</v>
+        <v>530.6584718996961</v>
       </c>
       <c r="D32">
-        <v>658.6794006696814</v>
+        <v>658.2636718996961</v>
       </c>
       <c r="E32">
-        <v>231.256</v>
+        <v>239.0852</v>
       </c>
       <c r="F32">
-        <v>234.876</v>
+        <v>242.7052</v>
       </c>
       <c r="G32">
         <v>115.1</v>
@@ -4036,28 +4036,28 @@
         <v>47.9</v>
       </c>
       <c r="M32">
-        <v>15.0555516</v>
+        <v>15.55740332</v>
       </c>
       <c r="N32">
-        <v>32.8444484</v>
+        <v>32.34259668</v>
       </c>
       <c r="O32">
-        <v>4.795289466399999</v>
+        <v>4.722019115279999</v>
       </c>
       <c r="P32">
-        <v>28.0491589336</v>
+        <v>27.62057756472</v>
       </c>
       <c r="Q32">
-        <v>83.14915893360001</v>
+        <v>82.72057756472</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1038579905656167</v>
+        <v>0.104609478550106</v>
       </c>
       <c r="T32">
-        <v>1.340831190891842</v>
+        <v>1.358186571595982</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.181550651388954</v>
+        <v>3.078919985215116</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08915037419957315</v>
+        <v>0.0913093190032146</v>
       </c>
       <c r="C33">
-        <v>530.6584718996961</v>
+        <v>491.6014933918833</v>
       </c>
       <c r="D33">
-        <v>658.2636718996961</v>
+        <v>627.0358933918833</v>
       </c>
       <c r="E33">
-        <v>239.0852</v>
+        <v>246.9144</v>
       </c>
       <c r="F33">
-        <v>242.7052</v>
+        <v>250.5344</v>
       </c>
       <c r="G33">
         <v>115.1</v>
@@ -4118,45 +4118,45 @@
         <v>47.9</v>
       </c>
       <c r="M33">
-        <v>15.55740332</v>
+        <v>18.01342336</v>
       </c>
       <c r="N33">
-        <v>32.34259668</v>
+        <v>29.88657664</v>
       </c>
       <c r="O33">
-        <v>4.722019115279999</v>
+        <v>4.363440189439999</v>
       </c>
       <c r="P33">
-        <v>27.62057756472</v>
+        <v>25.52313645056</v>
       </c>
       <c r="Q33">
-        <v>82.72057756472</v>
+        <v>80.62313645056</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.104609478550106</v>
+        <v>0.1053830691223744</v>
       </c>
       <c r="T33">
-        <v>1.358186571595982</v>
+        <v>1.376052404673774</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.146</v>
       </c>
       <c r="W33">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.078919985215116</v>
+        <v>2.659128087022321</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0913093190032146</v>
+        <v>0.09140329180685602</v>
       </c>
       <c r="C34">
-        <v>491.6014933918833</v>
+        <v>482.4801866480235</v>
       </c>
       <c r="D34">
-        <v>627.0358933918833</v>
+        <v>625.7437866480235</v>
       </c>
       <c r="E34">
-        <v>246.9144</v>
+        <v>254.7436</v>
       </c>
       <c r="F34">
-        <v>250.5344</v>
+        <v>258.3636</v>
       </c>
       <c r="G34">
         <v>115.1</v>
@@ -4200,28 +4200,28 @@
         <v>47.9</v>
       </c>
       <c r="M34">
-        <v>18.01342336</v>
+        <v>18.57634284</v>
       </c>
       <c r="N34">
-        <v>29.88657664</v>
+        <v>29.32365716</v>
       </c>
       <c r="O34">
-        <v>4.363440189439999</v>
+        <v>4.28125394536</v>
       </c>
       <c r="P34">
-        <v>25.52313645056</v>
+        <v>25.04240321464</v>
       </c>
       <c r="Q34">
-        <v>80.62313645056</v>
+        <v>80.14240321464</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1053830691223744</v>
+        <v>0.1061797519505314</v>
       </c>
       <c r="T34">
-        <v>1.376052404673774</v>
+        <v>1.394451546201648</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.659128087022321</v>
+        <v>2.578548448021645</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09140329180685602</v>
+        <v>0.09149726461049744</v>
       </c>
       <c r="C35">
-        <v>482.4801866480235</v>
+        <v>473.3641941344296</v>
       </c>
       <c r="D35">
-        <v>625.7437866480235</v>
+        <v>624.4569941344296</v>
       </c>
       <c r="E35">
-        <v>254.7436</v>
+        <v>262.5728</v>
       </c>
       <c r="F35">
-        <v>258.3636</v>
+        <v>266.1928</v>
       </c>
       <c r="G35">
         <v>115.1</v>
@@ -4282,28 +4282,28 @@
         <v>47.9</v>
       </c>
       <c r="M35">
-        <v>18.57634284</v>
+        <v>19.13926232</v>
       </c>
       <c r="N35">
-        <v>29.32365716</v>
+        <v>28.76073768</v>
       </c>
       <c r="O35">
-        <v>4.28125394536</v>
+        <v>4.19906770128</v>
       </c>
       <c r="P35">
-        <v>25.04240321464</v>
+        <v>24.56166997872</v>
       </c>
       <c r="Q35">
-        <v>80.14240321464</v>
+        <v>79.66166997872</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1061797519505314</v>
+        <v>0.1070005766825719</v>
       </c>
       <c r="T35">
-        <v>1.394451546201648</v>
+        <v>1.413408237472792</v>
       </c>
       <c r="U35">
         <v>0.07190000000000001</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.578548448021645</v>
+        <v>2.502708787785714</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09149726461049744</v>
+        <v>0.09275694741413888</v>
       </c>
       <c r="C36">
-        <v>473.3641941344296</v>
+        <v>448.7831015936484</v>
       </c>
       <c r="D36">
-        <v>624.4569941344296</v>
+        <v>607.7051015936484</v>
       </c>
       <c r="E36">
-        <v>262.5728</v>
+        <v>270.402</v>
       </c>
       <c r="F36">
-        <v>266.1928</v>
+        <v>274.022</v>
       </c>
       <c r="G36">
         <v>115.1</v>
@@ -4364,45 +4364,45 @@
         <v>47.9</v>
       </c>
       <c r="M36">
-        <v>19.13926232</v>
+        <v>20.7708676</v>
       </c>
       <c r="N36">
-        <v>28.76073768</v>
+        <v>27.1291324</v>
       </c>
       <c r="O36">
-        <v>4.19906770128</v>
+        <v>3.960853330399999</v>
       </c>
       <c r="P36">
-        <v>24.56166997872</v>
+        <v>23.1682790696</v>
       </c>
       <c r="Q36">
-        <v>79.66166997872</v>
+        <v>78.2682790696</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1070005766825719</v>
+        <v>0.1078466575602137</v>
       </c>
       <c r="T36">
-        <v>1.413408237472792</v>
+        <v>1.432948211552279</v>
       </c>
       <c r="U36">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V36">
         <v>0.146</v>
       </c>
       <c r="W36">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.502708787785714</v>
+        <v>2.30611455055445</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09275694741413888</v>
+        <v>0.09288422621778032</v>
       </c>
       <c r="C37">
-        <v>448.7831015936484</v>
+        <v>439.3111438271753</v>
       </c>
       <c r="D37">
-        <v>607.7051015936484</v>
+        <v>606.0623438271753</v>
       </c>
       <c r="E37">
-        <v>270.402</v>
+        <v>278.2312</v>
       </c>
       <c r="F37">
-        <v>274.022</v>
+        <v>281.8512</v>
       </c>
       <c r="G37">
         <v>115.1</v>
@@ -4446,28 +4446,28 @@
         <v>47.9</v>
       </c>
       <c r="M37">
-        <v>20.7708676</v>
+        <v>21.36432096</v>
       </c>
       <c r="N37">
-        <v>27.1291324</v>
+        <v>26.53567904</v>
       </c>
       <c r="O37">
-        <v>3.960853330399999</v>
+        <v>3.87420913984</v>
       </c>
       <c r="P37">
-        <v>23.1682790696</v>
+        <v>22.66146990016</v>
       </c>
       <c r="Q37">
-        <v>78.2682790696</v>
+        <v>77.76146990015999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1078466575602137</v>
+        <v>0.1087191784652818</v>
       </c>
       <c r="T37">
-        <v>1.432948211552279</v>
+        <v>1.453098809821749</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.30611455055445</v>
+        <v>2.242055813039049</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09288422621778034</v>
+        <v>0.09301150502142176</v>
       </c>
       <c r="C38">
-        <v>439.3111438271751</v>
+        <v>429.848043573001</v>
       </c>
       <c r="D38">
-        <v>606.062343827175</v>
+        <v>604.4284435730009</v>
       </c>
       <c r="E38">
-        <v>278.2311999999999</v>
+        <v>286.0604</v>
       </c>
       <c r="F38">
-        <v>281.8511999999999</v>
+        <v>289.6804</v>
       </c>
       <c r="G38">
         <v>115.1</v>
@@ -4528,28 +4528,28 @@
         <v>47.9</v>
       </c>
       <c r="M38">
-        <v>21.36432096</v>
+        <v>21.95777432</v>
       </c>
       <c r="N38">
-        <v>26.53567904</v>
+        <v>25.94222568</v>
       </c>
       <c r="O38">
-        <v>3.87420913984</v>
+        <v>3.78756494928</v>
       </c>
       <c r="P38">
-        <v>22.66146990016</v>
+        <v>22.15466073072</v>
       </c>
       <c r="Q38">
-        <v>77.76146990015999</v>
+        <v>77.25466073072</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1087191784652818</v>
+        <v>0.1096193984467012</v>
       </c>
       <c r="T38">
-        <v>1.453098809821749</v>
+        <v>1.473889109623584</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.24205581303905</v>
+        <v>2.18145970998394</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09301150502142176</v>
+        <v>0.09313878382506319</v>
       </c>
       <c r="C39">
-        <v>429.848043573001</v>
+        <v>420.3937293860985</v>
       </c>
       <c r="D39">
-        <v>604.4284435730009</v>
+        <v>602.8033293860984</v>
       </c>
       <c r="E39">
-        <v>286.0604</v>
+        <v>293.8896</v>
       </c>
       <c r="F39">
-        <v>289.6804</v>
+        <v>297.5096</v>
       </c>
       <c r="G39">
         <v>115.1</v>
@@ -4610,28 +4610,28 @@
         <v>47.9</v>
       </c>
       <c r="M39">
-        <v>21.95777432</v>
+        <v>22.55122768</v>
       </c>
       <c r="N39">
-        <v>25.94222568</v>
+        <v>25.34877232</v>
       </c>
       <c r="O39">
-        <v>3.78756494928</v>
+        <v>3.70092075872</v>
       </c>
       <c r="P39">
-        <v>22.15466073072</v>
+        <v>21.64785156128</v>
       </c>
       <c r="Q39">
-        <v>77.25466073072</v>
+        <v>76.74785156128</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1096193984467012</v>
+        <v>0.11054865778236</v>
       </c>
       <c r="T39">
-        <v>1.473889109623584</v>
+        <v>1.495350064257736</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.18145970998394</v>
+        <v>2.124052875510678</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09313878382506319</v>
+        <v>0.09326606262870464</v>
       </c>
       <c r="C40">
-        <v>420.3937293860985</v>
+        <v>410.9481305877505</v>
       </c>
       <c r="D40">
-        <v>602.8033293860984</v>
+        <v>601.1869305877505</v>
       </c>
       <c r="E40">
-        <v>293.8896</v>
+        <v>301.7188</v>
       </c>
       <c r="F40">
-        <v>297.5096</v>
+        <v>305.3388</v>
       </c>
       <c r="G40">
         <v>115.1</v>
@@ -4692,28 +4692,28 @@
         <v>47.9</v>
       </c>
       <c r="M40">
-        <v>22.55122768</v>
+        <v>23.14468104</v>
       </c>
       <c r="N40">
-        <v>25.34877232</v>
+        <v>24.75531896</v>
       </c>
       <c r="O40">
-        <v>3.70092075872</v>
+        <v>3.614276568159999</v>
       </c>
       <c r="P40">
-        <v>21.64785156128</v>
+        <v>21.14104239184</v>
       </c>
       <c r="Q40">
-        <v>76.74785156128</v>
+        <v>76.24104239184</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.11054865778236</v>
+        <v>0.1115083846372207</v>
       </c>
       <c r="T40">
-        <v>1.495350064257736</v>
+        <v>1.517514656748746</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.124052875510678</v>
+        <v>2.069589981266814</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09326606262870464</v>
+        <v>0.09339334143234605</v>
       </c>
       <c r="C41">
-        <v>410.9481305877505</v>
+        <v>401.5111772553053</v>
       </c>
       <c r="D41">
-        <v>601.1869305877505</v>
+        <v>599.5791772553052</v>
       </c>
       <c r="E41">
-        <v>301.7188</v>
+        <v>309.548</v>
       </c>
       <c r="F41">
-        <v>305.3388</v>
+        <v>313.168</v>
       </c>
       <c r="G41">
         <v>115.1</v>
@@ -4774,28 +4774,28 @@
         <v>47.9</v>
       </c>
       <c r="M41">
-        <v>23.14468104</v>
+        <v>23.7381344</v>
       </c>
       <c r="N41">
-        <v>24.75531896</v>
+        <v>24.1618656</v>
       </c>
       <c r="O41">
-        <v>3.614276568159999</v>
+        <v>3.527632377599999</v>
       </c>
       <c r="P41">
-        <v>21.14104239184</v>
+        <v>20.6342332224</v>
       </c>
       <c r="Q41">
-        <v>76.24104239184</v>
+        <v>75.73423322239999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1115083846372207</v>
+        <v>0.1125001023872434</v>
       </c>
       <c r="T41">
-        <v>1.517514656748746</v>
+        <v>1.540418068989456</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.069589981266814</v>
+        <v>2.017850231735144</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09339334143234605</v>
+        <v>0.09849260823598752</v>
       </c>
       <c r="C42">
-        <v>401.5111772553053</v>
+        <v>335.6583891831452</v>
       </c>
       <c r="D42">
-        <v>599.5791772553052</v>
+        <v>541.5555891831452</v>
       </c>
       <c r="E42">
-        <v>309.548</v>
+        <v>317.3772</v>
       </c>
       <c r="F42">
-        <v>313.168</v>
+        <v>320.9972</v>
       </c>
       <c r="G42">
         <v>115.1</v>
@@ -4856,45 +4856,45 @@
         <v>47.9</v>
       </c>
       <c r="M42">
-        <v>23.7381344</v>
+        <v>28.889748</v>
       </c>
       <c r="N42">
-        <v>24.1618656</v>
+        <v>19.01025199999999</v>
       </c>
       <c r="O42">
-        <v>3.527632377599999</v>
+        <v>2.775496791999999</v>
       </c>
       <c r="P42">
-        <v>20.6342332224</v>
+        <v>16.234755208</v>
       </c>
       <c r="Q42">
-        <v>75.73423322239999</v>
+        <v>71.33475520799999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1125001023872434</v>
+        <v>0.1135254376881144</v>
       </c>
       <c r="T42">
-        <v>1.540418068989456</v>
+        <v>1.564097868085783</v>
       </c>
       <c r="U42">
-        <v>0.07580000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V42">
         <v>0.146</v>
       </c>
       <c r="W42">
-        <v>0.0647332</v>
+        <v>0.07686000000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.017850231735144</v>
+        <v>1.658027615886438</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09849260823598752</v>
+        <v>0.09874115503962894</v>
       </c>
       <c r="C43">
-        <v>335.6583891831452</v>
+        <v>325.2867076187582</v>
       </c>
       <c r="D43">
-        <v>541.5555891831452</v>
+        <v>539.0131076187582</v>
       </c>
       <c r="E43">
-        <v>317.3772</v>
+        <v>325.2064</v>
       </c>
       <c r="F43">
-        <v>320.9972</v>
+        <v>328.8264</v>
       </c>
       <c r="G43">
         <v>115.1</v>
@@ -4938,28 +4938,28 @@
         <v>47.9</v>
       </c>
       <c r="M43">
-        <v>28.889748</v>
+        <v>29.59437600000001</v>
       </c>
       <c r="N43">
-        <v>19.01025199999999</v>
+        <v>18.30562399999999</v>
       </c>
       <c r="O43">
-        <v>2.775496791999999</v>
+        <v>2.672621103999998</v>
       </c>
       <c r="P43">
-        <v>16.234755208</v>
+        <v>15.63300289599999</v>
       </c>
       <c r="Q43">
-        <v>71.33475520799999</v>
+        <v>70.73300289599999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1135254376881144</v>
+        <v>0.1145861293786706</v>
       </c>
       <c r="T43">
-        <v>1.564097868085783</v>
+        <v>1.588594211978535</v>
       </c>
       <c r="U43">
         <v>0.09000000000000001</v>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.658027615886438</v>
+        <v>1.618550767889142</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09874115503962894</v>
+        <v>0.09898970184327037</v>
       </c>
       <c r="C44">
-        <v>325.2867076187583</v>
+        <v>314.9387872579215</v>
       </c>
       <c r="D44">
-        <v>539.0131076187582</v>
+        <v>536.4943872579215</v>
       </c>
       <c r="E44">
-        <v>325.2064</v>
+        <v>333.0356</v>
       </c>
       <c r="F44">
-        <v>328.8264</v>
+        <v>336.6556</v>
       </c>
       <c r="G44">
         <v>115.1</v>
@@ -5020,28 +5020,28 @@
         <v>47.9</v>
       </c>
       <c r="M44">
-        <v>29.594376</v>
+        <v>30.299004</v>
       </c>
       <c r="N44">
-        <v>18.305624</v>
+        <v>17.60099599999999</v>
       </c>
       <c r="O44">
-        <v>2.672621104</v>
+        <v>2.569745415999999</v>
       </c>
       <c r="P44">
-        <v>15.633002896</v>
+        <v>15.031250584</v>
       </c>
       <c r="Q44">
-        <v>70.733002896</v>
+        <v>70.131250584</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1145861293786706</v>
+        <v>0.1156840383215269</v>
       </c>
       <c r="T44">
-        <v>1.588594211978535</v>
+        <v>1.613950076709629</v>
       </c>
       <c r="U44">
         <v>0.09000000000000001</v>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.618550767889142</v>
+        <v>1.580910052356836</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09898970184327037</v>
+        <v>0.0992382486469118</v>
       </c>
       <c r="C45">
-        <v>314.9387872579215</v>
+        <v>304.6142965532133</v>
       </c>
       <c r="D45">
-        <v>536.4943872579215</v>
+        <v>533.9990965532132</v>
       </c>
       <c r="E45">
-        <v>333.0356</v>
+        <v>340.8648</v>
       </c>
       <c r="F45">
-        <v>336.6556</v>
+        <v>344.4848</v>
       </c>
       <c r="G45">
         <v>115.1</v>
@@ -5102,28 +5102,28 @@
         <v>47.9</v>
       </c>
       <c r="M45">
-        <v>30.299004</v>
+        <v>31.003632</v>
       </c>
       <c r="N45">
-        <v>17.60099599999999</v>
+        <v>16.896368</v>
       </c>
       <c r="O45">
-        <v>2.569745415999999</v>
+        <v>2.466869727999999</v>
       </c>
       <c r="P45">
-        <v>15.031250584</v>
+        <v>14.429498272</v>
       </c>
       <c r="Q45">
-        <v>70.131250584</v>
+        <v>69.529498272</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1156840383215269</v>
+        <v>0.1168211582980568</v>
       </c>
       <c r="T45">
-        <v>1.613950076709629</v>
+        <v>1.640211508038263</v>
       </c>
       <c r="U45">
         <v>0.09000000000000001</v>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.580910052356836</v>
+        <v>1.544980278439636</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0992382486469118</v>
+        <v>0.09948679545055325</v>
       </c>
       <c r="C46">
-        <v>304.6142965532133</v>
+        <v>294.3129100968999</v>
       </c>
       <c r="D46">
-        <v>533.9990965532132</v>
+        <v>531.5269100968999</v>
       </c>
       <c r="E46">
-        <v>340.8648</v>
+        <v>348.694</v>
       </c>
       <c r="F46">
-        <v>344.4848</v>
+        <v>352.314</v>
       </c>
       <c r="G46">
         <v>115.1</v>
@@ -5184,28 +5184,28 @@
         <v>47.9</v>
       </c>
       <c r="M46">
-        <v>31.003632</v>
+        <v>31.70826</v>
       </c>
       <c r="N46">
-        <v>16.896368</v>
+        <v>16.19174</v>
       </c>
       <c r="O46">
-        <v>2.466869727999999</v>
+        <v>2.36399404</v>
       </c>
       <c r="P46">
-        <v>14.429498272</v>
+        <v>13.82774596</v>
       </c>
       <c r="Q46">
-        <v>69.529498272</v>
+        <v>68.92774596</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1168211582980568</v>
+        <v>0.117999628091915</v>
       </c>
       <c r="T46">
-        <v>1.640211508038263</v>
+        <v>1.667427900506119</v>
       </c>
       <c r="U46">
         <v>0.09000000000000001</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.544980278439636</v>
+        <v>1.510647383363199</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09948679545055325</v>
+        <v>0.1232435663240598</v>
       </c>
       <c r="C47">
-        <v>294.3129100968999</v>
+        <v>123.4312628033931</v>
       </c>
       <c r="D47">
-        <v>531.5269100968999</v>
+        <v>368.4744628033931</v>
       </c>
       <c r="E47">
-        <v>348.694</v>
+        <v>356.5232</v>
       </c>
       <c r="F47">
-        <v>352.314</v>
+        <v>360.1432</v>
       </c>
       <c r="G47">
         <v>115.1</v>
@@ -5266,45 +5266,45 @@
         <v>47.9</v>
       </c>
       <c r="M47">
-        <v>31.70826</v>
+        <v>52.86902176</v>
       </c>
       <c r="N47">
-        <v>16.19174</v>
+        <v>-4.969021760000004</v>
       </c>
       <c r="O47">
-        <v>2.36399404</v>
+        <v>-0.7254771769600006</v>
       </c>
       <c r="P47">
-        <v>13.82774596</v>
+        <v>-4.243544583040004</v>
       </c>
       <c r="Q47">
-        <v>68.92774596</v>
+        <v>50.85645541696</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.117999628091915</v>
+        <v>0.1197185635220118</v>
       </c>
       <c r="T47">
-        <v>1.667427900506119</v>
+        <v>1.707126178337455</v>
       </c>
       <c r="U47">
-        <v>0.09000000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.146</v>
+        <v>0.132277839974923</v>
       </c>
       <c r="W47">
-        <v>0.07686000000000001</v>
+        <v>0.1273816130916813</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.510647383363199</v>
+        <v>0.9060126025679655</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1232435663240598</v>
+        <v>0.1242535663240598</v>
       </c>
       <c r="C48">
-        <v>123.4312628033931</v>
+        <v>110.858375232911</v>
       </c>
       <c r="D48">
-        <v>368.4744628033931</v>
+        <v>363.7307752329111</v>
       </c>
       <c r="E48">
-        <v>356.5232</v>
+        <v>364.3524</v>
       </c>
       <c r="F48">
-        <v>360.1432</v>
+        <v>367.9724</v>
       </c>
       <c r="G48">
         <v>115.1</v>
@@ -5348,37 +5348,37 @@
         <v>47.9</v>
       </c>
       <c r="M48">
-        <v>52.86902176</v>
+        <v>54.01834832</v>
       </c>
       <c r="N48">
-        <v>-4.969021760000004</v>
+        <v>-6.118348320000003</v>
       </c>
       <c r="O48">
-        <v>-0.7254771769600006</v>
+        <v>-0.8932788547200003</v>
       </c>
       <c r="P48">
-        <v>-4.243544583040004</v>
+        <v>-5.225069465280002</v>
       </c>
       <c r="Q48">
-        <v>50.85645541696</v>
+        <v>49.87493053472</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1197185635220118</v>
+        <v>0.1211132533997856</v>
       </c>
       <c r="T48">
-        <v>1.707126178337455</v>
+        <v>1.739336106230615</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.132277839974923</v>
+        <v>0.1294634178477969</v>
       </c>
       <c r="W48">
-        <v>0.1273816130916813</v>
+        <v>0.1277947702599434</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.9060126025679655</v>
+        <v>0.8867357386835406</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1242535663240598</v>
+        <v>0.1252635663240598</v>
       </c>
       <c r="C49">
-        <v>110.858375232911</v>
+        <v>98.40607435813922</v>
       </c>
       <c r="D49">
-        <v>363.7307752329111</v>
+        <v>359.1076743581393</v>
       </c>
       <c r="E49">
-        <v>364.3524</v>
+        <v>372.1816</v>
       </c>
       <c r="F49">
-        <v>367.9724</v>
+        <v>375.8016</v>
       </c>
       <c r="G49">
         <v>115.1</v>
@@ -5430,37 +5430,37 @@
         <v>47.9</v>
       </c>
       <c r="M49">
-        <v>54.01834832</v>
+        <v>55.16767488000001</v>
       </c>
       <c r="N49">
-        <v>-6.118348320000003</v>
+        <v>-7.267674880000008</v>
       </c>
       <c r="O49">
-        <v>-0.8932788547200003</v>
+        <v>-1.061080532480001</v>
       </c>
       <c r="P49">
-        <v>-5.225069465280002</v>
+        <v>-6.206594347520007</v>
       </c>
       <c r="Q49">
-        <v>49.87493053472</v>
+        <v>48.89340565247999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1211132533997856</v>
+        <v>0.1225615851959354</v>
       </c>
       <c r="T49">
-        <v>1.739336106230615</v>
+        <v>1.77278487750428</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1294634178477969</v>
+        <v>0.1267662633093012</v>
       </c>
       <c r="W49">
-        <v>0.1277947702599434</v>
+        <v>0.1281907125461946</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8867357386835406</v>
+        <v>0.8682620774609668</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1252635663240598</v>
+        <v>0.1262735663240598</v>
       </c>
       <c r="C50">
-        <v>98.40607435813951</v>
+        <v>86.06981983490419</v>
       </c>
       <c r="D50">
-        <v>359.1076743581394</v>
+        <v>354.6006198349042</v>
       </c>
       <c r="E50">
-        <v>372.1815999999999</v>
+        <v>380.0108</v>
       </c>
       <c r="F50">
-        <v>375.8016</v>
+        <v>383.6308</v>
       </c>
       <c r="G50">
         <v>115.1</v>
@@ -5512,37 +5512,37 @@
         <v>47.9</v>
       </c>
       <c r="M50">
-        <v>55.16767488</v>
+        <v>56.31700144</v>
       </c>
       <c r="N50">
-        <v>-7.267674880000001</v>
+        <v>-8.41700144</v>
       </c>
       <c r="O50">
-        <v>-1.06108053248</v>
+        <v>-1.22888221024</v>
       </c>
       <c r="P50">
-        <v>-6.206594347520001</v>
+        <v>-7.18811922976</v>
       </c>
       <c r="Q50">
-        <v>48.89340565248</v>
+        <v>47.91188077024</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1225615851959353</v>
+        <v>0.1240667143174242</v>
       </c>
       <c r="T50">
-        <v>1.77278487750428</v>
+        <v>1.807545365298482</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1267662633093012</v>
+        <v>0.1241791967111522</v>
       </c>
       <c r="W50">
-        <v>0.1281907125461946</v>
+        <v>0.1285704939228029</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.868262077460967</v>
+        <v>0.8505424432270696</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1262735663240598</v>
+        <v>0.1272835663240598</v>
       </c>
       <c r="C51">
-        <v>86.06981983490419</v>
+        <v>73.84529643179116</v>
       </c>
       <c r="D51">
-        <v>354.6006198349042</v>
+        <v>350.2052964317911</v>
       </c>
       <c r="E51">
-        <v>380.0108</v>
+        <v>387.84</v>
       </c>
       <c r="F51">
-        <v>383.6308</v>
+        <v>391.46</v>
       </c>
       <c r="G51">
         <v>115.1</v>
@@ -5594,37 +5594,37 @@
         <v>47.9</v>
       </c>
       <c r="M51">
-        <v>56.31700144</v>
+        <v>57.466328</v>
       </c>
       <c r="N51">
-        <v>-8.41700144</v>
+        <v>-9.566328000000006</v>
       </c>
       <c r="O51">
-        <v>-1.22888221024</v>
+        <v>-1.396683888000001</v>
       </c>
       <c r="P51">
-        <v>-7.18811922976</v>
+        <v>-8.169644112000006</v>
       </c>
       <c r="Q51">
-        <v>47.91188077024</v>
+        <v>46.93035588799999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1240667143174242</v>
+        <v>0.1256320486037728</v>
       </c>
       <c r="T51">
-        <v>1.807545365298482</v>
+        <v>1.843696272604451</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.1241791967111522</v>
+        <v>0.1216956127769291</v>
       </c>
       <c r="W51">
-        <v>0.1285704939228029</v>
+        <v>0.1289350840443468</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8505424432270696</v>
+        <v>0.8335315943625281</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1272835663240598</v>
+        <v>0.1282935663240598</v>
       </c>
       <c r="C52">
-        <v>73.84529643179116</v>
+        <v>61.72840024944122</v>
       </c>
       <c r="D52">
-        <v>350.2052964317911</v>
+        <v>345.9176002494412</v>
       </c>
       <c r="E52">
-        <v>387.84</v>
+        <v>395.6692</v>
       </c>
       <c r="F52">
-        <v>391.46</v>
+        <v>399.2892</v>
       </c>
       <c r="G52">
         <v>115.1</v>
@@ -5676,37 +5676,37 @@
         <v>47.9</v>
       </c>
       <c r="M52">
-        <v>57.466328</v>
+        <v>58.61565456</v>
       </c>
       <c r="N52">
-        <v>-9.566328000000006</v>
+        <v>-10.71565456</v>
       </c>
       <c r="O52">
-        <v>-1.396683888000001</v>
+        <v>-1.564485565760001</v>
       </c>
       <c r="P52">
-        <v>-8.169644112000006</v>
+        <v>-9.151168994240004</v>
       </c>
       <c r="Q52">
-        <v>46.93035588799999</v>
+        <v>45.94883100576</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1256320486037728</v>
+        <v>0.1272612740854824</v>
       </c>
       <c r="T52">
-        <v>1.843696272604451</v>
+        <v>1.8813227271474</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1216956127769291</v>
+        <v>0.119309424291107</v>
       </c>
       <c r="W52">
-        <v>0.1289350840443468</v>
+        <v>0.1292853765140655</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8335315943625281</v>
+        <v>0.8171878376103218</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1282935663240598</v>
+        <v>0.1293035663240598</v>
       </c>
       <c r="C53">
-        <v>61.72840024944122</v>
+        <v>49.71522593993581</v>
       </c>
       <c r="D53">
-        <v>345.9176002494412</v>
+        <v>341.7336259399358</v>
       </c>
       <c r="E53">
-        <v>395.6692</v>
+        <v>403.4984</v>
       </c>
       <c r="F53">
-        <v>399.2892</v>
+        <v>407.1184</v>
       </c>
       <c r="G53">
         <v>115.1</v>
@@ -5758,37 +5758,37 @@
         <v>47.9</v>
       </c>
       <c r="M53">
-        <v>58.61565456</v>
+        <v>59.76498112000001</v>
       </c>
       <c r="N53">
-        <v>-10.71565456</v>
+        <v>-11.86498112000001</v>
       </c>
       <c r="O53">
-        <v>-1.564485565760001</v>
+        <v>-1.732287243520001</v>
       </c>
       <c r="P53">
-        <v>-9.151168994240004</v>
+        <v>-10.13269387648001</v>
       </c>
       <c r="Q53">
-        <v>45.94883100576</v>
+        <v>44.96730612351999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1272612740854824</v>
+        <v>0.1289583839622633</v>
       </c>
       <c r="T53">
-        <v>1.8813227271474</v>
+        <v>1.920516950629637</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.119309424291107</v>
+        <v>0.1170150122855088</v>
       </c>
       <c r="W53">
-        <v>0.1292853765140655</v>
+        <v>0.1296221961964873</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8171878376103218</v>
+        <v>0.8014726868870463</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1293035663240598</v>
+        <v>0.1596290489394947</v>
       </c>
       <c r="C54">
-        <v>49.71522593993581</v>
+        <v>-49.15608702772664</v>
       </c>
       <c r="D54">
-        <v>341.7336259399358</v>
+        <v>250.6915129722734</v>
       </c>
       <c r="E54">
-        <v>403.4984</v>
+        <v>411.3276</v>
       </c>
       <c r="F54">
-        <v>407.1184</v>
+        <v>414.9476</v>
       </c>
       <c r="G54">
         <v>115.1</v>
@@ -5840,45 +5840,45 @@
         <v>47.9</v>
       </c>
       <c r="M54">
-        <v>59.76498112000001</v>
+        <v>83.32147808000001</v>
       </c>
       <c r="N54">
-        <v>-11.86498112000001</v>
+        <v>-35.42147808000001</v>
       </c>
       <c r="O54">
-        <v>-1.732287243520001</v>
+        <v>-5.171535799680001</v>
       </c>
       <c r="P54">
-        <v>-10.13269387648001</v>
+        <v>-30.24994228032001</v>
       </c>
       <c r="Q54">
-        <v>44.96730612351999</v>
+        <v>24.85005771968</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1289583839622633</v>
+        <v>0.1322074615262154</v>
       </c>
       <c r="T54">
-        <v>1.920516950629637</v>
+        <v>1.995553383977262</v>
       </c>
       <c r="U54">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1170150122855088</v>
+        <v>0.08393274052682285</v>
       </c>
       <c r="W54">
-        <v>0.1296221961964873</v>
+        <v>0.183946305702214</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.8014726868870463</v>
+        <v>0.5748817844302936</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1596290489394947</v>
+        <v>0.1611790489394947</v>
       </c>
       <c r="C55">
-        <v>-49.15608702772664</v>
+        <v>-60.35307215577689</v>
       </c>
       <c r="D55">
-        <v>250.6915129722734</v>
+        <v>247.3237278442231</v>
       </c>
       <c r="E55">
-        <v>411.3276</v>
+        <v>419.1568</v>
       </c>
       <c r="F55">
-        <v>414.9476</v>
+        <v>422.7768</v>
       </c>
       <c r="G55">
         <v>115.1</v>
@@ -5922,37 +5922,37 @@
         <v>47.9</v>
       </c>
       <c r="M55">
-        <v>83.32147808000001</v>
+        <v>84.89358144000001</v>
       </c>
       <c r="N55">
-        <v>-35.42147808000001</v>
+        <v>-36.99358144000001</v>
       </c>
       <c r="O55">
-        <v>-5.171535799680001</v>
+        <v>-5.40106289024</v>
       </c>
       <c r="P55">
-        <v>-30.24994228032001</v>
+        <v>-31.59251854976001</v>
       </c>
       <c r="Q55">
-        <v>24.85005771968</v>
+        <v>23.50748145023999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1322074615262154</v>
+        <v>0.1340858846028723</v>
       </c>
       <c r="T55">
-        <v>1.995553383977262</v>
+        <v>2.038934979281116</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.08393274052682285</v>
+        <v>0.08237843051706688</v>
       </c>
       <c r="W55">
-        <v>0.183946305702214</v>
+        <v>0.184258411152173</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5748817844302936</v>
+        <v>0.5642358254593622</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1611790489394947</v>
+        <v>0.1627290489394946</v>
       </c>
       <c r="C56">
-        <v>-60.35307215577689</v>
+        <v>-71.46077122538713</v>
       </c>
       <c r="D56">
-        <v>247.3237278442231</v>
+        <v>244.0452287746129</v>
       </c>
       <c r="E56">
-        <v>419.1568</v>
+        <v>426.986</v>
       </c>
       <c r="F56">
-        <v>422.7768</v>
+        <v>430.606</v>
       </c>
       <c r="G56">
         <v>115.1</v>
@@ -6004,37 +6004,37 @@
         <v>47.9</v>
       </c>
       <c r="M56">
-        <v>84.89358144000001</v>
+        <v>86.46568480000001</v>
       </c>
       <c r="N56">
-        <v>-36.99358144000001</v>
+        <v>-38.56568480000001</v>
       </c>
       <c r="O56">
-        <v>-5.40106289024</v>
+        <v>-5.630589980800001</v>
       </c>
       <c r="P56">
-        <v>-31.59251854976001</v>
+        <v>-32.9350948192</v>
       </c>
       <c r="Q56">
-        <v>23.50748145023999</v>
+        <v>22.1649051808</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1340858846028723</v>
+        <v>0.1360477931496028</v>
       </c>
       <c r="T56">
-        <v>2.038934979281116</v>
+        <v>2.084244645487363</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.08237843051706688</v>
+        <v>0.08088064087130203</v>
       </c>
       <c r="W56">
-        <v>0.184258411152173</v>
+        <v>0.1845591673130425</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5642358254593622</v>
+        <v>0.5539769922691921</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1627290489394946</v>
+        <v>0.1642790489394947</v>
       </c>
       <c r="C57">
-        <v>-71.46077122538713</v>
+        <v>-82.48268848625776</v>
       </c>
       <c r="D57">
-        <v>244.0452287746129</v>
+        <v>240.8525115137422</v>
       </c>
       <c r="E57">
-        <v>426.986</v>
+        <v>434.8152</v>
       </c>
       <c r="F57">
-        <v>430.606</v>
+        <v>438.4352</v>
       </c>
       <c r="G57">
         <v>115.1</v>
@@ -6086,37 +6086,37 @@
         <v>47.9</v>
       </c>
       <c r="M57">
-        <v>86.46568480000001</v>
+        <v>88.03778816000001</v>
       </c>
       <c r="N57">
-        <v>-38.56568480000001</v>
+        <v>-40.13778816000001</v>
       </c>
       <c r="O57">
-        <v>-5.630589980800001</v>
+        <v>-5.86011707136</v>
       </c>
       <c r="P57">
-        <v>-32.9350948192</v>
+        <v>-34.27767108864001</v>
       </c>
       <c r="Q57">
-        <v>22.1649051808</v>
+        <v>20.82232891136</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1360477931496028</v>
+        <v>0.1380988793575483</v>
       </c>
       <c r="T57">
-        <v>2.084244645487363</v>
+        <v>2.131613841975712</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.08088064087130203</v>
+        <v>0.07943634371288592</v>
       </c>
       <c r="W57">
-        <v>0.1845591673130425</v>
+        <v>0.1848491821824525</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5539769922691921</v>
+        <v>0.5440845459786707</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1642790489394947</v>
+        <v>0.1658290489394947</v>
       </c>
       <c r="C58">
-        <v>-82.48268848625776</v>
+        <v>-93.42214717900549</v>
       </c>
       <c r="D58">
-        <v>240.8525115137422</v>
+        <v>237.7422528209946</v>
       </c>
       <c r="E58">
-        <v>434.8152</v>
+        <v>442.6444</v>
       </c>
       <c r="F58">
-        <v>438.4352</v>
+        <v>446.2644</v>
       </c>
       <c r="G58">
         <v>115.1</v>
@@ -6168,37 +6168,37 @@
         <v>47.9</v>
       </c>
       <c r="M58">
-        <v>88.03778816000001</v>
+        <v>89.60989152000001</v>
       </c>
       <c r="N58">
-        <v>-40.13778816000001</v>
+        <v>-41.70989152000001</v>
       </c>
       <c r="O58">
-        <v>-5.86011707136</v>
+        <v>-6.089644161920001</v>
       </c>
       <c r="P58">
-        <v>-34.27767108864001</v>
+        <v>-35.62024735808001</v>
       </c>
       <c r="Q58">
-        <v>20.82232891136</v>
+        <v>19.47975264191999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1380988793575483</v>
+        <v>0.1402453649240029</v>
       </c>
       <c r="T58">
-        <v>2.131613841975712</v>
+        <v>2.181186256905379</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.07943634371288592</v>
+        <v>0.07804272364774759</v>
       </c>
       <c r="W58">
-        <v>0.1848491821824525</v>
+        <v>0.1851290210915323</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5440845459786707</v>
+        <v>0.5345392030667643</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1658290489394947</v>
+        <v>0.1673790489394947</v>
       </c>
       <c r="C59">
-        <v>-93.42214717900549</v>
+        <v>-104.2823010735036</v>
       </c>
       <c r="D59">
-        <v>237.7422528209946</v>
+        <v>234.7112989264964</v>
       </c>
       <c r="E59">
-        <v>442.6444</v>
+        <v>450.4736</v>
       </c>
       <c r="F59">
-        <v>446.2644</v>
+        <v>454.0936</v>
       </c>
       <c r="G59">
         <v>115.1</v>
@@ -6250,37 +6250,37 @@
         <v>47.9</v>
       </c>
       <c r="M59">
-        <v>89.60989152000001</v>
+        <v>91.18199488</v>
       </c>
       <c r="N59">
-        <v>-41.70989152000001</v>
+        <v>-43.28199488000001</v>
       </c>
       <c r="O59">
-        <v>-6.089644161920001</v>
+        <v>-6.31917125248</v>
       </c>
       <c r="P59">
-        <v>-35.62024735808001</v>
+        <v>-36.96282362752001</v>
       </c>
       <c r="Q59">
-        <v>19.47975264191999</v>
+        <v>18.13717637247999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1402453649240029</v>
+        <v>0.1424940640888601</v>
       </c>
       <c r="T59">
-        <v>2.181186256905379</v>
+        <v>2.233119263022175</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.07804272364774759</v>
+        <v>0.07669715944692435</v>
       </c>
       <c r="W59">
-        <v>0.1851290210915323</v>
+        <v>0.1853992103830576</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5345392030667643</v>
+        <v>0.5253230099104407</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1673790489394947</v>
+        <v>0.1689290489394947</v>
       </c>
       <c r="C60">
-        <v>-104.2823010735035</v>
+        <v>-115.0661451357251</v>
       </c>
       <c r="D60">
-        <v>234.7112989264965</v>
+        <v>231.7566548642749</v>
       </c>
       <c r="E60">
-        <v>450.4735999999999</v>
+        <v>458.3027999999999</v>
       </c>
       <c r="F60">
-        <v>454.0935999999999</v>
+        <v>461.9227999999999</v>
       </c>
       <c r="G60">
         <v>115.1</v>
@@ -6332,37 +6332,37 @@
         <v>47.9</v>
       </c>
       <c r="M60">
-        <v>91.18199487999999</v>
+        <v>92.75409823999999</v>
       </c>
       <c r="N60">
-        <v>-43.28199487999999</v>
+        <v>-44.85409823999999</v>
       </c>
       <c r="O60">
-        <v>-6.319171252479999</v>
+        <v>-6.548698343039998</v>
       </c>
       <c r="P60">
-        <v>-36.96282362752</v>
+        <v>-38.30539989696</v>
       </c>
       <c r="Q60">
-        <v>18.13717637248001</v>
+        <v>16.79460010304</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1424940640888601</v>
+        <v>0.1448524558959055</v>
       </c>
       <c r="T60">
-        <v>2.233119263022174</v>
+        <v>2.28758558651052</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.07669715944692435</v>
+        <v>0.07539720759189174</v>
       </c>
       <c r="W60">
-        <v>0.1853992103830576</v>
+        <v>0.1856602407155482</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5253230099104408</v>
+        <v>0.5164192300814503</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1689290489394947</v>
+        <v>0.1704790489394946</v>
       </c>
       <c r="C61">
-        <v>-115.0661451357251</v>
+        <v>-125.7765253989299</v>
       </c>
       <c r="D61">
-        <v>231.7566548642749</v>
+        <v>228.87547460107</v>
       </c>
       <c r="E61">
-        <v>458.3027999999999</v>
+        <v>466.1319999999999</v>
       </c>
       <c r="F61">
-        <v>461.9227999999999</v>
+        <v>469.752</v>
       </c>
       <c r="G61">
         <v>115.1</v>
@@ -6414,37 +6414,37 @@
         <v>47.9</v>
       </c>
       <c r="M61">
-        <v>92.75409823999999</v>
+        <v>94.32620159999999</v>
       </c>
       <c r="N61">
-        <v>-44.85409823999999</v>
+        <v>-46.42620159999999</v>
       </c>
       <c r="O61">
-        <v>-6.548698343039998</v>
+        <v>-6.778225433599999</v>
       </c>
       <c r="P61">
-        <v>-38.30539989696</v>
+        <v>-39.64797616639999</v>
       </c>
       <c r="Q61">
-        <v>16.79460010304</v>
+        <v>15.45202383360001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1448524558959055</v>
+        <v>0.1473287672933031</v>
       </c>
       <c r="T61">
-        <v>2.28758558651052</v>
+        <v>2.344775226173283</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.07539720759189174</v>
+        <v>0.0741405874653602</v>
       </c>
       <c r="W61">
-        <v>0.1856602407155482</v>
+        <v>0.1859125700369557</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5164192300814503</v>
+        <v>0.5078122429134262</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1704790489394946</v>
+        <v>0.1936596845753211</v>
       </c>
       <c r="C62">
-        <v>-125.7765253989299</v>
+        <v>-169.4875751265452</v>
       </c>
       <c r="D62">
-        <v>228.87547460107</v>
+        <v>192.9936248734548</v>
       </c>
       <c r="E62">
-        <v>466.1319999999999</v>
+        <v>473.9612</v>
       </c>
       <c r="F62">
-        <v>469.752</v>
+        <v>477.5812</v>
       </c>
       <c r="G62">
         <v>115.1</v>
@@ -6496,45 +6496,45 @@
         <v>47.9</v>
       </c>
       <c r="M62">
-        <v>94.32620159999999</v>
+        <v>112.61364696</v>
       </c>
       <c r="N62">
-        <v>-46.42620159999999</v>
+        <v>-64.71364696000001</v>
       </c>
       <c r="O62">
-        <v>-6.778225433599999</v>
+        <v>-9.448192456160001</v>
       </c>
       <c r="P62">
-        <v>-39.64797616639999</v>
+        <v>-55.26545450384</v>
       </c>
       <c r="Q62">
-        <v>15.45202383360001</v>
+        <v>-0.165454503840003</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1473287672933031</v>
+        <v>0.1506516475721734</v>
       </c>
       <c r="T62">
-        <v>2.344775226173283</v>
+        <v>2.421516110211857</v>
       </c>
       <c r="U62">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0741405874653602</v>
+        <v>0.06210082160365549</v>
       </c>
       <c r="W62">
-        <v>0.1859125700369557</v>
+        <v>0.2211566262658581</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.5078122429134262</v>
+        <v>0.4253480931757224</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1936596845753211</v>
+        <v>0.195559684575321</v>
       </c>
       <c r="C63">
-        <v>-169.4875751265452</v>
+        <v>-179.7652838042936</v>
       </c>
       <c r="D63">
-        <v>192.9936248734548</v>
+        <v>190.5451161957063</v>
       </c>
       <c r="E63">
-        <v>473.9612</v>
+        <v>481.7904</v>
       </c>
       <c r="F63">
-        <v>477.5812</v>
+        <v>485.4104</v>
       </c>
       <c r="G63">
         <v>115.1</v>
@@ -6578,37 +6578,37 @@
         <v>47.9</v>
       </c>
       <c r="M63">
-        <v>112.61364696</v>
+        <v>114.45977232</v>
       </c>
       <c r="N63">
-        <v>-64.71364696000001</v>
+        <v>-66.55977232000001</v>
       </c>
       <c r="O63">
-        <v>-9.448192456160001</v>
+        <v>-9.717726758720001</v>
       </c>
       <c r="P63">
-        <v>-55.26545450384</v>
+        <v>-56.84204556128</v>
       </c>
       <c r="Q63">
-        <v>-0.165454503840003</v>
+        <v>-1.742045561280001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1506516475721734</v>
+        <v>0.1534109014556517</v>
       </c>
       <c r="T63">
-        <v>2.421516110211857</v>
+        <v>2.485240218375327</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06210082160365549</v>
+        <v>0.06109919544875782</v>
       </c>
       <c r="W63">
-        <v>0.2211566262658581</v>
+        <v>0.2213928097131829</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4253480931757224</v>
+        <v>0.418487640059985</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.195559684575321</v>
+        <v>0.197459684575321</v>
       </c>
       <c r="C64">
-        <v>-179.7652838042936</v>
+        <v>-189.981642407357</v>
       </c>
       <c r="D64">
-        <v>190.5451161957063</v>
+        <v>188.157957592643</v>
       </c>
       <c r="E64">
-        <v>481.7904</v>
+        <v>489.6196</v>
       </c>
       <c r="F64">
-        <v>485.4104</v>
+        <v>493.2396</v>
       </c>
       <c r="G64">
         <v>115.1</v>
@@ -6660,37 +6660,37 @@
         <v>47.9</v>
       </c>
       <c r="M64">
-        <v>114.45977232</v>
+        <v>116.30589768</v>
       </c>
       <c r="N64">
-        <v>-66.55977232000001</v>
+        <v>-68.40589768000001</v>
       </c>
       <c r="O64">
-        <v>-9.717726758720001</v>
+        <v>-9.98726106128</v>
       </c>
       <c r="P64">
-        <v>-56.84204556128</v>
+        <v>-58.41863661872001</v>
       </c>
       <c r="Q64">
-        <v>-1.742045561280001</v>
+        <v>-3.318636618720006</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1534109014556517</v>
+        <v>0.1563193041976963</v>
       </c>
       <c r="T64">
-        <v>2.485240218375327</v>
+        <v>2.552408872926012</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06109919544875782</v>
+        <v>0.06012936694957118</v>
       </c>
       <c r="W64">
-        <v>0.2213928097131829</v>
+        <v>0.2216214952732911</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.418487640059985</v>
+        <v>0.4118449791066519</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.197459684575321</v>
+        <v>0.1993596845753211</v>
       </c>
       <c r="C65">
-        <v>-189.981642407357</v>
+        <v>-200.1389281963759</v>
       </c>
       <c r="D65">
-        <v>188.157957592643</v>
+        <v>185.8298718036241</v>
       </c>
       <c r="E65">
-        <v>489.6196</v>
+        <v>497.4488</v>
       </c>
       <c r="F65">
-        <v>493.2396</v>
+        <v>501.0688</v>
       </c>
       <c r="G65">
         <v>115.1</v>
@@ -6742,37 +6742,37 @@
         <v>47.9</v>
       </c>
       <c r="M65">
-        <v>116.30589768</v>
+        <v>118.15202304</v>
       </c>
       <c r="N65">
-        <v>-68.40589768000001</v>
+        <v>-70.25202304000001</v>
       </c>
       <c r="O65">
-        <v>-9.98726106128</v>
+        <v>-10.25679536384</v>
       </c>
       <c r="P65">
-        <v>-58.41863661872001</v>
+        <v>-59.99522767616001</v>
       </c>
       <c r="Q65">
-        <v>-3.318636618720006</v>
+        <v>-4.895227676160012</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1563193041976963</v>
+        <v>0.1593892848698545</v>
       </c>
       <c r="T65">
-        <v>2.552408872926012</v>
+        <v>2.623309119396179</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06012936694957118</v>
+        <v>0.05918984559098413</v>
       </c>
       <c r="W65">
-        <v>0.2216214952732911</v>
+        <v>0.221843034409646</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4118449791066519</v>
+        <v>0.4054099013081104</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1993596845753211</v>
+        <v>0.2012596845753211</v>
       </c>
       <c r="C66">
-        <v>-200.1389281963759</v>
+        <v>-210.2393071029291</v>
       </c>
       <c r="D66">
-        <v>185.8298718036241</v>
+        <v>183.5586928970709</v>
       </c>
       <c r="E66">
-        <v>497.4488</v>
+        <v>505.278</v>
       </c>
       <c r="F66">
-        <v>501.0688</v>
+        <v>508.898</v>
       </c>
       <c r="G66">
         <v>115.1</v>
@@ -6824,37 +6824,37 @@
         <v>47.9</v>
       </c>
       <c r="M66">
-        <v>118.15202304</v>
+        <v>119.9981484</v>
       </c>
       <c r="N66">
-        <v>-70.25202304000001</v>
+        <v>-72.09814839999999</v>
       </c>
       <c r="O66">
-        <v>-10.25679536384</v>
+        <v>-10.5263296664</v>
       </c>
       <c r="P66">
-        <v>-59.99522767616001</v>
+        <v>-61.57181873359999</v>
       </c>
       <c r="Q66">
-        <v>-4.895227676160012</v>
+        <v>-6.471818733599989</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1593892848698545</v>
+        <v>0.1626346930089932</v>
       </c>
       <c r="T66">
-        <v>2.623309119396179</v>
+        <v>2.698260808521784</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05918984559098413</v>
+        <v>0.05827923258189207</v>
       </c>
       <c r="W66">
-        <v>0.221843034409646</v>
+        <v>0.2220577569571899</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4054099013081104</v>
+        <v>0.3991728259033704</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2012596845753211</v>
+        <v>0.203159684575321</v>
       </c>
       <c r="C67">
-        <v>-210.2393071029291</v>
+        <v>-220.2848404506075</v>
       </c>
       <c r="D67">
-        <v>183.5586928970709</v>
+        <v>181.3423595493925</v>
       </c>
       <c r="E67">
-        <v>505.278</v>
+        <v>513.1072</v>
       </c>
       <c r="F67">
-        <v>508.898</v>
+        <v>516.7272</v>
       </c>
       <c r="G67">
         <v>115.1</v>
@@ -6906,37 +6906,37 @@
         <v>47.9</v>
       </c>
       <c r="M67">
-        <v>119.9981484</v>
+        <v>121.84427376</v>
       </c>
       <c r="N67">
-        <v>-72.09814839999999</v>
+        <v>-73.94427376000002</v>
       </c>
       <c r="O67">
-        <v>-10.5263296664</v>
+        <v>-10.79586396896</v>
       </c>
       <c r="P67">
-        <v>-61.57181873359999</v>
+        <v>-63.14840979104002</v>
       </c>
       <c r="Q67">
-        <v>-6.471818733599989</v>
+        <v>-8.048409791040015</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1626346930089932</v>
+        <v>0.1660710075092577</v>
       </c>
       <c r="T67">
-        <v>2.698260808521784</v>
+        <v>2.77762142053713</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05827923258189207</v>
+        <v>0.05739621390640885</v>
       </c>
       <c r="W67">
-        <v>0.2220577569571899</v>
+        <v>0.2222659727608688</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3991728259033704</v>
+        <v>0.3931247527836222</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.203159684575321</v>
+        <v>0.205059684575321</v>
       </c>
       <c r="C68">
-        <v>-220.2848404506075</v>
+        <v>-230.2774911949853</v>
       </c>
       <c r="D68">
-        <v>181.3423595493925</v>
+        <v>179.1789088050148</v>
       </c>
       <c r="E68">
-        <v>513.1072</v>
+        <v>520.9364</v>
       </c>
       <c r="F68">
-        <v>516.7272</v>
+        <v>524.5564000000001</v>
       </c>
       <c r="G68">
         <v>115.1</v>
@@ -6988,37 +6988,37 @@
         <v>47.9</v>
       </c>
       <c r="M68">
-        <v>121.84427376</v>
+        <v>123.69039912</v>
       </c>
       <c r="N68">
-        <v>-73.94427376000002</v>
+        <v>-75.79039912000002</v>
       </c>
       <c r="O68">
-        <v>-10.79586396896</v>
+        <v>-11.06539827152</v>
       </c>
       <c r="P68">
-        <v>-63.14840979104002</v>
+        <v>-64.72500084848002</v>
       </c>
       <c r="Q68">
-        <v>-8.048409791040015</v>
+        <v>-9.62500084848002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1660710075092577</v>
+        <v>0.1697155834943868</v>
       </c>
       <c r="T68">
-        <v>2.77762142053713</v>
+        <v>2.861791766614013</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05739621390640885</v>
+        <v>0.05653955399735796</v>
       </c>
       <c r="W68">
-        <v>0.2222659727608688</v>
+        <v>0.222467973167423</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3931247527836222</v>
+        <v>0.3872572191599861</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.205059684575321</v>
+        <v>0.206959684575321</v>
       </c>
       <c r="C69">
-        <v>-230.2774911949853</v>
+        <v>-240.2191297221927</v>
       </c>
       <c r="D69">
-        <v>179.1789088050148</v>
+        <v>177.0664702778072</v>
       </c>
       <c r="E69">
-        <v>520.9364</v>
+        <v>528.7655999999999</v>
       </c>
       <c r="F69">
-        <v>524.5564000000001</v>
+        <v>532.3856</v>
       </c>
       <c r="G69">
         <v>115.1</v>
@@ -7070,37 +7070,37 @@
         <v>47.9</v>
       </c>
       <c r="M69">
-        <v>123.69039912</v>
+        <v>125.53652448</v>
       </c>
       <c r="N69">
-        <v>-75.79039912000002</v>
+        <v>-77.63652447999999</v>
       </c>
       <c r="O69">
-        <v>-11.06539827152</v>
+        <v>-11.33493257408</v>
       </c>
       <c r="P69">
-        <v>-64.72500084848002</v>
+        <v>-66.30159190591999</v>
       </c>
       <c r="Q69">
-        <v>-9.62500084848002</v>
+        <v>-11.20159190591999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1697155834943868</v>
+        <v>0.1735879454785864</v>
       </c>
       <c r="T69">
-        <v>2.861791766614013</v>
+        <v>2.951222759320702</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05653955399735796</v>
+        <v>0.05570808996798506</v>
       </c>
       <c r="W69">
-        <v>0.222467973167423</v>
+        <v>0.2226640323855491</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3872572191599861</v>
+        <v>0.3815622600546923</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.206959684575321</v>
+        <v>0.2088596845753211</v>
       </c>
       <c r="C70">
-        <v>-240.2191297221927</v>
+        <v>-250.1115392420936</v>
       </c>
       <c r="D70">
-        <v>177.0664702778072</v>
+        <v>175.0032607579063</v>
       </c>
       <c r="E70">
-        <v>528.7655999999999</v>
+        <v>536.5948</v>
       </c>
       <c r="F70">
-        <v>532.3856</v>
+        <v>540.2148</v>
       </c>
       <c r="G70">
         <v>115.1</v>
@@ -7152,37 +7152,37 @@
         <v>47.9</v>
       </c>
       <c r="M70">
-        <v>125.53652448</v>
+        <v>127.38264984</v>
       </c>
       <c r="N70">
-        <v>-77.63652447999999</v>
+        <v>-79.48264983999999</v>
       </c>
       <c r="O70">
-        <v>-11.33493257408</v>
+        <v>-11.60446687664</v>
       </c>
       <c r="P70">
-        <v>-66.30159190591999</v>
+        <v>-67.87818296335999</v>
       </c>
       <c r="Q70">
-        <v>-11.20159190591999</v>
+        <v>-12.77818296335999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1735879454785864</v>
+        <v>0.1777101372682182</v>
       </c>
       <c r="T70">
-        <v>2.951222759320702</v>
+        <v>3.046423493492337</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05570808996798506</v>
+        <v>0.05490072634526064</v>
       </c>
       <c r="W70">
-        <v>0.2226640323855491</v>
+        <v>0.2228544087277876</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3815622600546923</v>
+        <v>0.3760323722278127</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2088596845753211</v>
+        <v>0.2107596845753211</v>
       </c>
       <c r="C71">
-        <v>-250.1115392420936</v>
+        <v>-259.9564208087506</v>
       </c>
       <c r="D71">
-        <v>175.0032607579063</v>
+        <v>172.9875791912494</v>
       </c>
       <c r="E71">
-        <v>536.5948</v>
+        <v>544.424</v>
       </c>
       <c r="F71">
-        <v>540.2148</v>
+        <v>548.044</v>
       </c>
       <c r="G71">
         <v>115.1</v>
@@ -7234,37 +7234,37 @@
         <v>47.9</v>
       </c>
       <c r="M71">
-        <v>127.38264984</v>
+        <v>129.2287752</v>
       </c>
       <c r="N71">
-        <v>-79.48264983999999</v>
+        <v>-81.3287752</v>
       </c>
       <c r="O71">
-        <v>-11.60446687664</v>
+        <v>-11.8740011792</v>
       </c>
       <c r="P71">
-        <v>-67.87818296335999</v>
+        <v>-69.4547740208</v>
       </c>
       <c r="Q71">
-        <v>-12.77818296335999</v>
+        <v>-14.3547740208</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1777101372682182</v>
+        <v>0.1821071418438255</v>
       </c>
       <c r="T71">
-        <v>3.046423493492337</v>
+        <v>3.147970943275415</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05490072634526064</v>
+        <v>0.05411643025461407</v>
       </c>
       <c r="W71">
-        <v>0.2228544087277876</v>
+        <v>0.223039345745962</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3760323722278127</v>
+        <v>0.3706604811959868</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2107596845753211</v>
+        <v>0.2126596845753211</v>
       </c>
       <c r="C72">
-        <v>-259.9564208087506</v>
+        <v>-269.7553979978895</v>
       </c>
       <c r="D72">
-        <v>172.9875791912494</v>
+        <v>171.0178020021105</v>
       </c>
       <c r="E72">
-        <v>544.424</v>
+        <v>552.2532</v>
       </c>
       <c r="F72">
-        <v>548.044</v>
+        <v>555.8732</v>
       </c>
       <c r="G72">
         <v>115.1</v>
@@ -7316,37 +7316,37 @@
         <v>47.9</v>
       </c>
       <c r="M72">
-        <v>129.2287752</v>
+        <v>131.07490056</v>
       </c>
       <c r="N72">
-        <v>-81.3287752</v>
+        <v>-83.17490056</v>
       </c>
       <c r="O72">
-        <v>-11.8740011792</v>
+        <v>-12.14353548176</v>
       </c>
       <c r="P72">
-        <v>-69.4547740208</v>
+        <v>-71.03136507824</v>
       </c>
       <c r="Q72">
-        <v>-14.3547740208</v>
+        <v>-15.93136507824</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1821071418438255</v>
+        <v>0.1868073881143023</v>
       </c>
       <c r="T72">
-        <v>3.147970943275415</v>
+        <v>3.256521665457327</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05411643025461407</v>
+        <v>0.05335422701159132</v>
       </c>
       <c r="W72">
-        <v>0.223039345745962</v>
+        <v>0.2232190732706668</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3706604811959868</v>
+        <v>0.3654399110382969</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2126596845753211</v>
+        <v>0.214559684575321</v>
       </c>
       <c r="C73">
-        <v>-269.7553979978895</v>
+        <v>-279.5100212683921</v>
       </c>
       <c r="D73">
-        <v>171.0178020021105</v>
+        <v>169.0923787316079</v>
       </c>
       <c r="E73">
-        <v>552.2532</v>
+        <v>560.0823999999999</v>
       </c>
       <c r="F73">
-        <v>555.8732</v>
+        <v>563.7023999999999</v>
       </c>
       <c r="G73">
         <v>115.1</v>
@@ -7398,37 +7398,37 @@
         <v>47.9</v>
       </c>
       <c r="M73">
-        <v>131.07490056</v>
+        <v>132.92102592</v>
       </c>
       <c r="N73">
-        <v>-83.17490056</v>
+        <v>-85.02102591999997</v>
       </c>
       <c r="O73">
-        <v>-12.14353548176</v>
+        <v>-12.41306978432</v>
       </c>
       <c r="P73">
-        <v>-71.03136507824</v>
+        <v>-72.60795613567997</v>
       </c>
       <c r="Q73">
-        <v>-15.93136507824</v>
+        <v>-17.50795613567997</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1868073881143022</v>
+        <v>0.1918433662612415</v>
       </c>
       <c r="T73">
-        <v>3.256521665457325</v>
+        <v>3.37282601065223</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05335422701159132</v>
+        <v>0.05261319608087479</v>
       </c>
       <c r="W73">
-        <v>0.2232190732706668</v>
+        <v>0.2233938083641297</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3654399110382969</v>
+        <v>0.3603643567183206</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.214559684575321</v>
+        <v>0.2164596845753211</v>
       </c>
       <c r="C74">
-        <v>-279.5100212683921</v>
+        <v>-289.2217720324436</v>
       </c>
       <c r="D74">
-        <v>169.0923787316079</v>
+        <v>167.2098279675564</v>
       </c>
       <c r="E74">
-        <v>560.0823999999999</v>
+        <v>567.9115999999999</v>
       </c>
       <c r="F74">
-        <v>563.7023999999999</v>
+        <v>571.5315999999999</v>
       </c>
       <c r="G74">
         <v>115.1</v>
@@ -7480,37 +7480,37 @@
         <v>47.9</v>
       </c>
       <c r="M74">
-        <v>132.92102592</v>
+        <v>134.76715128</v>
       </c>
       <c r="N74">
-        <v>-85.02102591999997</v>
+        <v>-86.86715127999997</v>
       </c>
       <c r="O74">
-        <v>-12.41306978432</v>
+        <v>-12.68260408688</v>
       </c>
       <c r="P74">
-        <v>-72.60795613567997</v>
+        <v>-74.18454719311998</v>
       </c>
       <c r="Q74">
-        <v>-17.50795613567997</v>
+        <v>-19.08454719311998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1918433662612415</v>
+        <v>0.1972523798264727</v>
       </c>
       <c r="T74">
-        <v>3.37282601065223</v>
+        <v>3.497745492528238</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05261319608087479</v>
+        <v>0.05189246736743815</v>
       </c>
       <c r="W74">
-        <v>0.2233938083641297</v>
+        <v>0.2235637561947581</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3603643567183206</v>
+        <v>0.3554278586810833</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2164596845753211</v>
+        <v>0.218359684575321</v>
       </c>
       <c r="C75">
-        <v>-289.2217720324436</v>
+        <v>-298.8920664567885</v>
       </c>
       <c r="D75">
-        <v>167.2098279675564</v>
+        <v>165.3687335432114</v>
       </c>
       <c r="E75">
-        <v>567.9115999999999</v>
+        <v>575.7407999999999</v>
       </c>
       <c r="F75">
-        <v>571.5315999999999</v>
+        <v>579.3607999999999</v>
       </c>
       <c r="G75">
         <v>115.1</v>
@@ -7562,37 +7562,37 @@
         <v>47.9</v>
       </c>
       <c r="M75">
-        <v>134.76715128</v>
+        <v>136.61327664</v>
       </c>
       <c r="N75">
-        <v>-86.86715127999997</v>
+        <v>-88.71327663999998</v>
       </c>
       <c r="O75">
-        <v>-12.68260408688</v>
+        <v>-12.95213838944</v>
       </c>
       <c r="P75">
-        <v>-74.18454719311998</v>
+        <v>-75.76113825055998</v>
       </c>
       <c r="Q75">
-        <v>-19.08454719311998</v>
+        <v>-20.66113825055998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1972523798264727</v>
+        <v>0.2030774713582601</v>
       </c>
       <c r="T75">
-        <v>3.497745492528238</v>
+        <v>3.632274165317785</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05189246736743815</v>
+        <v>0.05119121780841872</v>
       </c>
       <c r="W75">
-        <v>0.2235637561947581</v>
+        <v>0.2237291108407749</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3554278586810833</v>
+        <v>0.3506247795097173</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.218359684575321</v>
+        <v>0.220259684575321</v>
       </c>
       <c r="C76">
-        <v>-298.8920664567885</v>
+        <v>-308.5222590155963</v>
       </c>
       <c r="D76">
-        <v>165.3687335432114</v>
+        <v>163.5677409844036</v>
       </c>
       <c r="E76">
-        <v>575.7407999999999</v>
+        <v>583.5699999999999</v>
       </c>
       <c r="F76">
-        <v>579.3607999999999</v>
+        <v>587.1899999999999</v>
       </c>
       <c r="G76">
         <v>115.1</v>
@@ -7644,37 +7644,37 @@
         <v>47.9</v>
       </c>
       <c r="M76">
-        <v>136.61327664</v>
+        <v>138.459402</v>
       </c>
       <c r="N76">
-        <v>-88.71327663999998</v>
+        <v>-90.55940199999998</v>
       </c>
       <c r="O76">
-        <v>-12.95213838944</v>
+        <v>-13.221672692</v>
       </c>
       <c r="P76">
-        <v>-75.76113825055998</v>
+        <v>-77.33772930799998</v>
       </c>
       <c r="Q76">
-        <v>-20.66113825055998</v>
+        <v>-22.23772930799998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2030774713582601</v>
+        <v>0.2093685702125905</v>
       </c>
       <c r="T76">
-        <v>3.632274165317785</v>
+        <v>3.777565131930497</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05119121780841872</v>
+        <v>0.0505086682376398</v>
       </c>
       <c r="W76">
-        <v>0.2237291108407749</v>
+        <v>0.2238900560295645</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3506247795097173</v>
+        <v>0.3459497824495877</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.220259684575321</v>
+        <v>0.222159684575321</v>
       </c>
       <c r="C77">
-        <v>-308.5222590155963</v>
+        <v>-318.113645813666</v>
       </c>
       <c r="D77">
-        <v>163.5677409844036</v>
+        <v>161.8055541863339</v>
       </c>
       <c r="E77">
-        <v>583.5699999999999</v>
+        <v>591.3992</v>
       </c>
       <c r="F77">
-        <v>587.1899999999999</v>
+        <v>595.0192</v>
       </c>
       <c r="G77">
         <v>115.1</v>
@@ -7726,37 +7726,37 @@
         <v>47.9</v>
       </c>
       <c r="M77">
-        <v>138.459402</v>
+        <v>140.30552736</v>
       </c>
       <c r="N77">
-        <v>-90.55940199999998</v>
+        <v>-92.40552735999998</v>
       </c>
       <c r="O77">
-        <v>-13.221672692</v>
+        <v>-13.49120699456</v>
       </c>
       <c r="P77">
-        <v>-77.33772930799998</v>
+        <v>-78.91432036543998</v>
       </c>
       <c r="Q77">
-        <v>-22.23772930799998</v>
+        <v>-23.81432036543998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2093685702125905</v>
+        <v>0.2161839273047818</v>
       </c>
       <c r="T77">
-        <v>3.777565131930497</v>
+        <v>3.934963679094269</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0505086682376398</v>
+        <v>0.04984408049767085</v>
       </c>
       <c r="W77">
-        <v>0.2238900560295645</v>
+        <v>0.2240467658186492</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3459497824495877</v>
+        <v>0.3413978116278826</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.222159684575321</v>
+        <v>0.224059684575321</v>
       </c>
       <c r="C78">
-        <v>-318.113645813666</v>
+        <v>-327.6674676971078</v>
       </c>
       <c r="D78">
-        <v>161.8055541863339</v>
+        <v>160.0809323028921</v>
       </c>
       <c r="E78">
-        <v>591.3992</v>
+        <v>599.2284</v>
       </c>
       <c r="F78">
-        <v>595.0192</v>
+        <v>602.8484</v>
       </c>
       <c r="G78">
         <v>115.1</v>
@@ -7808,37 +7808,37 @@
         <v>47.9</v>
       </c>
       <c r="M78">
-        <v>140.30552736</v>
+        <v>142.15165272</v>
       </c>
       <c r="N78">
-        <v>-92.40552735999998</v>
+        <v>-94.25165271999998</v>
       </c>
       <c r="O78">
-        <v>-13.49120699456</v>
+        <v>-13.76074129712</v>
       </c>
       <c r="P78">
-        <v>-78.91432036543998</v>
+        <v>-80.49091142287999</v>
       </c>
       <c r="Q78">
-        <v>-23.81432036543998</v>
+        <v>-25.39091142287999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2161839273047818</v>
+        <v>0.2235919241441202</v>
       </c>
       <c r="T78">
-        <v>3.934963679094269</v>
+        <v>4.106049056446193</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04984408049767085</v>
+        <v>0.04919675477692188</v>
       </c>
       <c r="W78">
-        <v>0.2240467658186492</v>
+        <v>0.2241994052236018</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3413978116278826</v>
+        <v>0.3369640738145335</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.224059684575321</v>
+        <v>0.225959684575321</v>
       </c>
       <c r="C79">
-        <v>-327.6674676971078</v>
+        <v>-337.1849131671888</v>
       </c>
       <c r="D79">
-        <v>160.0809323028921</v>
+        <v>158.3926868328112</v>
       </c>
       <c r="E79">
-        <v>599.2284</v>
+        <v>607.0576</v>
       </c>
       <c r="F79">
-        <v>602.8484</v>
+        <v>610.6776</v>
       </c>
       <c r="G79">
         <v>115.1</v>
@@ -7890,37 +7890,37 @@
         <v>47.9</v>
       </c>
       <c r="M79">
-        <v>142.15165272</v>
+        <v>143.99777808</v>
       </c>
       <c r="N79">
-        <v>-94.25165271999998</v>
+        <v>-96.09777807999998</v>
       </c>
       <c r="O79">
-        <v>-13.76074129712</v>
+        <v>-14.03027559968</v>
       </c>
       <c r="P79">
-        <v>-80.49091142287999</v>
+        <v>-82.06750248031999</v>
       </c>
       <c r="Q79">
-        <v>-25.39091142287999</v>
+        <v>-26.96750248031999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2235919241441202</v>
+        <v>0.2316733752415802</v>
       </c>
       <c r="T79">
-        <v>4.106049056446193</v>
+        <v>4.29268764992102</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04919675477692188</v>
+        <v>0.04856602715157673</v>
       </c>
       <c r="W79">
-        <v>0.2241994052236018</v>
+        <v>0.2243481307976582</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3369640738145335</v>
+        <v>0.332644021586142</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.225959684575321</v>
+        <v>0.2278596845753211</v>
       </c>
       <c r="C80">
-        <v>-337.1849131671888</v>
+        <v>-346.6671211117227</v>
       </c>
       <c r="D80">
-        <v>158.3926868328112</v>
+        <v>156.7396788882773</v>
       </c>
       <c r="E80">
-        <v>607.0576</v>
+        <v>614.8868</v>
       </c>
       <c r="F80">
-        <v>610.6776</v>
+        <v>618.5068</v>
       </c>
       <c r="G80">
         <v>115.1</v>
@@ -7972,37 +7972,37 @@
         <v>47.9</v>
       </c>
       <c r="M80">
-        <v>143.99777808</v>
+        <v>145.84390344</v>
       </c>
       <c r="N80">
-        <v>-96.09777807999998</v>
+        <v>-97.94390344000001</v>
       </c>
       <c r="O80">
-        <v>-14.03027559968</v>
+        <v>-14.29980990224</v>
       </c>
       <c r="P80">
-        <v>-82.06750248031999</v>
+        <v>-83.64409353776001</v>
       </c>
       <c r="Q80">
-        <v>-26.96750248031999</v>
+        <v>-28.54409353776001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2316733752415802</v>
+        <v>0.2405244883483221</v>
       </c>
       <c r="T80">
-        <v>4.29268764992102</v>
+        <v>4.497101347536308</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04856602715157673</v>
+        <v>0.04795126731421498</v>
       </c>
       <c r="W80">
-        <v>0.2243481307976582</v>
+        <v>0.2244930911673081</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.332644021586142</v>
+        <v>0.3284333377685958</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2278596845753211</v>
+        <v>0.2297596845753211</v>
       </c>
       <c r="C81">
-        <v>-346.6671211117227</v>
+        <v>-356.1151833671959</v>
       </c>
       <c r="D81">
-        <v>156.7396788882773</v>
+        <v>155.1208166328042</v>
       </c>
       <c r="E81">
-        <v>614.8868</v>
+        <v>622.716</v>
       </c>
       <c r="F81">
-        <v>618.5068</v>
+        <v>626.336</v>
       </c>
       <c r="G81">
         <v>115.1</v>
@@ -8054,37 +8054,37 @@
         <v>47.9</v>
       </c>
       <c r="M81">
-        <v>145.84390344</v>
+        <v>147.6900288</v>
       </c>
       <c r="N81">
-        <v>-97.94390344000001</v>
+        <v>-99.79002880000002</v>
       </c>
       <c r="O81">
-        <v>-14.29980990224</v>
+        <v>-14.5693442048</v>
       </c>
       <c r="P81">
-        <v>-83.64409353776001</v>
+        <v>-85.22068459520001</v>
       </c>
       <c r="Q81">
-        <v>-28.54409353776001</v>
+        <v>-30.12068459520001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2405244883483221</v>
+        <v>0.2502607127657382</v>
       </c>
       <c r="T81">
-        <v>4.497101347536308</v>
+        <v>4.721956414913122</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04795126731421498</v>
+        <v>0.0473518764727873</v>
       </c>
       <c r="W81">
-        <v>0.2244930911673081</v>
+        <v>0.2246344275277168</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3284333377685958</v>
+        <v>0.3243279210464884</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2297596845753211</v>
+        <v>0.231659684575321</v>
       </c>
       <c r="C82">
-        <v>-356.1151833671959</v>
+        <v>-365.5301471237403</v>
       </c>
       <c r="D82">
-        <v>155.1208166328042</v>
+        <v>153.5350528762598</v>
       </c>
       <c r="E82">
-        <v>622.716</v>
+        <v>630.5452</v>
       </c>
       <c r="F82">
-        <v>626.336</v>
+        <v>634.1652</v>
       </c>
       <c r="G82">
         <v>115.1</v>
@@ -8136,37 +8136,37 @@
         <v>47.9</v>
       </c>
       <c r="M82">
-        <v>147.6900288</v>
+        <v>149.53615416</v>
       </c>
       <c r="N82">
-        <v>-99.79002880000002</v>
+        <v>-101.63615416</v>
       </c>
       <c r="O82">
-        <v>-14.5693442048</v>
+        <v>-14.83887850736</v>
       </c>
       <c r="P82">
-        <v>-85.22068459520001</v>
+        <v>-86.79727565264001</v>
       </c>
       <c r="Q82">
-        <v>-30.12068459520001</v>
+        <v>-31.69727565264001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2502607127657382</v>
+        <v>0.2610218029113034</v>
       </c>
       <c r="T82">
-        <v>4.721956414913122</v>
+        <v>4.970480436750656</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0473518764727873</v>
+        <v>0.04676728540522202</v>
       </c>
       <c r="W82">
-        <v>0.2246344275277168</v>
+        <v>0.2247722741014486</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3243279210464884</v>
+        <v>0.320323872638507</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.231659684575321</v>
+        <v>0.2335596845753211</v>
       </c>
       <c r="C83">
-        <v>-365.5301471237403</v>
+        <v>-374.9130171840875</v>
       </c>
       <c r="D83">
-        <v>153.5350528762598</v>
+        <v>151.9813828159126</v>
       </c>
       <c r="E83">
-        <v>630.5452</v>
+        <v>638.3744</v>
       </c>
       <c r="F83">
-        <v>634.1652</v>
+        <v>641.9944</v>
       </c>
       <c r="G83">
         <v>115.1</v>
@@ -8218,37 +8218,37 @@
         <v>47.9</v>
       </c>
       <c r="M83">
-        <v>149.53615416</v>
+        <v>151.38227952</v>
       </c>
       <c r="N83">
-        <v>-101.63615416</v>
+        <v>-103.48227952</v>
       </c>
       <c r="O83">
-        <v>-14.83887850736</v>
+        <v>-15.10841280992</v>
       </c>
       <c r="P83">
-        <v>-86.79727565264001</v>
+        <v>-88.37386671008002</v>
       </c>
       <c r="Q83">
-        <v>-31.69727565264001</v>
+        <v>-33.27386671008002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2610218029113034</v>
+        <v>0.2729785697397092</v>
       </c>
       <c r="T83">
-        <v>4.970480436750656</v>
+        <v>5.24661823879236</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04676728540522202</v>
+        <v>0.04619695265637785</v>
       </c>
       <c r="W83">
-        <v>0.2247722741014486</v>
+        <v>0.2249067585636261</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.320323872638507</v>
+        <v>0.3164174839477936</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2335596845753211</v>
+        <v>0.2354596845753211</v>
       </c>
       <c r="C84">
-        <v>-374.9130171840875</v>
+        <v>-384.2647580867406</v>
       </c>
       <c r="D84">
-        <v>151.9813828159126</v>
+        <v>150.4588419132594</v>
       </c>
       <c r="E84">
-        <v>638.3744</v>
+        <v>646.2036000000001</v>
       </c>
       <c r="F84">
-        <v>641.9944</v>
+        <v>649.8236000000001</v>
       </c>
       <c r="G84">
         <v>115.1</v>
@@ -8300,37 +8300,37 @@
         <v>47.9</v>
       </c>
       <c r="M84">
-        <v>151.38227952</v>
+        <v>153.22840488</v>
       </c>
       <c r="N84">
-        <v>-103.48227952</v>
+        <v>-105.32840488</v>
       </c>
       <c r="O84">
-        <v>-15.10841280992</v>
+        <v>-15.37794711248</v>
       </c>
       <c r="P84">
-        <v>-88.37386671008002</v>
+        <v>-89.95045776752002</v>
       </c>
       <c r="Q84">
-        <v>-33.27386671008002</v>
+        <v>-34.85045776752002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2729785697397092</v>
+        <v>0.2863420150185155</v>
       </c>
       <c r="T84">
-        <v>5.24661823879236</v>
+        <v>5.555242841074262</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04619695265637785</v>
+        <v>0.04564036286533715</v>
       </c>
       <c r="W84">
-        <v>0.2249067585636261</v>
+        <v>0.2250380024363535</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3164174839477936</v>
+        <v>0.3126052251050491</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2354596845753211</v>
+        <v>0.2373596845753211</v>
       </c>
       <c r="C85">
-        <v>-384.2647580867406</v>
+        <v>-393.5862961027954</v>
       </c>
       <c r="D85">
-        <v>150.4588419132594</v>
+        <v>148.9665038972047</v>
       </c>
       <c r="E85">
-        <v>646.2036000000001</v>
+        <v>654.0328000000001</v>
       </c>
       <c r="F85">
-        <v>649.8236000000001</v>
+        <v>657.6528000000001</v>
       </c>
       <c r="G85">
         <v>115.1</v>
@@ -8382,37 +8382,37 @@
         <v>47.9</v>
       </c>
       <c r="M85">
-        <v>153.22840488</v>
+        <v>155.07453024</v>
       </c>
       <c r="N85">
-        <v>-105.32840488</v>
+        <v>-107.17453024</v>
       </c>
       <c r="O85">
-        <v>-15.37794711248</v>
+        <v>-15.64748141504</v>
       </c>
       <c r="P85">
-        <v>-89.95045776752002</v>
+        <v>-91.52704882496002</v>
       </c>
       <c r="Q85">
-        <v>-34.85045776752002</v>
+        <v>-36.42704882496002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2863420150185155</v>
+        <v>0.3013758909571729</v>
       </c>
       <c r="T85">
-        <v>5.555242841074262</v>
+        <v>5.902445518641406</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04564036286533715</v>
+        <v>0.04509702521217838</v>
       </c>
       <c r="W85">
-        <v>0.2250380024363535</v>
+        <v>0.2251661214549683</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3126052251050491</v>
+        <v>0.3088837343299889</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.237359684575321</v>
+        <v>0.239259684575321</v>
       </c>
       <c r="C86">
-        <v>-393.5862961027952</v>
+        <v>-402.8785211150918</v>
       </c>
       <c r="D86">
-        <v>148.9665038972047</v>
+        <v>147.5034788849082</v>
       </c>
       <c r="E86">
-        <v>654.0328</v>
+        <v>661.862</v>
       </c>
       <c r="F86">
-        <v>657.6528</v>
+        <v>665.482</v>
       </c>
       <c r="G86">
         <v>115.1</v>
@@ -8464,37 +8464,37 @@
         <v>47.9</v>
       </c>
       <c r="M86">
-        <v>155.07453024</v>
+        <v>156.9206556</v>
       </c>
       <c r="N86">
-        <v>-107.17453024</v>
+        <v>-109.0206556</v>
       </c>
       <c r="O86">
-        <v>-15.64748141504</v>
+        <v>-15.9170157176</v>
       </c>
       <c r="P86">
-        <v>-91.52704882495999</v>
+        <v>-93.1036398824</v>
       </c>
       <c r="Q86">
-        <v>-36.42704882495999</v>
+        <v>-38.0036398824</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3013758909571727</v>
+        <v>0.3184142836876508</v>
       </c>
       <c r="T86">
-        <v>5.902445518641402</v>
+        <v>6.295941886550828</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04509702521217838</v>
+        <v>0.04456647197438805</v>
       </c>
       <c r="W86">
-        <v>0.2251661214549683</v>
+        <v>0.2252912259084393</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3088837343299889</v>
+        <v>0.3052498080437538</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.239259684575321</v>
+        <v>0.2411596845753211</v>
       </c>
       <c r="C87">
-        <v>-402.8785211150918</v>
+        <v>-412.1422883877128</v>
       </c>
       <c r="D87">
-        <v>147.5034788849082</v>
+        <v>146.0689116122872</v>
       </c>
       <c r="E87">
-        <v>661.862</v>
+        <v>669.6912</v>
       </c>
       <c r="F87">
-        <v>665.482</v>
+        <v>673.3112</v>
       </c>
       <c r="G87">
         <v>115.1</v>
@@ -8546,37 +8546,37 @@
         <v>47.9</v>
       </c>
       <c r="M87">
-        <v>156.9206556</v>
+        <v>158.76678096</v>
       </c>
       <c r="N87">
-        <v>-109.0206556</v>
+        <v>-110.86678096</v>
       </c>
       <c r="O87">
-        <v>-15.9170157176</v>
+        <v>-16.18655002016</v>
       </c>
       <c r="P87">
-        <v>-93.1036398824</v>
+        <v>-94.68023093984</v>
       </c>
       <c r="Q87">
-        <v>-38.0036398824</v>
+        <v>-39.58023093984</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3184142836876508</v>
+        <v>0.3378867325224831</v>
       </c>
       <c r="T87">
-        <v>6.295941886550828</v>
+        <v>6.745652021304459</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04456647197438805</v>
+        <v>0.04404825718398819</v>
       </c>
       <c r="W87">
-        <v>0.2252912259084393</v>
+        <v>0.2254134209560156</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3052498080437538</v>
+        <v>0.301700391671152</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2411596845753211</v>
+        <v>0.243059684575321</v>
       </c>
       <c r="C88">
-        <v>-412.1422883877128</v>
+        <v>-421.3784202332181</v>
       </c>
       <c r="D88">
-        <v>146.0689116122872</v>
+        <v>144.6619797667819</v>
       </c>
       <c r="E88">
-        <v>669.6912</v>
+        <v>677.5204</v>
       </c>
       <c r="F88">
-        <v>673.3112</v>
+        <v>681.1404</v>
       </c>
       <c r="G88">
         <v>115.1</v>
@@ -8628,37 +8628,37 @@
         <v>47.9</v>
       </c>
       <c r="M88">
-        <v>158.76678096</v>
+        <v>160.61290632</v>
       </c>
       <c r="N88">
-        <v>-110.86678096</v>
+        <v>-112.71290632</v>
       </c>
       <c r="O88">
-        <v>-16.18655002016</v>
+        <v>-16.45608432272</v>
       </c>
       <c r="P88">
-        <v>-94.68023093984</v>
+        <v>-96.25682199728</v>
       </c>
       <c r="Q88">
-        <v>-39.58023093984</v>
+        <v>-41.15682199728</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3378867325224831</v>
+        <v>0.3603549427165202</v>
       </c>
       <c r="T88">
-        <v>6.745652021304459</v>
+        <v>7.264548330635572</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04404825718398819</v>
+        <v>0.04354195537727568</v>
       </c>
       <c r="W88">
-        <v>0.2254134209560156</v>
+        <v>0.2255328069220384</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.301700391671152</v>
+        <v>0.2982325710772308</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.243059684575321</v>
+        <v>0.2449596845753211</v>
       </c>
       <c r="C89">
-        <v>-421.3784202332181</v>
+        <v>-430.5877075844458</v>
       </c>
       <c r="D89">
-        <v>144.6619797667819</v>
+        <v>143.2818924155542</v>
       </c>
       <c r="E89">
-        <v>677.5204</v>
+        <v>685.3496</v>
       </c>
       <c r="F89">
-        <v>681.1404</v>
+        <v>688.9696</v>
       </c>
       <c r="G89">
         <v>115.1</v>
@@ -8710,37 +8710,37 @@
         <v>47.9</v>
       </c>
       <c r="M89">
-        <v>160.61290632</v>
+        <v>162.45903168</v>
       </c>
       <c r="N89">
-        <v>-112.71290632</v>
+        <v>-114.55903168</v>
       </c>
       <c r="O89">
-        <v>-16.45608432272</v>
+        <v>-16.72561862528</v>
       </c>
       <c r="P89">
-        <v>-96.25682199728</v>
+        <v>-97.83341305472001</v>
       </c>
       <c r="Q89">
-        <v>-41.15682199728</v>
+        <v>-42.73341305472001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3603549427165202</v>
+        <v>0.3865678546095637</v>
       </c>
       <c r="T89">
-        <v>7.264548330635572</v>
+        <v>7.869927358188537</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04354195537727568</v>
+        <v>0.04304716042980664</v>
       </c>
       <c r="W89">
-        <v>0.2255328069220384</v>
+        <v>0.2256494795706516</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2982325710772308</v>
+        <v>0.2948435645877168</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2449596845753211</v>
+        <v>0.246859684575321</v>
       </c>
       <c r="C90">
-        <v>-430.5877075844458</v>
+        <v>-439.7709114771932</v>
       </c>
       <c r="D90">
-        <v>143.2818924155542</v>
+        <v>141.9278885228068</v>
       </c>
       <c r="E90">
-        <v>685.3496</v>
+        <v>693.1788</v>
       </c>
       <c r="F90">
-        <v>688.9696</v>
+        <v>696.7988</v>
       </c>
       <c r="G90">
         <v>115.1</v>
@@ -8792,37 +8792,37 @@
         <v>47.9</v>
       </c>
       <c r="M90">
-        <v>162.45903168</v>
+        <v>164.30515704</v>
       </c>
       <c r="N90">
-        <v>-114.55903168</v>
+        <v>-116.40515704</v>
       </c>
       <c r="O90">
-        <v>-16.72561862528</v>
+        <v>-16.99515292784</v>
       </c>
       <c r="P90">
-        <v>-97.83341305472001</v>
+        <v>-99.41000411216001</v>
       </c>
       <c r="Q90">
-        <v>-42.73341305472001</v>
+        <v>-44.31000411216001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3865678546095637</v>
+        <v>0.4175467504831603</v>
       </c>
       <c r="T90">
-        <v>7.869927358188537</v>
+        <v>8.58537529984204</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04304716042980664</v>
+        <v>0.04256348446992117</v>
       </c>
       <c r="W90">
-        <v>0.2256494795706516</v>
+        <v>0.2257635303619926</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2948435645877168</v>
+        <v>0.2915307155474053</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.246859684575321</v>
+        <v>0.248759684575321</v>
       </c>
       <c r="C91">
-        <v>-439.7709114771932</v>
+        <v>-448.9287644496176</v>
       </c>
       <c r="D91">
-        <v>141.9278885228068</v>
+        <v>140.5992355503824</v>
       </c>
       <c r="E91">
-        <v>693.1788</v>
+        <v>701.0079999999999</v>
       </c>
       <c r="F91">
-        <v>696.7988</v>
+        <v>704.6279999999999</v>
       </c>
       <c r="G91">
         <v>115.1</v>
@@ -8874,37 +8874,37 @@
         <v>47.9</v>
       </c>
       <c r="M91">
-        <v>164.30515704</v>
+        <v>166.1512824</v>
       </c>
       <c r="N91">
-        <v>-116.40515704</v>
+        <v>-118.2512824</v>
       </c>
       <c r="O91">
-        <v>-16.99515292784</v>
+        <v>-17.2646872304</v>
       </c>
       <c r="P91">
-        <v>-99.41000411216001</v>
+        <v>-100.9865951696</v>
       </c>
       <c r="Q91">
-        <v>-44.31000411216001</v>
+        <v>-45.88659516959998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4175467504831603</v>
+        <v>0.4547214255314764</v>
       </c>
       <c r="T91">
-        <v>8.58537529984204</v>
+        <v>9.443912829826244</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04256348446992117</v>
+        <v>0.04209055686469983</v>
       </c>
       <c r="W91">
-        <v>0.2257635303619926</v>
+        <v>0.2258750466913038</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2915307155474053</v>
+        <v>0.2882914853746564</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.248759684575321</v>
+        <v>0.2506596845753211</v>
       </c>
       <c r="C92">
-        <v>-448.9287644496176</v>
+        <v>-458.0619718637631</v>
       </c>
       <c r="D92">
-        <v>140.5992355503824</v>
+        <v>139.2952281362368</v>
       </c>
       <c r="E92">
-        <v>701.0079999999999</v>
+        <v>708.8371999999999</v>
       </c>
       <c r="F92">
-        <v>704.6279999999999</v>
+        <v>712.4571999999999</v>
       </c>
       <c r="G92">
         <v>115.1</v>
@@ -8956,37 +8956,37 @@
         <v>47.9</v>
       </c>
       <c r="M92">
-        <v>166.1512824</v>
+        <v>167.99740776</v>
       </c>
       <c r="N92">
-        <v>-118.2512824</v>
+        <v>-120.09740776</v>
       </c>
       <c r="O92">
-        <v>-17.2646872304</v>
+        <v>-17.53422153296</v>
       </c>
       <c r="P92">
-        <v>-100.9865951696</v>
+        <v>-102.56318622704</v>
       </c>
       <c r="Q92">
-        <v>-45.88659516959998</v>
+        <v>-47.46318622703998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4547214255314764</v>
+        <v>0.5001571394794182</v>
       </c>
       <c r="T92">
-        <v>9.443912829826244</v>
+        <v>10.49323647758472</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04209055686469983</v>
+        <v>0.04162802327278005</v>
       </c>
       <c r="W92">
-        <v>0.2258750466913038</v>
+        <v>0.2259841121122785</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2882914853746564</v>
+        <v>0.2851234470738361</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2506596845753211</v>
+        <v>0.2525596845753211</v>
       </c>
       <c r="C93">
-        <v>-458.0619718637631</v>
+        <v>-467.1712131542229</v>
       </c>
       <c r="D93">
-        <v>139.2952281362368</v>
+        <v>138.0151868457771</v>
       </c>
       <c r="E93">
-        <v>708.8371999999999</v>
+        <v>716.6664</v>
       </c>
       <c r="F93">
-        <v>712.4571999999999</v>
+        <v>720.2864</v>
       </c>
       <c r="G93">
         <v>115.1</v>
@@ -9038,37 +9038,37 @@
         <v>47.9</v>
       </c>
       <c r="M93">
-        <v>167.99740776</v>
+        <v>169.84353312</v>
       </c>
       <c r="N93">
-        <v>-120.09740776</v>
+        <v>-121.94353312</v>
       </c>
       <c r="O93">
-        <v>-17.53422153296</v>
+        <v>-17.80375583552</v>
       </c>
       <c r="P93">
-        <v>-102.56318622704</v>
+        <v>-104.13977728448</v>
       </c>
       <c r="Q93">
-        <v>-47.46318622703998</v>
+        <v>-49.03977728447999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5001571394794182</v>
+        <v>0.5569517819143457</v>
       </c>
       <c r="T93">
-        <v>10.49323647758472</v>
+        <v>11.80489103728281</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04162802327278005</v>
+        <v>0.04117554475894548</v>
       </c>
       <c r="W93">
-        <v>0.2259841121122785</v>
+        <v>0.2260908065458407</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2851234470738361</v>
+        <v>0.2820242791708596</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2525596845753211</v>
+        <v>0.2544596845753211</v>
       </c>
       <c r="C94">
-        <v>-467.1712131542229</v>
+        <v>-476.2571430085821</v>
       </c>
       <c r="D94">
-        <v>138.0151868457771</v>
+        <v>136.7584569914179</v>
       </c>
       <c r="E94">
-        <v>716.6664</v>
+        <v>724.4956</v>
       </c>
       <c r="F94">
-        <v>720.2864</v>
+        <v>728.1156</v>
       </c>
       <c r="G94">
         <v>115.1</v>
@@ -9120,37 +9120,37 @@
         <v>47.9</v>
       </c>
       <c r="M94">
-        <v>169.84353312</v>
+        <v>171.68965848</v>
       </c>
       <c r="N94">
-        <v>-121.94353312</v>
+        <v>-123.78965848</v>
       </c>
       <c r="O94">
-        <v>-17.80375583552</v>
+        <v>-18.07329013808</v>
       </c>
       <c r="P94">
-        <v>-104.13977728448</v>
+        <v>-105.71636834192</v>
       </c>
       <c r="Q94">
-        <v>-49.03977728447999</v>
+        <v>-50.61636834191999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5569517819143457</v>
+        <v>0.6299734650449665</v>
       </c>
       <c r="T94">
-        <v>11.80489103728281</v>
+        <v>13.49130404260893</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04117554475894548</v>
+        <v>0.04073279696583854</v>
       </c>
       <c r="W94">
-        <v>0.2260908065458407</v>
+        <v>0.2261952064754553</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2820242791708596</v>
+        <v>0.27899176003999</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2544596845753211</v>
+        <v>0.256359684575321</v>
       </c>
       <c r="C95">
-        <v>-476.2571430085821</v>
+        <v>-485.3203924839495</v>
       </c>
       <c r="D95">
-        <v>136.7584569914179</v>
+        <v>135.5244075160505</v>
       </c>
       <c r="E95">
-        <v>724.4956</v>
+        <v>732.3248</v>
       </c>
       <c r="F95">
-        <v>728.1156</v>
+        <v>735.9448</v>
       </c>
       <c r="G95">
         <v>115.1</v>
@@ -9202,37 +9202,37 @@
         <v>47.9</v>
       </c>
       <c r="M95">
-        <v>171.68965848</v>
+        <v>173.53578384</v>
       </c>
       <c r="N95">
-        <v>-123.78965848</v>
+        <v>-125.63578384</v>
       </c>
       <c r="O95">
-        <v>-18.07329013808</v>
+        <v>-18.34282444064</v>
       </c>
       <c r="P95">
-        <v>-105.71636834192</v>
+        <v>-107.29295939936</v>
       </c>
       <c r="Q95">
-        <v>-50.61636834191999</v>
+        <v>-52.19295939935999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6299734650449665</v>
+        <v>0.7273357092191278</v>
       </c>
       <c r="T95">
-        <v>13.49130404260893</v>
+        <v>15.73985471637709</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04073279696583854</v>
+        <v>0.04029946933854239</v>
       </c>
       <c r="W95">
-        <v>0.2261952064754553</v>
+        <v>0.2262973851299717</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.27899176003999</v>
+        <v>0.2760237625927562</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.256359684575321</v>
+        <v>0.2582596845753211</v>
       </c>
       <c r="C96">
-        <v>-485.3203924839495</v>
+        <v>-494.3615700635793</v>
       </c>
       <c r="D96">
-        <v>135.5244075160505</v>
+        <v>134.3124299364208</v>
       </c>
       <c r="E96">
-        <v>732.3248</v>
+        <v>740.154</v>
       </c>
       <c r="F96">
-        <v>735.9448</v>
+        <v>743.774</v>
       </c>
       <c r="G96">
         <v>115.1</v>
@@ -9284,37 +9284,37 @@
         <v>47.9</v>
       </c>
       <c r="M96">
-        <v>173.53578384</v>
+        <v>175.3819092</v>
       </c>
       <c r="N96">
-        <v>-125.63578384</v>
+        <v>-127.4819092</v>
       </c>
       <c r="O96">
-        <v>-18.34282444064</v>
+        <v>-18.6123587432</v>
       </c>
       <c r="P96">
-        <v>-107.29295939936</v>
+        <v>-108.8695504568</v>
       </c>
       <c r="Q96">
-        <v>-52.19295939935999</v>
+        <v>-53.7695504568</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7273357092191278</v>
+        <v>0.8636428510629538</v>
       </c>
       <c r="T96">
-        <v>15.73985471637709</v>
+        <v>18.88782565965251</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04029946933854239</v>
+        <v>0.03987526439813668</v>
       </c>
       <c r="W96">
-        <v>0.2262973851299717</v>
+        <v>0.2263974126549194</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2760237625927562</v>
+        <v>0.2731182493023061</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2582596845753211</v>
+        <v>0.2601596845753211</v>
       </c>
       <c r="C97">
-        <v>-494.3615700635793</v>
+        <v>-503.3812626572998</v>
       </c>
       <c r="D97">
-        <v>134.3124299364208</v>
+        <v>133.1219373427002</v>
       </c>
       <c r="E97">
-        <v>740.154</v>
+        <v>747.9832</v>
       </c>
       <c r="F97">
-        <v>743.774</v>
+        <v>751.6032</v>
       </c>
       <c r="G97">
         <v>115.1</v>
@@ -9366,37 +9366,37 @@
         <v>47.9</v>
       </c>
       <c r="M97">
-        <v>175.3819092</v>
+        <v>177.22803456</v>
       </c>
       <c r="N97">
-        <v>-127.4819092</v>
+        <v>-129.32803456</v>
       </c>
       <c r="O97">
-        <v>-18.6123587432</v>
+        <v>-18.88189304576</v>
       </c>
       <c r="P97">
-        <v>-108.8695504568</v>
+        <v>-110.44614151424</v>
       </c>
       <c r="Q97">
-        <v>-53.7695504568</v>
+        <v>-55.34614151424</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8636428510629538</v>
+        <v>1.068103563828693</v>
       </c>
       <c r="T97">
-        <v>18.88782565965251</v>
+        <v>23.60978207456565</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03987526439813668</v>
+        <v>0.03945989706065609</v>
       </c>
       <c r="W97">
-        <v>0.2263974126549194</v>
+        <v>0.2264953562730973</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2731182493023061</v>
+        <v>0.2702732675387404</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2601596845753211</v>
+        <v>0.262059684575321</v>
       </c>
       <c r="C98">
-        <v>-503.3812626572997</v>
+        <v>-512.3800365492058</v>
       </c>
       <c r="D98">
-        <v>133.1219373427002</v>
+        <v>131.9523634507942</v>
       </c>
       <c r="E98">
-        <v>747.9831999999999</v>
+        <v>755.8123999999999</v>
       </c>
       <c r="F98">
-        <v>751.6031999999999</v>
+        <v>759.4323999999999</v>
       </c>
       <c r="G98">
         <v>115.1</v>
@@ -9448,37 +9448,37 @@
         <v>47.9</v>
       </c>
       <c r="M98">
-        <v>177.22803456</v>
+        <v>179.07415992</v>
       </c>
       <c r="N98">
-        <v>-129.32803456</v>
+        <v>-131.17415992</v>
       </c>
       <c r="O98">
-        <v>-18.88189304576</v>
+        <v>-19.15142734832</v>
       </c>
       <c r="P98">
-        <v>-110.44614151424</v>
+        <v>-112.02273257168</v>
       </c>
       <c r="Q98">
-        <v>-55.34614151424</v>
+        <v>-56.92273257167999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.06810356382869</v>
+        <v>1.408871418438253</v>
       </c>
       <c r="T98">
-        <v>23.60978207456559</v>
+        <v>31.47970943275412</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03945989706065609</v>
+        <v>0.0390530939981751</v>
       </c>
       <c r="W98">
-        <v>0.2264953562730973</v>
+        <v>0.2265912804352303</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2702732675387404</v>
+        <v>0.2674869451929802</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.262059684575321</v>
+        <v>0.263959684575321</v>
       </c>
       <c r="C99">
-        <v>-512.3800365492058</v>
+        <v>-521.358438295828</v>
       </c>
       <c r="D99">
-        <v>131.9523634507942</v>
+        <v>130.8031617041719</v>
       </c>
       <c r="E99">
-        <v>755.8123999999999</v>
+        <v>763.6415999999999</v>
       </c>
       <c r="F99">
-        <v>759.4323999999999</v>
+        <v>767.2615999999999</v>
       </c>
       <c r="G99">
         <v>115.1</v>
@@ -9530,37 +9530,37 @@
         <v>47.9</v>
       </c>
       <c r="M99">
-        <v>179.07415992</v>
+        <v>180.92028528</v>
       </c>
       <c r="N99">
-        <v>-131.17415992</v>
+        <v>-133.02028528</v>
       </c>
       <c r="O99">
-        <v>-19.15142734832</v>
+        <v>-19.42096165088</v>
       </c>
       <c r="P99">
-        <v>-112.02273257168</v>
+        <v>-113.59932362912</v>
       </c>
       <c r="Q99">
-        <v>-56.92273257167999</v>
+        <v>-58.49932362911999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.408871418438253</v>
+        <v>2.09040712765738</v>
       </c>
       <c r="T99">
-        <v>31.47970943275412</v>
+        <v>47.21956414913118</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0390530939981751</v>
+        <v>0.03865459303901005</v>
       </c>
       <c r="W99">
-        <v>0.2265912804352303</v>
+        <v>0.2266852469614014</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2674869451929802</v>
+        <v>0.264757486568562</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.263959684575321</v>
+        <v>0.2658596845753211</v>
       </c>
       <c r="C100">
-        <v>-521.358438295828</v>
+        <v>-530.3169955777742</v>
       </c>
       <c r="D100">
-        <v>130.8031617041719</v>
+        <v>129.6738044222257</v>
       </c>
       <c r="E100">
-        <v>763.6415999999999</v>
+        <v>771.4707999999999</v>
       </c>
       <c r="F100">
-        <v>767.2615999999999</v>
+        <v>775.0907999999999</v>
       </c>
       <c r="G100">
         <v>115.1</v>
@@ -9612,37 +9612,37 @@
         <v>47.9</v>
       </c>
       <c r="M100">
-        <v>180.92028528</v>
+        <v>182.76641064</v>
       </c>
       <c r="N100">
-        <v>-133.02028528</v>
+        <v>-134.86641064</v>
       </c>
       <c r="O100">
-        <v>-19.42096165088</v>
+        <v>-19.69049595344</v>
       </c>
       <c r="P100">
-        <v>-113.59932362912</v>
+        <v>-115.17591468656</v>
       </c>
       <c r="Q100">
-        <v>-58.49932362911999</v>
+        <v>-60.07591468655999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.09040712765738</v>
+        <v>4.13501425531476</v>
       </c>
       <c r="T100">
-        <v>47.21956414913118</v>
+        <v>94.43912829826236</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03865459303901005</v>
+        <v>0.03826414260427257</v>
       </c>
       <c r="W100">
-        <v>0.2266852469614014</v>
+        <v>0.2267773151739125</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.264757486568562</v>
+        <v>0.2620831685224149</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2658596845753211</v>
-      </c>
-      <c r="C101">
-        <v>-530.3169955777742</v>
-      </c>
-      <c r="D101">
-        <v>129.6738044222257</v>
-      </c>
-      <c r="E101">
-        <v>771.4707999999999</v>
-      </c>
-      <c r="F101">
-        <v>775.0907999999999</v>
-      </c>
-      <c r="G101">
-        <v>115.1</v>
-      </c>
-      <c r="H101">
-        <v>779.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>103</v>
-      </c>
-      <c r="K101">
-        <v>55.1</v>
-      </c>
-      <c r="L101">
-        <v>47.9</v>
-      </c>
-      <c r="M101">
-        <v>182.76641064</v>
-      </c>
-      <c r="N101">
-        <v>-134.86641064</v>
-      </c>
-      <c r="O101">
-        <v>-19.69049595344</v>
-      </c>
-      <c r="P101">
-        <v>-115.17591468656</v>
-      </c>
-      <c r="Q101">
-        <v>-60.07591468655999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.13501425531476</v>
-      </c>
-      <c r="T101">
-        <v>94.43912829826236</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03826414260427257</v>
-      </c>
-      <c r="W101">
-        <v>0.2267773151739125</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2620831685224149</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
